--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="250">
   <si>
     <t>site_name</t>
   </si>
@@ -61,6 +61,9 @@
     <t>1.US CBP News</t>
   </si>
   <si>
+    <t>1-1.US CBP News all</t>
+  </si>
+  <si>
     <t>2.Korea Customs 보도자료</t>
   </si>
   <si>
@@ -73,15 +76,252 @@
     <t>5.WTO News</t>
   </si>
   <si>
+    <t>52.aeo협회(공지)</t>
+  </si>
+  <si>
+    <t>53.fta korea(동향)</t>
+  </si>
+  <si>
+    <t>54.관세사회(공지)</t>
+  </si>
+  <si>
+    <t>55.관세사회(뉴스)</t>
+  </si>
+  <si>
+    <t>57.custra</t>
+  </si>
+  <si>
+    <t>59.산업통상부(보도)</t>
+  </si>
+  <si>
+    <t>60.GACC (중국 관세, 뉴스)</t>
+  </si>
+  <si>
+    <t>61.NDRC (중국,뉴스)</t>
+  </si>
+  <si>
+    <t>65.METI Japan</t>
+  </si>
+  <si>
+    <t>66.Brazil Receita</t>
+  </si>
+  <si>
+    <t>68.UNCTAD</t>
+  </si>
+  <si>
+    <t>69.OECD Trade</t>
+  </si>
+  <si>
+    <t>70.WCO News</t>
+  </si>
+  <si>
+    <t>71.WCO News</t>
+  </si>
+  <si>
+    <t>72.WCO News(origin)</t>
+  </si>
+  <si>
+    <t>83.EU Trade News</t>
+  </si>
+  <si>
+    <t>87.USITC News</t>
+  </si>
+  <si>
     <t>89.Korea Customs FTA공지사항</t>
   </si>
   <si>
     <t>90.Korea Customs 공지사항</t>
   </si>
   <si>
+    <t>1-2.US CBP rulling</t>
+  </si>
+  <si>
+    <t>12.유니패스(행정규칙</t>
+  </si>
+  <si>
+    <t>1-3.US CBP report</t>
+  </si>
+  <si>
+    <t>13.유니패스(판례)</t>
+  </si>
+  <si>
+    <t>14.유니패스(공지사항)</t>
+  </si>
+  <si>
+    <t>15.재정경제부(훈령)</t>
+  </si>
+  <si>
+    <t>16.재정경제부(예규)</t>
+  </si>
+  <si>
+    <t>17.재정경제부(고시)</t>
+  </si>
+  <si>
+    <t>18.재정경제부(지침)</t>
+  </si>
+  <si>
+    <t>19.재정경제부(입법예고)</t>
+  </si>
+  <si>
+    <t>20.재정경제부(행정예고)</t>
+  </si>
+  <si>
+    <t>21.재정경제부(공고)</t>
+  </si>
+  <si>
+    <t>22.산업통상부(입법예고)</t>
+  </si>
+  <si>
+    <t>23.산업통상부(고시)</t>
+  </si>
+  <si>
+    <t>24.산업통상부(지침)</t>
+  </si>
+  <si>
+    <t>25.산업통상부(예규)</t>
+  </si>
+  <si>
+    <t>26.산업통상부(훈령)</t>
+  </si>
+  <si>
+    <t>27.산업통상부(입법예교)</t>
+  </si>
+  <si>
+    <t>28.산업통상부(행정예고</t>
+  </si>
+  <si>
+    <t>29.산업통상부(공고)</t>
+  </si>
+  <si>
+    <t>30.관보</t>
+  </si>
+  <si>
+    <t>3-1.USTR world</t>
+  </si>
+  <si>
+    <t>31.국가법령정보센터(행정심판)</t>
+  </si>
+  <si>
+    <t>32.국가법령정보센터(시행예정)</t>
+  </si>
+  <si>
+    <t>33.국가법령정보센터(공포)</t>
+  </si>
+  <si>
+    <t>33.국가법령정보센터(최신법령)</t>
+  </si>
+  <si>
+    <t>33.국가법령정보센터(행정규칙)</t>
+  </si>
+  <si>
+    <t>35.국가법령정보센터(시행법령)</t>
+  </si>
+  <si>
+    <t>36.국가법령정보센터(공포법령)</t>
+  </si>
+  <si>
+    <t>37.입법지원센터(행정예고)</t>
+  </si>
+  <si>
+    <t>38.입법지원센터(국괴입법현황)</t>
+  </si>
+  <si>
+    <t>39.입법지원센터(입법예고)</t>
+  </si>
+  <si>
+    <t>40.입법지원센터(정부입법현황)</t>
+  </si>
+  <si>
+    <t>42.대법원(최근판결)</t>
+  </si>
+  <si>
+    <t>43.조세심판원(최근사례)</t>
+  </si>
+  <si>
+    <t>44.국회의안정보시스템(의안현황)</t>
+  </si>
+  <si>
+    <t>45.국회의안정보시스템(계류)</t>
+  </si>
+  <si>
+    <t>47.국가전략정보포털(최신동향)</t>
+  </si>
+  <si>
+    <t>48.세계법제정보센터</t>
+  </si>
+  <si>
+    <t>49.세계법제정보센터(법제동향)</t>
+  </si>
+  <si>
+    <t>50.세계법제정보센터(연구보고)</t>
+  </si>
+  <si>
+    <t>56.ciel hs(최신법령)</t>
+  </si>
+  <si>
+    <t>58.Federal Register</t>
+  </si>
+  <si>
+    <t>62.MOFCOM (중국)</t>
+  </si>
+  <si>
+    <t>63.MOFCOM (중국)</t>
+  </si>
+  <si>
+    <t>64.Japan Customs</t>
+  </si>
+  <si>
     <t>7.Korea Customs 공고</t>
   </si>
   <si>
+    <t>74.India CBIC</t>
+  </si>
+  <si>
+    <t>75.India DGFT</t>
+  </si>
+  <si>
+    <t>75-1.India DGFT public</t>
+  </si>
+  <si>
+    <t>75-2.India DGFT trade</t>
+  </si>
+  <si>
+    <t>76.CUSTOMS(일본)</t>
+  </si>
+  <si>
+    <t>77.Vietnam MOIT</t>
+  </si>
+  <si>
+    <t>78.Vietnam MOIT</t>
+  </si>
+  <si>
+    <t>78-1.Vietnam MOIT bao</t>
+  </si>
+  <si>
+    <t>78-2.Vietnam MOIT mai</t>
+  </si>
+  <si>
+    <t>79.Vietnam Customs-1</t>
+  </si>
+  <si>
+    <t>80.Vietnam Customs-2</t>
+  </si>
+  <si>
+    <t>81.Vietnam Customs-3</t>
+  </si>
+  <si>
+    <t>84.EU TAXUD</t>
+  </si>
+  <si>
+    <t>86.USITC Commission</t>
+  </si>
+  <si>
+    <t>86-1.USITC calendar</t>
+  </si>
+  <si>
+    <t>86-1.USITC Library</t>
+  </si>
+  <si>
     <t>88.Korea Customs(행정예고)</t>
   </si>
   <si>
@@ -91,255 +331,12 @@
     <t>92.관세법령(최신법령)</t>
   </si>
   <si>
-    <t>12.유니패스(행정규칙</t>
-  </si>
-  <si>
-    <t>13.유니패스(판례)</t>
-  </si>
-  <si>
-    <t>14.유니패스(공지사항)</t>
-  </si>
-  <si>
-    <t>15.재정경제부(훈령)</t>
-  </si>
-  <si>
-    <t>16.재정경제부(예규)</t>
-  </si>
-  <si>
-    <t>17.재정경제부(고시)</t>
-  </si>
-  <si>
-    <t>21.재정경제부(공고)</t>
-  </si>
-  <si>
-    <t>18.재정경제부(지침)</t>
-  </si>
-  <si>
-    <t>19.재정경제부(입법예고)</t>
-  </si>
-  <si>
-    <t>20.재정경제부(행정예고)</t>
-  </si>
-  <si>
-    <t>59.산업통상부(보도)</t>
-  </si>
-  <si>
-    <t>22.산업통상부(입법예고)</t>
-  </si>
-  <si>
-    <t>23.산업통상부(고시)</t>
-  </si>
-  <si>
-    <t>24.산업통상부(지침)</t>
-  </si>
-  <si>
-    <t>25.산업통상부(예규)</t>
-  </si>
-  <si>
-    <t>26.산업통상부(훈령)</t>
-  </si>
-  <si>
-    <t>27.산업통상부(입법예교)</t>
-  </si>
-  <si>
-    <t>28.산업통상부(행정예고</t>
-  </si>
-  <si>
-    <t>29.산업통상부(공고)</t>
-  </si>
-  <si>
-    <t>30.관보</t>
-  </si>
-  <si>
-    <t>31.국가법령정보센터(행정심판)</t>
-  </si>
-  <si>
-    <t>32.국가법령정보센터(시행예정)</t>
-  </si>
-  <si>
-    <t>33.국가법령정보센터(공포)</t>
-  </si>
-  <si>
-    <t>35.국가법령정보센터(시행법령)</t>
-  </si>
-  <si>
-    <t>36.국가법령정보센터(공포법령)</t>
-  </si>
-  <si>
-    <t>33.국가법령정보센터(행정규칙)</t>
-  </si>
-  <si>
-    <t>33.국가법령정보센터(최신법령)</t>
-  </si>
-  <si>
-    <t>37.입법지원센터(행정예고)</t>
-  </si>
-  <si>
-    <t>38.입법지원센터(국괴입법현황)</t>
-  </si>
-  <si>
-    <t>39.입법지원센터(입법예고)</t>
-  </si>
-  <si>
-    <t>40.입법지원센터(정부입법현황)</t>
-  </si>
-  <si>
-    <t>42.대법원(최근판결)</t>
-  </si>
-  <si>
-    <t>43.조세심판원(최근사례)</t>
-  </si>
-  <si>
-    <t>44.국회의안정보시스템(의안현황)</t>
-  </si>
-  <si>
-    <t>45.국회의안정보시스템(계류)</t>
-  </si>
-  <si>
-    <t>47.국가전략정보포털(최신동향)</t>
-  </si>
-  <si>
-    <t>48.세계법제정보센터</t>
-  </si>
-  <si>
-    <t>49.세계법제정보센터(법제동향)</t>
-  </si>
-  <si>
-    <t>50.세계법제정보센터(연구보고)</t>
-  </si>
-  <si>
-    <t>52.aeo협회(공지)</t>
-  </si>
-  <si>
-    <t>53.fta korea(동향)</t>
-  </si>
-  <si>
-    <t>54.관세사회(공지)</t>
-  </si>
-  <si>
-    <t>55.관세사회(뉴스)</t>
-  </si>
-  <si>
-    <t>56.ciel hs(최신법령)</t>
-  </si>
-  <si>
-    <t>57.custra</t>
-  </si>
-  <si>
-    <t>58.Federal Register</t>
-  </si>
-  <si>
-    <t>60.GACC (중국 관세, 뉴스)</t>
-  </si>
-  <si>
-    <t>61.NDRC (중국,뉴스)</t>
-  </si>
-  <si>
-    <t>62.MOFCOM (중국)</t>
-  </si>
-  <si>
-    <t>63.MOFCOM (중국)</t>
-  </si>
-  <si>
-    <t>64.Japan Customs</t>
-  </si>
-  <si>
-    <t>65.METI Japan</t>
-  </si>
-  <si>
-    <t>66.Brazil Receita</t>
-  </si>
-  <si>
-    <t>67.WTO News</t>
-  </si>
-  <si>
-    <t>68.UNCTAD</t>
-  </si>
-  <si>
-    <t>69.OECD Trade</t>
-  </si>
-  <si>
-    <t>70.WCO News</t>
-  </si>
-  <si>
-    <t>71.WCO News</t>
-  </si>
-  <si>
-    <t>72.WCO News(origin)</t>
-  </si>
-  <si>
-    <t>73.WCO News</t>
-  </si>
-  <si>
-    <t>74.India CBIC</t>
-  </si>
-  <si>
-    <t>75.India DGFT</t>
-  </si>
-  <si>
-    <t>76.CUSTOMS(일본)</t>
-  </si>
-  <si>
-    <t>77.Vietnam MOIT</t>
-  </si>
-  <si>
-    <t>78.Vietnam MOIT</t>
-  </si>
-  <si>
-    <t>79.Vietnam Customs-1</t>
-  </si>
-  <si>
-    <t>80.Vietnam Customs-2</t>
-  </si>
-  <si>
-    <t>81.Vietnam Customs-3</t>
-  </si>
-  <si>
-    <t>83.EU Trade News</t>
-  </si>
-  <si>
-    <t>84.EU TAXUD</t>
-  </si>
-  <si>
-    <t>86.USITC Commission</t>
-  </si>
-  <si>
-    <t>87.USITC News</t>
-  </si>
-  <si>
-    <t>1-1.US CBP News all</t>
-  </si>
-  <si>
-    <t>1-2.US CBP rulling</t>
-  </si>
-  <si>
-    <t>1-3.US CBP report</t>
-  </si>
-  <si>
-    <t>3-1.USTR world</t>
-  </si>
-  <si>
-    <t>86-1.USITC Library</t>
-  </si>
-  <si>
-    <t>86-1.USITC calendar</t>
-  </si>
-  <si>
-    <t>78-1.Vietnam MOIT bao</t>
-  </si>
-  <si>
-    <t>78-2.Vietnam MOIT mai</t>
-  </si>
-  <si>
-    <t>75-1.India DGFT public</t>
-  </si>
-  <si>
-    <t>75-2.India DGFT trade</t>
-  </si>
-  <si>
     <t>https://www.cbp.gov/newsroom</t>
   </si>
   <si>
+    <t>https://www.cbp.gov/newsroom/media-releases/all</t>
+  </si>
+  <si>
     <t>https://www.customs.go.kr/kcs/na/ntt/selectNttList.do?mi=2891&amp;bbsId=1362</t>
   </si>
   <si>
@@ -352,15 +349,252 @@
     <t>https://www.wto.org/english/news_e/news26_e/news26_e.htm</t>
   </si>
   <si>
+    <t>https://aeo.or.kr/sub/sub04_01.php/rss.do</t>
+  </si>
+  <si>
+    <t>https://fta.motir.go.kr/ftamain/promo/news/trend/</t>
+  </si>
+  <si>
+    <t>https://krcaa.or.kr/_Document/Notify/N20101L.aspx?MenuCode=N20101</t>
+  </si>
+  <si>
+    <t>https://krcaa.or.kr/_Document/Notify/N20601L.aspx?MenuCode=N20601</t>
+  </si>
+  <si>
+    <t>https://www.kctdi.or.kr/kctdi/research/research11.do</t>
+  </si>
+  <si>
+    <t>https://www.motie.go.kr/kor/article/ATCL3f49a5a8c</t>
+  </si>
+  <si>
+    <t>http://english.customs.gov.cn/newsroom/news</t>
+  </si>
+  <si>
+    <t>https://en.ndrc.gov.cn/news/</t>
+  </si>
+  <si>
+    <t>https://www.meti.go.jp/english/press/</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/planalto/en/latest-news</t>
+  </si>
+  <si>
+    <t>https://unctad.org/news-search</t>
+  </si>
+  <si>
+    <t>https://www.oecd.org/en/about/newsroom.html</t>
+  </si>
+  <si>
+    <t>https://www.wcoomd.org/en/media/newsroom.aspx</t>
+  </si>
+  <si>
+    <t>https://www.wcoomd.org/en/topics/nomenclature/news.aspx</t>
+  </si>
+  <si>
+    <t>https://www.wcoomd.org/en/topics/origin.aspx</t>
+  </si>
+  <si>
+    <t>https://policy.trade.ec.europa.eu/news_en</t>
+  </si>
+  <si>
+    <t>https://www.usitc.gov/news_releases</t>
+  </si>
+  <si>
     <t>https://www.customs.go.kr/ftaportalkor/na/ntt/selectNttList.do?mi=3556&amp;bbsId=1483</t>
   </si>
   <si>
     <t>https://www.customs.go.kr/kcs/na/ntt/selectNttList.do?mi=2889&amp;bbsId=1341</t>
   </si>
   <si>
+    <t>https://www.cbp.gov/trade/rulings/cbp-trade-related-federal-register-notices-2026</t>
+  </si>
+  <si>
+    <t>https://unipass.customs.go.kr/clip/lworsrch/openULS0102001Q.do?lworKcd=all</t>
+  </si>
+  <si>
+    <t>https://www.cbp.gov/newsroom/accountability-and-transparency/cbp-reports-search</t>
+  </si>
+  <si>
+    <t>https://unipass.customs.go.kr/clip/lworsrch/openULS0105001Q.do?dsbdIncdClsfCd=all</t>
+  </si>
+  <si>
+    <t>https://unipass.customs.go.kr/csp/index.do?tgMenuId=MYC_MNU_00000181</t>
+  </si>
+  <si>
+    <t>https://mofe.go.kr/lw/admrul.do?bbsId=MOSFBBS_000000000118&amp;menuNo=7090100</t>
+  </si>
+  <si>
+    <t>https://mofe.go.kr/lw/denm/TbDenmList.do?bbsId=MOSFBBS_000000000119&amp;menuNo=7090100</t>
+  </si>
+  <si>
+    <t>https://mofe.go.kr/lw/denm/TbDenmList.do?bbsId=MOSFBBS_000000000120&amp;menuNo=7090200</t>
+  </si>
+  <si>
+    <t>https://mofe.go.kr/lw/denm/TbDenmList.do?bbsId=MOSFBBS_000000000121&amp;menuNo=7090200</t>
+  </si>
+  <si>
+    <t>https://mofe.go.kr/lw/lap/TbPrvntcList.do?bbsId=MOSFBBS_000000000055&amp;menuNo=7050300</t>
+  </si>
+  <si>
+    <t>https://mofe.go.kr/lw/lap/TbPrvntcList.do?bbsId=MOSFBBS_000000000056&amp;menuNo=7050300</t>
+  </si>
+  <si>
+    <t>https://mofe.go.kr/lw/pblanc/TbPblancList.do?bbsId=MOSFBBS_000000000060&amp;menuNo=7090200</t>
+  </si>
+  <si>
+    <t>https://www.motie.go.kr/kor/article/ATCLa1cb24c71</t>
+  </si>
+  <si>
+    <t>https://www.motir.go.kr/kor/article/ATCL0c554f816</t>
+  </si>
+  <si>
+    <t>https://www.motir.go.kr/kor/article/ATCL516d59376</t>
+  </si>
+  <si>
+    <t>https://www.motir.go.kr/kor/article/ATCL520ce518e</t>
+  </si>
+  <si>
+    <t>https://www.motir.go.kr/kor/article/ATCL825d20c7e</t>
+  </si>
+  <si>
+    <t>https://www.motir.go.kr/kor/article/ATCLa1cb24c71</t>
+  </si>
+  <si>
+    <t>https://www.motir.go.kr/kor/article/ATCLa6723dc7b</t>
+  </si>
+  <si>
+    <t>https://www.motir.go.kr/kor/article/ATCLc01b2801b</t>
+  </si>
+  <si>
+    <t>https://gwanbo.go.kr/user/search/searchDaily.do</t>
+  </si>
+  <si>
+    <t>https://www.federalregister.gov/world</t>
+  </si>
+  <si>
+    <t>https://www.law.go.kr/allDeccSc.do?menuId=7&amp;subMenuId=53&amp;tabMenuId=249&amp;query=</t>
+  </si>
+  <si>
+    <t>https://www.law.go.kr/efLsPop.do?p_epubdt=</t>
+  </si>
+  <si>
+    <t>https://www.law.go.kr/lsSc.do?menuId=1&amp;subMenuId=23</t>
+  </si>
+  <si>
+    <t>https://www.law.go.kr/lsSc.do?menuId=1&amp;subMenuId=23&amp;tabMenuId=121&amp;query=</t>
+  </si>
+  <si>
+    <t>https://www.law.go.kr/admRulSc.do?menuId=5&amp;subMenuId=45&amp;tabMenuId=203&amp;query=</t>
+  </si>
+  <si>
+    <t>https://www.law.go.kr/nwEfLsPop.do?p_epubdt=</t>
+  </si>
+  <si>
+    <t>https://www.law.go.kr/nwRvsLsPop.do?p_epubdt=</t>
+  </si>
+  <si>
+    <t>https://opinion.lawmaking.go.kr/gcom/admpp</t>
+  </si>
+  <si>
+    <t>https://opinion.lawmaking.go.kr/gcom/nsmLmSts/out</t>
+  </si>
+  <si>
+    <t>https://opinion.lawmaking.go.kr/gcom/ogLmPp</t>
+  </si>
+  <si>
+    <t>https://opinion.lawmaking.go.kr/lmSts/govLm</t>
+  </si>
+  <si>
+    <t>https://www.scourt.go.kr/portal/news/NewsListAction.work?gubun=4&amp;type=5</t>
+  </si>
+  <si>
+    <t>https://www.tt.go.kr/mUser/dem/newDemList.do</t>
+  </si>
+  <si>
+    <t>https://likms.assembly.go.kr/bill/bi/bill/state/finishBillPage.do?mainProcYn=N</t>
+  </si>
+  <si>
+    <t>https://likms.assembly.go.kr/bill/bi/bill/state/mooringBillPage.do</t>
+  </si>
+  <si>
+    <t>https://nsp.nanet.go.kr/trend/latest/list.do</t>
+  </si>
+  <si>
+    <t>https://world.moleg.go.kr/web/wli/lgslInfoListPage.do</t>
+  </si>
+  <si>
+    <t>https://world.moleg.go.kr/web/dta/lgslTrendListPage.do</t>
+  </si>
+  <si>
+    <t>https://world.moleg.go.kr/web/wli/rsrchReprtListPage.do</t>
+  </si>
+  <si>
+    <t>https://www.clhs.co.kr/lawlist.asp</t>
+  </si>
+  <si>
+    <t>https://www.federalregister.gov/documents/search?order=newest</t>
+  </si>
+  <si>
+    <t>https://english.mofcom.gov.cn/News/index.html</t>
+  </si>
+  <si>
+    <t>https://english.mofcom.gov.cn/Policies/AnnouncementsOrders/index.html</t>
+  </si>
+  <si>
+    <t>https://www.customs.go.jp/english/news.rss</t>
+  </si>
+  <si>
     <t>https://www.customs.go.kr/kcs/na/ntt/selectNttList.do?mi=2895&amp;bbsId=1364</t>
   </si>
   <si>
+    <t>https://www.cbic.gov.in/entities/view-sticker</t>
+  </si>
+  <si>
+    <t>https://www.dgft.gov.in/CP/?opt=notification</t>
+  </si>
+  <si>
+    <t>https://www.dgft.gov.in/CP/?opt=public-notice</t>
+  </si>
+  <si>
+    <t>https://www.dgft.gov.in/CP/?opt=trade-notice</t>
+  </si>
+  <si>
+    <t>https://www.customs.go.jp/english/news/index_e2.htm</t>
+  </si>
+  <si>
+    <t>https://moit.gov.vn/en/news/industry-and-trade</t>
+  </si>
+  <si>
+    <t>https://moit.gov.vn/en/news/latest-news</t>
+  </si>
+  <si>
+    <t>https://moit.gov.vn/tin-tuc/thong-bao</t>
+  </si>
+  <si>
+    <t>https://moit.gov.vn/tin-tuc/xuc-tien-thuong-mai</t>
+  </si>
+  <si>
+    <t>https://www.customs.gov.vn/index.jsp?pageId=4&amp;cid=25</t>
+  </si>
+  <si>
+    <t>https://www.customs.gov.vn/index.jsp?pageId=4&amp;cid=32</t>
+  </si>
+  <si>
+    <t>https://www.customs.gov.vn/index.jsp?pageId=4&amp;cid=36</t>
+  </si>
+  <si>
+    <t>https://taxation-customs.ec.europa.eu/node/2/rss_en</t>
+  </si>
+  <si>
+    <t>https://www.usitc.gov/commission_notices</t>
+  </si>
+  <si>
+    <t>https://www.usitc.gov/calendar</t>
+  </si>
+  <si>
+    <t>https://www.usitc.gov/commission_publications_library?search=&amp;order=field_pub_arch_pub_date_1&amp;sort=desc</t>
+  </si>
+  <si>
     <t>https://www.customs.go.kr/kcs/na/ntt/selectNttList.do?mi=2897&amp;bbsId=1366</t>
   </si>
   <si>
@@ -370,306 +604,63 @@
     <t>https://unipass.customs.go.kr/clip/lworsrch/openULS0101047Q.do?lworKcd=all</t>
   </si>
   <si>
-    <t>https://unipass.customs.go.kr/clip/lworsrch/openULS0102001Q.do?lworKcd=all</t>
-  </si>
-  <si>
-    <t>https://unipass.customs.go.kr/clip/lworsrch/openULS0105001Q.do?dsbdIncdClsfCd=all</t>
-  </si>
-  <si>
-    <t>https://unipass.customs.go.kr/csp/index.do?tgMenuId=MYC_MNU_00000181</t>
-  </si>
-  <si>
-    <t>https://mofe.go.kr/lw/admrul.do?bbsId=MOSFBBS_000000000118&amp;menuNo=7090100</t>
-  </si>
-  <si>
-    <t>https://mofe.go.kr/lw/denm/TbDenmList.do?bbsId=MOSFBBS_000000000119&amp;menuNo=7090100</t>
-  </si>
-  <si>
-    <t>https://mofe.go.kr/lw/denm/TbDenmList.do?bbsId=MOSFBBS_000000000120&amp;menuNo=7090200</t>
-  </si>
-  <si>
-    <t>https://mofe.go.kr/lw/pblanc/TbPblancList.do?bbsId=MOSFBBS_000000000060&amp;menuNo=7090200</t>
-  </si>
-  <si>
-    <t>https://mofe.go.kr/lw/denm/TbDenmList.do?bbsId=MOSFBBS_000000000121&amp;menuNo=7090200</t>
-  </si>
-  <si>
-    <t>https://mofe.go.kr/lw/lap/TbPrvntcList.do?bbsId=MOSFBBS_000000000055&amp;menuNo=7050300</t>
-  </si>
-  <si>
-    <t>https://mofe.go.kr/lw/lap/TbPrvntcList.do?bbsId=MOSFBBS_000000000056&amp;menuNo=7050300</t>
-  </si>
-  <si>
-    <t>https://www.motie.go.kr/kor/article/ATCL3f49a5a8c</t>
-  </si>
-  <si>
-    <t>https://www.motie.go.kr/kor/article/ATCLa1cb24c71</t>
-  </si>
-  <si>
-    <t>https://www.motir.go.kr/kor/article/ATCL0c554f816</t>
-  </si>
-  <si>
-    <t>https://www.motir.go.kr/kor/article/ATCL516d59376</t>
-  </si>
-  <si>
-    <t>https://www.motir.go.kr/kor/article/ATCL520ce518e</t>
-  </si>
-  <si>
-    <t>https://www.motir.go.kr/kor/article/ATCL825d20c7e</t>
-  </si>
-  <si>
-    <t>https://www.motir.go.kr/kor/article/ATCLa1cb24c71</t>
-  </si>
-  <si>
-    <t>https://www.motir.go.kr/kor/article/ATCLa6723dc7b</t>
-  </si>
-  <si>
-    <t>https://www.motir.go.kr/kor/article/ATCLc01b2801b</t>
-  </si>
-  <si>
-    <t>https://gwanbo.go.kr/user/search/searchDaily.do</t>
-  </si>
-  <si>
-    <t>https://www.law.go.kr/allDeccSc.do?menuId=7&amp;subMenuId=53&amp;tabMenuId=249&amp;query=</t>
-  </si>
-  <si>
-    <t>https://www.law.go.kr/efLsPop.do?p_epubdt=</t>
-  </si>
-  <si>
-    <t>https://www.law.go.kr/lsSc.do?menuId=1&amp;subMenuId=23</t>
-  </si>
-  <si>
-    <t>https://www.law.go.kr/nwEfLsPop.do?p_epubdt=</t>
-  </si>
-  <si>
-    <t>https://www.law.go.kr/nwRvsLsPop.do?p_epubdt=</t>
-  </si>
-  <si>
-    <t>https://www.law.go.kr/admRulSc.do?menuId=5&amp;subMenuId=45&amp;tabMenuId=203&amp;query=</t>
-  </si>
-  <si>
-    <t>https://www.law.go.kr/lsSc.do?menuId=1&amp;subMenuId=23&amp;tabMenuId=121&amp;query=</t>
-  </si>
-  <si>
-    <t>https://opinion.lawmaking.go.kr/gcom/admpp</t>
-  </si>
-  <si>
-    <t>https://opinion.lawmaking.go.kr/gcom/nsmLmSts/out</t>
-  </si>
-  <si>
-    <t>https://opinion.lawmaking.go.kr/gcom/ogLmPp</t>
-  </si>
-  <si>
-    <t>https://opinion.lawmaking.go.kr/lmSts/govLm</t>
-  </si>
-  <si>
-    <t>https://www.scourt.go.kr/portal/news/NewsListAction.work?gubun=4&amp;type=5</t>
-  </si>
-  <si>
-    <t>https://www.tt.go.kr/mUser/dem/newDemList.do</t>
-  </si>
-  <si>
-    <t>https://likms.assembly.go.kr/bill/bi/bill/state/finishBillPage.do?mainProcYn=N</t>
-  </si>
-  <si>
-    <t>https://likms.assembly.go.kr/bill/bi/bill/state/mooringBillPage.do</t>
-  </si>
-  <si>
-    <t>https://nsp.nanet.go.kr/trend/latest/list.do</t>
-  </si>
-  <si>
-    <t>https://world.moleg.go.kr/web/wli/lgslInfoListPage.do</t>
-  </si>
-  <si>
-    <t>https://world.moleg.go.kr/web/dta/lgslTrendListPage.do</t>
-  </si>
-  <si>
-    <t>https://world.moleg.go.kr/web/wli/rsrchReprtListPage.do</t>
-  </si>
-  <si>
-    <t>https://aeo.or.kr/sub/sub04_01.php/rss.do</t>
-  </si>
-  <si>
-    <t>https://fta.motir.go.kr/ftamain/promo/news/trend/</t>
-  </si>
-  <si>
-    <t>https://krcaa.or.kr/_Document/Notify/N20101L.aspx?MenuCode=N20101</t>
-  </si>
-  <si>
-    <t>https://krcaa.or.kr/_Document/Notify/N20601L.aspx?MenuCode=N20601</t>
-  </si>
-  <si>
-    <t>https://www.clhs.co.kr/lawlist.asp</t>
-  </si>
-  <si>
-    <t>https://www.kctdi.or.kr/kctdi/research/research11.do</t>
-  </si>
-  <si>
-    <t>https://www.federalregister.gov/documents/search?order=newest</t>
-  </si>
-  <si>
-    <t>http://english.customs.gov.cn/newsroom/news</t>
-  </si>
-  <si>
-    <t>https://en.ndrc.gov.cn/news/</t>
-  </si>
-  <si>
-    <t>https://english.mofcom.gov.cn/News/index.html</t>
-  </si>
-  <si>
-    <t>https://english.mofcom.gov.cn/Policies/AnnouncementsOrders/index.html</t>
-  </si>
-  <si>
-    <t>https://www.customs.go.jp/english/news.rss</t>
-  </si>
-  <si>
-    <t>https://www.meti.go.jp/english/press/</t>
-  </si>
-  <si>
-    <t>https://www.gov.br/planalto/en/latest-news</t>
-  </si>
-  <si>
-    <t>http://www.wto.org/library/rss/latest_news_e.xml</t>
-  </si>
-  <si>
-    <t>https://unctad.org/news-search</t>
-  </si>
-  <si>
-    <t>https://www.oecd.org/en/about/newsroom.html</t>
-  </si>
-  <si>
-    <t>https://www.wcoomd.org/en/media/newsroom.aspx</t>
-  </si>
-  <si>
-    <t>https://www.wcoomd.org/en/topics/nomenclature/news.aspx</t>
-  </si>
-  <si>
-    <t>https://www.wcoomd.org/en/topics/origin.aspx</t>
-  </si>
-  <si>
-    <t>https://www.worldbank.org/en/topic/trade/brief/trade-news</t>
-  </si>
-  <si>
-    <t>https://www.cbic.gov.in/entities/view-sticker</t>
-  </si>
-  <si>
-    <t>https://www.dgft.gov.in/CP/?opt=notification</t>
-  </si>
-  <si>
-    <t>https://www.customs.go.jp/english/news/index_e2.htm</t>
-  </si>
-  <si>
-    <t>https://moit.gov.vn/en/news/industry-and-trade</t>
-  </si>
-  <si>
-    <t>https://moit.gov.vn/en/news/latest-news</t>
-  </si>
-  <si>
-    <t>https://www.customs.gov.vn/index.jsp?pageId=4&amp;cid=25</t>
-  </si>
-  <si>
-    <t>https://www.customs.gov.vn/index.jsp?pageId=4&amp;cid=32</t>
-  </si>
-  <si>
-    <t>https://www.customs.gov.vn/index.jsp?pageId=4&amp;cid=36</t>
-  </si>
-  <si>
-    <t>https://policy.trade.ec.europa.eu/news_en</t>
-  </si>
-  <si>
-    <t>https://taxation-customs.ec.europa.eu/node/2/rss_en</t>
-  </si>
-  <si>
-    <t>https://www.usitc.gov/commission_notices</t>
-  </si>
-  <si>
-    <t>https://www.usitc.gov/news_releases</t>
-  </si>
-  <si>
-    <t>https://www.cbp.gov/newsroom/media-releases/all</t>
-  </si>
-  <si>
-    <t>https://www.cbp.gov/trade/rulings/cbp-trade-related-federal-register-notices-2026</t>
-  </si>
-  <si>
-    <t>https://www.cbp.gov/newsroom/accountability-and-transparency/cbp-reports-search</t>
-  </si>
-  <si>
-    <t>https://www.federalregister.gov/world</t>
-  </si>
-  <si>
-    <t>https://www.usitc.gov/commission_publications_library?search=&amp;order=field_pub_arch_pub_date_1&amp;sort=desc</t>
-  </si>
-  <si>
-    <t>https://www.usitc.gov/calendar</t>
-  </si>
-  <si>
-    <t>https://moit.gov.vn/tin-tuc/thong-bao</t>
-  </si>
-  <si>
-    <t>https://moit.gov.vn/tin-tuc/xuc-tien-thuong-mai</t>
-  </si>
-  <si>
-    <t>https://www.dgft.gov.in/CP/?opt=public-notice</t>
-  </si>
-  <si>
-    <t>https://www.dgft.gov.in/CP/?opt=trade-notice</t>
-  </si>
-  <si>
     <t>cbp</t>
   </si>
   <si>
+    <t>korea</t>
+  </si>
+  <si>
+    <t>ustr</t>
+  </si>
+  <si>
+    <t>eu</t>
+  </si>
+  <si>
+    <t>wto</t>
+  </si>
+  <si>
+    <t>rss</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>krcaa</t>
+  </si>
+  <si>
+    <t>custra</t>
+  </si>
+  <si>
+    <t>motie</t>
+  </si>
+  <si>
+    <t>oecd</t>
+  </si>
+  <si>
+    <t>usitc</t>
+  </si>
+  <si>
+    <t>cbp_ruling</t>
+  </si>
+  <si>
+    <t>unipass</t>
+  </si>
+  <si>
+    <t>gwanbo</t>
+  </si>
+  <si>
+    <t>law_decision</t>
+  </si>
+  <si>
+    <t>law</t>
+  </si>
+  <si>
+    <t>nsp</t>
+  </si>
+  <si>
     <t>cbp_parser</t>
   </si>
   <si>
-    <t>ustr</t>
-  </si>
-  <si>
-    <t>eu</t>
-  </si>
-  <si>
-    <t>wto</t>
-  </si>
-  <si>
-    <t>korea_fta</t>
-  </si>
-  <si>
-    <t>korea_notice</t>
-  </si>
-  <si>
-    <t>korea</t>
-  </si>
-  <si>
-    <t>table</t>
-  </si>
-  <si>
-    <t>motie</t>
-  </si>
-  <si>
-    <t>gwanbo</t>
-  </si>
-  <si>
-    <t>law</t>
-  </si>
-  <si>
-    <t>nsp</t>
-  </si>
-  <si>
-    <t>rss</t>
-  </si>
-  <si>
-    <t>krcaa</t>
-  </si>
-  <si>
-    <t>custra</t>
-  </si>
-  <si>
-    <t>oecd</t>
-  </si>
-  <si>
-    <t>usitc</t>
-  </si>
-  <si>
     <t>customs_board</t>
   </si>
   <si>
@@ -682,39 +673,48 @@
     <t>wto_parser</t>
   </si>
   <si>
+    <t>rss_parser</t>
+  </si>
+  <si>
     <t>table_date</t>
   </si>
   <si>
+    <t>krcaa_parser</t>
+  </si>
+  <si>
+    <t>custra_parser</t>
+  </si>
+  <si>
     <t>motie_parser</t>
   </si>
   <si>
+    <t>card_parser</t>
+  </si>
+  <si>
+    <t>oecd_parser</t>
+  </si>
+  <si>
+    <t>usitc_parser</t>
+  </si>
+  <si>
+    <t>cbp_ruling_parser</t>
+  </si>
+  <si>
+    <t>unipass_parser</t>
+  </si>
+  <si>
     <t>gwanbo_parser</t>
   </si>
   <si>
+    <t>law_decision_parser</t>
+  </si>
+  <si>
     <t>law_parser</t>
   </si>
   <si>
     <t>nsp_parser</t>
   </si>
   <si>
-    <t>rss_parser</t>
-  </si>
-  <si>
-    <t>krcaa_parser</t>
-  </si>
-  <si>
-    <t>custra_parser</t>
-  </si>
-  <si>
-    <t>card_parser</t>
-  </si>
-  <si>
-    <t>oecd_parser</t>
-  </si>
-  <si>
-    <t>usitc_parser</t>
-  </si>
-  <si>
     <t>🇺🇸</t>
   </si>
   <si>
@@ -745,7 +745,10 @@
     <t>VN</t>
   </si>
   <si>
-    <t>policy</t>
+    <t>news</t>
+  </si>
+  <si>
+    <t>regulation</t>
   </si>
   <si>
     <t>customs</t>
@@ -761,42 +764,6 @@
   </si>
   <si>
     <t>CHECK</t>
-  </si>
-  <si>
-    <t>있음</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>4/20</t>
-  </si>
-  <si>
-    <t>generic</t>
-  </si>
-  <si>
-    <t>4/24</t>
-  </si>
-  <si>
-    <t>RSS</t>
-  </si>
-  <si>
-    <t>5/07</t>
-  </si>
-  <si>
-    <t>조회실패</t>
-  </si>
-  <si>
-    <t>날짜없음</t>
-  </si>
-  <si>
-    <t>5/11</t>
-  </si>
-  <si>
-    <t>5/08</t>
   </si>
 </sst>
 </file>
@@ -1145,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1197,13 +1164,13 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="E2" t="s">
         <v>233</v>
@@ -1212,7 +1179,7 @@
         <v>243</v>
       </c>
       <c r="G2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -1224,16 +1191,16 @@
         <v>5</v>
       </c>
       <c r="K2">
-        <v>200</v>
+        <v>431</v>
       </c>
       <c r="L2" s="2">
-        <v>46161.06959490741</v>
+        <v>46179.1761574074</v>
       </c>
       <c r="M2" t="s">
-        <v>247</v>
-      </c>
-      <c r="N2" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="N2" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1241,22 +1208,22 @@
         <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F3" t="s">
         <v>243</v>
       </c>
       <c r="G3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -1265,19 +1232,19 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K3">
-        <v>357</v>
+        <v>649</v>
       </c>
       <c r="L3" s="2">
-        <v>46161.06967592592</v>
+        <v>46179.17616898148</v>
       </c>
       <c r="M3" t="s">
-        <v>247</v>
-      </c>
-      <c r="N3" t="s">
-        <v>250</v>
+        <v>248</v>
+      </c>
+      <c r="N3" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1285,16 +1252,16 @@
         <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F4" t="s">
         <v>243</v>
@@ -1309,19 +1276,19 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>546</v>
+        <v>796</v>
       </c>
       <c r="L4" s="2">
-        <v>46161.06969907408</v>
+        <v>46179.17626157407</v>
       </c>
       <c r="M4" t="s">
-        <v>247</v>
-      </c>
-      <c r="N4" t="s">
-        <v>250</v>
+        <v>248</v>
+      </c>
+      <c r="N4" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1329,16 +1296,16 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F5" t="s">
         <v>243</v>
@@ -1353,19 +1320,19 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K5">
-        <v>673</v>
+        <v>1807</v>
       </c>
       <c r="L5" s="2">
-        <v>46161.06972222222</v>
+        <v>46179.17628472222</v>
       </c>
       <c r="M5" t="s">
-        <v>247</v>
-      </c>
-      <c r="N5" t="s">
-        <v>250</v>
+        <v>248</v>
+      </c>
+      <c r="N5" s="2">
+        <v>46161</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1373,22 +1340,22 @@
         <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F6" t="s">
         <v>243</v>
       </c>
       <c r="G6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -1397,19 +1364,19 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K6">
-        <v>74</v>
+        <v>1934</v>
       </c>
       <c r="L6" s="2">
-        <v>46161.0697337963</v>
+        <v>46179.17631944444</v>
       </c>
       <c r="M6" t="s">
-        <v>247</v>
-      </c>
-      <c r="N6" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="N6" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1417,22 +1384,22 @@
         <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D7" t="s">
         <v>218</v>
       </c>
       <c r="E7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F7" t="s">
         <v>243</v>
       </c>
       <c r="G7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -1441,19 +1408,19 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>220</v>
+        <v>351</v>
       </c>
       <c r="L7" s="2">
-        <v>46161.06974537037</v>
+        <v>46179.17633101852</v>
       </c>
       <c r="M7" t="s">
-        <v>247</v>
-      </c>
-      <c r="N7" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="N7" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1461,13 +1428,13 @@
         <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E8" t="s">
         <v>234</v>
@@ -1476,7 +1443,7 @@
         <v>243</v>
       </c>
       <c r="G8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -1488,16 +1455,16 @@
         <v>20</v>
       </c>
       <c r="K8">
-        <v>220</v>
+        <v>1141</v>
       </c>
       <c r="L8" s="2">
-        <v>46161.06976851852</v>
+        <v>46179.17635416667</v>
       </c>
       <c r="M8" t="s">
-        <v>247</v>
-      </c>
-      <c r="N8">
-        <v>4.2</v>
+        <v>248</v>
+      </c>
+      <c r="N8" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1505,13 +1472,13 @@
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E9" t="s">
         <v>234</v>
@@ -1520,7 +1487,7 @@
         <v>243</v>
       </c>
       <c r="G9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -1529,19 +1496,19 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>220</v>
+        <v>1133</v>
       </c>
       <c r="L9" s="2">
-        <v>46161.06978009259</v>
+        <v>46179.17637731481</v>
       </c>
       <c r="M9" t="s">
-        <v>247</v>
-      </c>
-      <c r="N9" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="N9" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1549,13 +1516,13 @@
         <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E10" t="s">
         <v>234</v>
@@ -1564,7 +1531,7 @@
         <v>243</v>
       </c>
       <c r="G10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H10">
         <v>5</v>
@@ -1573,19 +1540,19 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>220</v>
+        <v>430</v>
       </c>
       <c r="L10" s="2">
-        <v>46161.06980324074</v>
+        <v>46179.17640046297</v>
       </c>
       <c r="M10" t="s">
-        <v>247</v>
-      </c>
-      <c r="N10" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="N10" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1593,13 +1560,13 @@
         <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D11" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E11" t="s">
         <v>234</v>
@@ -1608,7 +1575,7 @@
         <v>243</v>
       </c>
       <c r="G11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H11">
         <v>5</v>
@@ -1617,19 +1584,19 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>357</v>
+        <v>454</v>
       </c>
       <c r="L11" s="2">
-        <v>46161.06981481481</v>
+        <v>46179.17642361111</v>
       </c>
       <c r="M11" t="s">
-        <v>247</v>
-      </c>
-      <c r="N11" t="s">
-        <v>251</v>
+        <v>248</v>
+      </c>
+      <c r="N11" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1637,13 +1604,13 @@
         <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E12" t="s">
         <v>234</v>
@@ -1652,7 +1619,7 @@
         <v>243</v>
       </c>
       <c r="G12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1661,19 +1628,19 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K12">
-        <v>357</v>
+        <v>1735</v>
       </c>
       <c r="L12" s="2">
-        <v>46161.06982638889</v>
+        <v>46179.17643518518</v>
       </c>
       <c r="M12" t="s">
-        <v>247</v>
-      </c>
-      <c r="N12" t="s">
-        <v>251</v>
+        <v>248</v>
+      </c>
+      <c r="N12" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1681,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D13" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E13" t="s">
         <v>234</v>
@@ -1696,7 +1663,7 @@
         <v>243</v>
       </c>
       <c r="G13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -1705,19 +1672,19 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>357</v>
+        <v>103</v>
       </c>
       <c r="L13" s="2">
-        <v>46161.06982638889</v>
+        <v>46179.17644675926</v>
       </c>
       <c r="M13" t="s">
-        <v>247</v>
-      </c>
-      <c r="N13" t="s">
-        <v>251</v>
+        <v>249</v>
+      </c>
+      <c r="N13" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1725,22 +1692,22 @@
         <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D14" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F14" t="s">
         <v>243</v>
       </c>
       <c r="G14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -1749,19 +1716,19 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K14">
-        <v>357</v>
+        <v>1482</v>
       </c>
       <c r="L14" s="2">
-        <v>46161.06983796296</v>
+        <v>46179.17648148148</v>
       </c>
       <c r="M14" t="s">
-        <v>247</v>
-      </c>
-      <c r="N14" t="s">
-        <v>251</v>
+        <v>248</v>
+      </c>
+      <c r="N14" s="2">
+        <v>46087</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1769,22 +1736,22 @@
         <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D15" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F15" t="s">
         <v>243</v>
       </c>
       <c r="G15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H15">
         <v>5</v>
@@ -1793,19 +1760,19 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K15">
-        <v>357</v>
+        <v>1317</v>
       </c>
       <c r="L15" s="2">
-        <v>46161.06984953704</v>
+        <v>46179.17649305556</v>
       </c>
       <c r="M15" t="s">
-        <v>247</v>
-      </c>
-      <c r="N15" t="s">
-        <v>251</v>
+        <v>248</v>
+      </c>
+      <c r="N15" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1813,22 +1780,22 @@
         <v>28</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D16" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E16" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F16" t="s">
         <v>243</v>
       </c>
       <c r="G16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H16">
         <v>5</v>
@@ -1840,16 +1807,16 @@
         <v>1</v>
       </c>
       <c r="K16">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="L16" s="2">
-        <v>46161.06986111111</v>
+        <v>46179.17679398148</v>
       </c>
       <c r="M16" t="s">
-        <v>248</v>
-      </c>
-      <c r="N16" t="s">
-        <v>252</v>
+        <v>249</v>
+      </c>
+      <c r="N16" s="2">
+        <v>46163</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1857,22 +1824,22 @@
         <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E17" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F17" t="s">
         <v>243</v>
       </c>
       <c r="G17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H17">
         <v>5</v>
@@ -1881,19 +1848,19 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K17">
-        <v>184</v>
+        <v>1525</v>
       </c>
       <c r="L17" s="2">
-        <v>46161.06987268518</v>
+        <v>46179.17684027777</v>
       </c>
       <c r="M17" t="s">
         <v>248</v>
       </c>
-      <c r="N17" t="s">
-        <v>208</v>
+      <c r="N17" s="2">
+        <v>46155</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1901,22 +1868,22 @@
         <v>30</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D18" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E18" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F18" t="s">
         <v>243</v>
       </c>
       <c r="G18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -1925,19 +1892,19 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>202</v>
+        <v>56</v>
       </c>
       <c r="L18" s="2">
-        <v>46161.06988425926</v>
+        <v>46179.17685185185</v>
       </c>
       <c r="M18" t="s">
-        <v>247</v>
-      </c>
-      <c r="N18" t="s">
-        <v>208</v>
+        <v>249</v>
+      </c>
+      <c r="N18" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1945,22 +1912,22 @@
         <v>31</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D19" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E19" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F19" t="s">
         <v>243</v>
       </c>
       <c r="G19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -1969,19 +1936,19 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>220</v>
+        <v>56</v>
       </c>
       <c r="L19" s="2">
-        <v>46161.06990740741</v>
+        <v>46179.176875</v>
       </c>
       <c r="M19" t="s">
-        <v>247</v>
-      </c>
-      <c r="N19" t="s">
-        <v>208</v>
+        <v>249</v>
+      </c>
+      <c r="N19" s="2">
+        <v>46155</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1989,22 +1956,22 @@
         <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D20" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E20" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F20" t="s">
         <v>243</v>
       </c>
       <c r="G20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -2013,19 +1980,19 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K20">
-        <v>203</v>
+        <v>1660</v>
       </c>
       <c r="L20" s="2">
-        <v>46161.06991898148</v>
+        <v>46179.17693287037</v>
       </c>
       <c r="M20" t="s">
-        <v>247</v>
-      </c>
-      <c r="N20" t="s">
-        <v>253</v>
+        <v>248</v>
+      </c>
+      <c r="N20" s="2">
+        <v>46045</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -2033,22 +2000,22 @@
         <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D21" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E21" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F21" t="s">
         <v>243</v>
       </c>
       <c r="G21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -2057,19 +2024,19 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K21">
-        <v>240</v>
+        <v>1463</v>
       </c>
       <c r="L21" s="2">
-        <v>46161.06994212963</v>
+        <v>46179.17712962963</v>
       </c>
       <c r="M21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N21" s="2">
-        <v>46142</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -2077,22 +2044,22 @@
         <v>34</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D22" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E22" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F22" t="s">
         <v>243</v>
       </c>
       <c r="G22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H22">
         <v>5</v>
@@ -2101,19 +2068,19 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K22">
-        <v>260</v>
+        <v>1434</v>
       </c>
       <c r="L22" s="2">
-        <v>46161.06995370371</v>
+        <v>46179.17719907407</v>
       </c>
       <c r="M22" t="s">
-        <v>247</v>
-      </c>
-      <c r="N22" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N22" s="2">
+        <v>46129</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -2121,22 +2088,22 @@
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C23" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D23" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F23" t="s">
         <v>243</v>
       </c>
       <c r="G23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H23">
         <v>5</v>
@@ -2145,19 +2112,19 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K23">
-        <v>12</v>
+        <v>1896</v>
       </c>
       <c r="L23" s="2">
-        <v>46161.06996527778</v>
+        <v>46179.17722222222</v>
       </c>
       <c r="M23" t="s">
         <v>248</v>
       </c>
       <c r="N23" s="2">
-        <v>46155</v>
+        <v>46172</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -2165,22 +2132,22 @@
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C24" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D24" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F24" t="s">
         <v>243</v>
       </c>
       <c r="G24" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -2189,19 +2156,19 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="L24" s="2">
-        <v>46161.07</v>
+        <v>46179.17724537037</v>
       </c>
       <c r="M24" t="s">
-        <v>247</v>
-      </c>
-      <c r="N24" t="s">
-        <v>254</v>
+        <v>249</v>
+      </c>
+      <c r="N24" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -2209,13 +2176,13 @@
         <v>37</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D25" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E25" t="s">
         <v>234</v>
@@ -2224,7 +2191,7 @@
         <v>243</v>
       </c>
       <c r="G25" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H25">
         <v>5</v>
@@ -2233,19 +2200,19 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>148</v>
+        <v>892</v>
       </c>
       <c r="L25" s="2">
-        <v>46161.07</v>
+        <v>46179.17725694444</v>
       </c>
       <c r="M25" t="s">
         <v>248</v>
       </c>
-      <c r="N25" t="s">
-        <v>208</v>
+      <c r="N25" s="2">
+        <v>46148</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -2253,13 +2220,13 @@
         <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D26" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E26" t="s">
         <v>234</v>
@@ -2268,7 +2235,7 @@
         <v>243</v>
       </c>
       <c r="G26" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -2277,19 +2244,19 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>145</v>
+        <v>901</v>
       </c>
       <c r="L26" s="2">
-        <v>46161.07002314815</v>
+        <v>46179.17726851852</v>
       </c>
       <c r="M26" t="s">
-        <v>247</v>
-      </c>
-      <c r="N26" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N26" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2297,22 +2264,22 @@
         <v>39</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D27" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E27" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F27" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G27" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -2321,19 +2288,19 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K27">
-        <v>165</v>
+        <v>514</v>
       </c>
       <c r="L27" s="2">
-        <v>46161.0700462963</v>
+        <v>46179.17729166667</v>
       </c>
       <c r="M27" t="s">
-        <v>247</v>
-      </c>
-      <c r="N27" t="s">
-        <v>208</v>
+        <v>249</v>
+      </c>
+      <c r="N27" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2341,22 +2308,22 @@
         <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
         <v>209</v>
       </c>
       <c r="D28" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E28" t="s">
         <v>234</v>
       </c>
       <c r="F28" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G28" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H28">
         <v>5</v>
@@ -2365,19 +2332,19 @@
         <v>1</v>
       </c>
       <c r="J28">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>165</v>
+        <v>792</v>
       </c>
       <c r="L28" s="2">
-        <v>46161.07005787037</v>
+        <v>46179.17743055556</v>
       </c>
       <c r="M28" t="s">
-        <v>247</v>
-      </c>
-      <c r="N28" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N28" s="2">
+        <v>46160</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -2385,22 +2352,22 @@
         <v>41</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="D29" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F29" t="s">
         <v>243</v>
       </c>
       <c r="G29" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -2409,19 +2376,19 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K29">
-        <v>156</v>
+        <v>403</v>
       </c>
       <c r="L29" s="2">
-        <v>46161.07008101852</v>
+        <v>46179.17746527777</v>
       </c>
       <c r="M29" t="s">
-        <v>247</v>
-      </c>
-      <c r="N29" t="s">
-        <v>208</v>
+        <v>249</v>
+      </c>
+      <c r="N29" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2429,22 +2396,22 @@
         <v>42</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s">
         <v>209</v>
       </c>
       <c r="D30" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E30" t="s">
         <v>234</v>
       </c>
       <c r="F30" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G30" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -2453,19 +2420,19 @@
         <v>1</v>
       </c>
       <c r="J30">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>167</v>
+        <v>776</v>
       </c>
       <c r="L30" s="2">
-        <v>46161.07009259259</v>
+        <v>46179.17758101852</v>
       </c>
       <c r="M30" t="s">
-        <v>247</v>
-      </c>
-      <c r="N30" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N30" s="2">
+        <v>46142</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2473,22 +2440,22 @@
         <v>43</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C31" t="s">
         <v>209</v>
       </c>
       <c r="D31" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E31" t="s">
         <v>234</v>
       </c>
       <c r="F31" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G31" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H31">
         <v>5</v>
@@ -2497,19 +2464,19 @@
         <v>1</v>
       </c>
       <c r="J31">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K31">
-        <v>169</v>
+        <v>861</v>
       </c>
       <c r="L31" s="2">
-        <v>46161.07011574074</v>
+        <v>46179.17774305555</v>
       </c>
       <c r="M31" t="s">
-        <v>247</v>
-      </c>
-      <c r="N31" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N31" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -2517,22 +2484,22 @@
         <v>44</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D32" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E32" t="s">
         <v>234</v>
       </c>
       <c r="F32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G32" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H32">
         <v>5</v>
@@ -2544,16 +2511,16 @@
         <v>1</v>
       </c>
       <c r="K32">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="L32" s="2">
-        <v>46161.07012731482</v>
+        <v>46179.17775462963</v>
       </c>
       <c r="M32" t="s">
-        <v>248</v>
-      </c>
-      <c r="N32" t="s">
-        <v>208</v>
+        <v>249</v>
+      </c>
+      <c r="N32" s="2">
+        <v>46132</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2561,22 +2528,22 @@
         <v>45</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D33" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E33" t="s">
         <v>234</v>
       </c>
       <c r="F33" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G33" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H33">
         <v>5</v>
@@ -2585,19 +2552,19 @@
         <v>1</v>
       </c>
       <c r="J33">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K33">
-        <v>156</v>
+        <v>954</v>
       </c>
       <c r="L33" s="2">
-        <v>46161.07015046296</v>
+        <v>46179.17776620371</v>
       </c>
       <c r="M33" t="s">
-        <v>247</v>
-      </c>
-      <c r="N33" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N33" s="2">
+        <v>46113</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2605,22 +2572,22 @@
         <v>46</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D34" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E34" t="s">
         <v>234</v>
       </c>
       <c r="F34" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G34" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -2629,19 +2596,19 @@
         <v>1</v>
       </c>
       <c r="J34">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K34">
-        <v>219</v>
+        <v>1222</v>
       </c>
       <c r="L34" s="2">
-        <v>46161.07016203704</v>
+        <v>46179.17777777778</v>
       </c>
       <c r="M34" t="s">
-        <v>247</v>
-      </c>
-      <c r="N34" t="s">
-        <v>208</v>
+        <v>249</v>
+      </c>
+      <c r="N34" s="2">
+        <v>46140</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2649,22 +2616,22 @@
         <v>47</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D35" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E35" t="s">
         <v>234</v>
       </c>
       <c r="F35" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G35" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -2673,19 +2640,19 @@
         <v>1</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="K35">
-        <v>39</v>
+        <v>1232</v>
       </c>
       <c r="L35" s="2">
-        <v>46161.07017361111</v>
+        <v>46179.17780092593</v>
       </c>
       <c r="M35" t="s">
-        <v>247</v>
-      </c>
-      <c r="N35" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="N35" s="2">
+        <v>46024</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2693,22 +2660,22 @@
         <v>48</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C36" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D36" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E36" t="s">
         <v>234</v>
       </c>
       <c r="F36" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G36" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H36">
         <v>5</v>
@@ -2717,19 +2684,19 @@
         <v>1</v>
       </c>
       <c r="J36">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K36">
-        <v>403</v>
+        <v>1501</v>
       </c>
       <c r="L36" s="2">
-        <v>46161.07018518518</v>
+        <v>46179.1778125</v>
       </c>
       <c r="M36" t="s">
-        <v>247</v>
-      </c>
-      <c r="N36" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N36" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2737,22 +2704,22 @@
         <v>49</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C37" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D37" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E37" t="s">
         <v>234</v>
       </c>
       <c r="F37" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G37" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H37">
         <v>5</v>
@@ -2761,19 +2728,19 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K37">
-        <v>415</v>
+        <v>1463</v>
       </c>
       <c r="L37" s="2">
-        <v>46161.07020833333</v>
+        <v>46179.17783564814</v>
       </c>
       <c r="M37" t="s">
-        <v>247</v>
-      </c>
-      <c r="N37" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N37" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2781,22 +2748,22 @@
         <v>50</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C38" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D38" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E38" t="s">
         <v>234</v>
       </c>
       <c r="F38" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G38" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H38">
         <v>5</v>
@@ -2805,19 +2772,19 @@
         <v>1</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="K38">
-        <v>39</v>
+        <v>1443</v>
       </c>
       <c r="L38" s="2">
-        <v>46161.07021990741</v>
+        <v>46179.17784722222</v>
       </c>
       <c r="M38" t="s">
-        <v>247</v>
-      </c>
-      <c r="N38" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="N38" s="2">
+        <v>46112</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2825,22 +2792,22 @@
         <v>51</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D39" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E39" t="s">
         <v>234</v>
       </c>
       <c r="F39" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G39" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H39">
         <v>5</v>
@@ -2849,19 +2816,19 @@
         <v>1</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K39">
-        <v>39</v>
+        <v>342</v>
       </c>
       <c r="L39" s="2">
-        <v>46161.07024305555</v>
+        <v>46179.1778587963</v>
       </c>
       <c r="M39" t="s">
-        <v>247</v>
-      </c>
-      <c r="N39" t="s">
         <v>249</v>
+      </c>
+      <c r="N39" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2869,22 +2836,22 @@
         <v>52</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C40" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D40" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E40" t="s">
         <v>234</v>
       </c>
       <c r="F40" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G40" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H40">
         <v>5</v>
@@ -2893,19 +2860,19 @@
         <v>1</v>
       </c>
       <c r="J40">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K40">
-        <v>535</v>
+        <v>569</v>
       </c>
       <c r="L40" s="2">
-        <v>46161.0702662037</v>
+        <v>46179.17788194444</v>
       </c>
       <c r="M40" t="s">
-        <v>247</v>
-      </c>
-      <c r="N40" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N40" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2913,22 +2880,22 @@
         <v>53</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C41" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E41" t="s">
         <v>234</v>
       </c>
       <c r="F41" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G41" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -2937,19 +2904,19 @@
         <v>1</v>
       </c>
       <c r="J41">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K41">
-        <v>704</v>
+        <v>665</v>
       </c>
       <c r="L41" s="2">
-        <v>46161.07027777778</v>
+        <v>46179.17790509259</v>
       </c>
       <c r="M41" t="s">
-        <v>247</v>
-      </c>
-      <c r="N41" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N41" s="2">
+        <v>46185</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2957,22 +2924,22 @@
         <v>54</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C42" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D42" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E42" t="s">
         <v>234</v>
       </c>
       <c r="F42" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G42" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H42">
         <v>5</v>
@@ -2981,19 +2948,19 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K42">
-        <v>741</v>
+        <v>663</v>
       </c>
       <c r="L42" s="2">
-        <v>46161.0703125</v>
+        <v>46179.17791666667</v>
       </c>
       <c r="M42" t="s">
-        <v>247</v>
-      </c>
-      <c r="N42" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N42" s="2">
+        <v>46149</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -3001,22 +2968,22 @@
         <v>55</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C43" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D43" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E43" t="s">
         <v>234</v>
       </c>
       <c r="F43" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G43" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H43">
         <v>5</v>
@@ -3025,19 +2992,19 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K43">
-        <v>233</v>
+        <v>707</v>
       </c>
       <c r="L43" s="2">
-        <v>46161.07032407408</v>
+        <v>46179.17793981481</v>
       </c>
       <c r="M43" t="s">
-        <v>247</v>
-      </c>
-      <c r="N43" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N43" s="2">
+        <v>46149</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -3045,22 +3012,22 @@
         <v>56</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D44" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E44" t="s">
         <v>234</v>
       </c>
       <c r="F44" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G44" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H44">
         <v>5</v>
@@ -3069,19 +3036,19 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K44">
-        <v>194</v>
+        <v>709</v>
       </c>
       <c r="L44" s="2">
-        <v>46161.07033564815</v>
+        <v>46179.17796296296</v>
       </c>
       <c r="M44" t="s">
-        <v>247</v>
-      </c>
-      <c r="N44" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N44" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -3089,22 +3056,22 @@
         <v>57</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D45" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E45" t="s">
         <v>234</v>
       </c>
       <c r="F45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H45">
         <v>5</v>
@@ -3113,19 +3080,19 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K45">
-        <v>260</v>
+        <v>720</v>
       </c>
       <c r="L45" s="2">
-        <v>46161.07037037037</v>
+        <v>46179.17797453704</v>
       </c>
       <c r="M45" t="s">
-        <v>247</v>
-      </c>
-      <c r="N45" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N45" s="2">
+        <v>46160</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -3133,22 +3100,22 @@
         <v>58</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C46" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D46" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E46" t="s">
         <v>234</v>
       </c>
       <c r="F46" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H46">
         <v>5</v>
@@ -3157,19 +3124,19 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K46">
-        <v>260</v>
+        <v>722</v>
       </c>
       <c r="L46" s="2">
-        <v>46161.07038194445</v>
+        <v>46179.17799768518</v>
       </c>
       <c r="M46" t="s">
-        <v>247</v>
-      </c>
-      <c r="N46" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N46" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -3177,22 +3144,22 @@
         <v>59</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C47" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D47" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E47" t="s">
         <v>234</v>
       </c>
       <c r="F47" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G47" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H47">
         <v>5</v>
@@ -3201,19 +3168,19 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>260</v>
+        <v>3380</v>
       </c>
       <c r="L47" s="2">
-        <v>46161.07040509259</v>
+        <v>46179.178125</v>
       </c>
       <c r="M47" t="s">
-        <v>247</v>
-      </c>
-      <c r="N47" t="s">
-        <v>208</v>
+        <v>249</v>
+      </c>
+      <c r="N47" s="2">
+        <v>46160</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -3221,22 +3188,22 @@
         <v>60</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D48" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E48" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F48" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G48" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H48">
         <v>5</v>
@@ -3245,19 +3212,19 @@
         <v>1</v>
       </c>
       <c r="J48">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K48">
-        <v>247</v>
+        <v>1481</v>
       </c>
       <c r="L48" s="2">
-        <v>46161.07041666667</v>
+        <v>46179.1781712963</v>
       </c>
       <c r="M48" t="s">
-        <v>247</v>
-      </c>
-      <c r="N48" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="N48" s="2">
+        <v>46163</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -3265,22 +3232,22 @@
         <v>61</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D49" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="E49" t="s">
         <v>234</v>
       </c>
       <c r="F49" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G49" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H49">
         <v>5</v>
@@ -3289,19 +3256,19 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K49">
-        <v>369</v>
+        <v>967</v>
       </c>
       <c r="L49" s="2">
-        <v>46161.07043981482</v>
+        <v>46179.17833333334</v>
       </c>
       <c r="M49" t="s">
-        <v>247</v>
-      </c>
-      <c r="N49" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N49" s="2">
+        <v>46160</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -3309,22 +3276,22 @@
         <v>62</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C50" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E50" t="s">
         <v>234</v>
       </c>
       <c r="F50" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G50" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H50">
         <v>5</v>
@@ -3333,19 +3300,19 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K50">
-        <v>160</v>
+        <v>735</v>
       </c>
       <c r="L50" s="2">
-        <v>46161.07046296296</v>
+        <v>46179.17834490741</v>
       </c>
       <c r="M50" t="s">
-        <v>247</v>
-      </c>
-      <c r="N50" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N50" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -3353,22 +3320,22 @@
         <v>63</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C51" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D51" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="E51" t="s">
         <v>234</v>
       </c>
       <c r="F51" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G51" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H51">
         <v>5</v>
@@ -3377,19 +3344,19 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K51">
-        <v>130</v>
+        <v>976</v>
       </c>
       <c r="L51" s="2">
-        <v>46161.07048611111</v>
+        <v>46179.17849537037</v>
       </c>
       <c r="M51" t="s">
-        <v>247</v>
-      </c>
-      <c r="N51" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N51" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -3397,22 +3364,22 @@
         <v>64</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C52" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D52" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E52" t="s">
         <v>234</v>
       </c>
       <c r="F52" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G52" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H52">
         <v>5</v>
@@ -3421,19 +3388,19 @@
         <v>1</v>
       </c>
       <c r="J52">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K52">
-        <v>220</v>
+        <v>976</v>
       </c>
       <c r="L52" s="2">
-        <v>46161.07049768518</v>
+        <v>46179.17864583333</v>
       </c>
       <c r="M52" t="s">
-        <v>247</v>
-      </c>
-      <c r="N52" t="s">
-        <v>255</v>
+        <v>248</v>
+      </c>
+      <c r="N52" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -3441,22 +3408,22 @@
         <v>65</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C53" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D53" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="E53" t="s">
         <v>234</v>
       </c>
       <c r="F53" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G53" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H53">
         <v>5</v>
@@ -3465,19 +3432,19 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K53">
-        <v>262</v>
+        <v>962</v>
       </c>
       <c r="L53" s="2">
-        <v>46161.07052083333</v>
+        <v>46179.1787962963</v>
       </c>
       <c r="M53" t="s">
-        <v>247</v>
-      </c>
-      <c r="N53" t="s">
-        <v>207</v>
+        <v>248</v>
+      </c>
+      <c r="N53" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -3485,22 +3452,22 @@
         <v>66</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C54" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D54" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E54" t="s">
         <v>234</v>
       </c>
       <c r="F54" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G54" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H54">
         <v>5</v>
@@ -3509,19 +3476,19 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K54">
-        <v>78</v>
+        <v>1019</v>
       </c>
       <c r="L54" s="2">
-        <v>46161.07054398148</v>
+        <v>46179.17880787037</v>
       </c>
       <c r="M54" t="s">
-        <v>247</v>
-      </c>
-      <c r="N54" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="N54" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -3529,22 +3496,22 @@
         <v>67</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C55" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D55" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E55" t="s">
         <v>234</v>
       </c>
       <c r="F55" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G55" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H55">
         <v>5</v>
@@ -3553,19 +3520,19 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K55">
-        <v>101</v>
+        <v>1017</v>
       </c>
       <c r="L55" s="2">
-        <v>46161.07055555555</v>
+        <v>46179.17881944445</v>
       </c>
       <c r="M55" t="s">
-        <v>247</v>
-      </c>
-      <c r="N55" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="N55" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -3573,22 +3540,22 @@
         <v>68</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C56" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D56" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E56" t="s">
         <v>234</v>
       </c>
       <c r="F56" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G56" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H56">
         <v>5</v>
@@ -3600,16 +3567,16 @@
         <v>20</v>
       </c>
       <c r="K56">
-        <v>371</v>
+        <v>1456</v>
       </c>
       <c r="L56" s="2">
-        <v>46161.07056712963</v>
+        <v>46179.17884259259</v>
       </c>
       <c r="M56" t="s">
-        <v>247</v>
-      </c>
-      <c r="N56" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N56" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -3617,22 +3584,22 @@
         <v>69</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C57" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="D57" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E57" t="s">
         <v>234</v>
       </c>
       <c r="F57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G57" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H57">
         <v>5</v>
@@ -3644,16 +3611,16 @@
         <v>20</v>
       </c>
       <c r="K57">
-        <v>532</v>
+        <v>1621</v>
       </c>
       <c r="L57" s="2">
-        <v>46161.07059027778</v>
+        <v>46179.17886574074</v>
       </c>
       <c r="M57" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N57" s="2">
-        <v>46155</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3661,22 +3628,22 @@
         <v>70</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C58" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D58" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F58" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G58" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H58">
         <v>5</v>
@@ -3688,16 +3655,16 @@
         <v>20</v>
       </c>
       <c r="K58">
-        <v>305</v>
+        <v>1662</v>
       </c>
       <c r="L58" s="2">
-        <v>46161.07060185185</v>
+        <v>46179.17888888889</v>
       </c>
       <c r="M58" t="s">
-        <v>247</v>
-      </c>
-      <c r="N58" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N58" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3705,22 +3672,22 @@
         <v>71</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C59" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D59" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E59" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G59" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -3729,19 +3696,19 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K59">
-        <v>240</v>
+        <v>1017</v>
       </c>
       <c r="L59" s="2">
-        <v>46161.07063657408</v>
+        <v>46179.17891203704</v>
       </c>
       <c r="M59" t="s">
-        <v>247</v>
-      </c>
-      <c r="N59" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N59" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3749,22 +3716,22 @@
         <v>72</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C60" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D60" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E60" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F60" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G60" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H60">
         <v>5</v>
@@ -3773,19 +3740,19 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K60">
-        <v>260</v>
+        <v>655</v>
       </c>
       <c r="L60" s="2">
-        <v>46161.07064814815</v>
+        <v>46179.17892361111</v>
       </c>
       <c r="M60" t="s">
-        <v>247</v>
-      </c>
-      <c r="N60" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N60" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3793,22 +3760,22 @@
         <v>73</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C61" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D61" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E61" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F61" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G61" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H61">
         <v>5</v>
@@ -3817,19 +3784,19 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K61">
-        <v>29</v>
+        <v>1521</v>
       </c>
       <c r="L61" s="2">
-        <v>46161.07065972222</v>
+        <v>46179.17894675926</v>
       </c>
       <c r="M61" t="s">
         <v>248</v>
       </c>
       <c r="N61" s="2">
-        <v>46153</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3837,22 +3804,22 @@
         <v>74</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C62" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D62" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E62" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F62" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G62" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H62">
         <v>5</v>
@@ -3861,19 +3828,19 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K62">
-        <v>53</v>
+        <v>1521</v>
       </c>
       <c r="L62" s="2">
-        <v>46161.07068287037</v>
+        <v>46179.17896990741</v>
       </c>
       <c r="M62" t="s">
         <v>248</v>
       </c>
-      <c r="N62" t="s">
-        <v>208</v>
+      <c r="N62" s="2">
+        <v>46157</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3881,22 +3848,22 @@
         <v>75</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C63" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D63" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E63" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F63" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G63" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -3905,19 +3872,19 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K63">
-        <v>278</v>
+        <v>1521</v>
       </c>
       <c r="L63" s="2">
-        <v>46161.07069444445</v>
+        <v>46179.17898148148</v>
       </c>
       <c r="M63" t="s">
-        <v>247</v>
-      </c>
-      <c r="N63" t="s">
-        <v>213</v>
+        <v>248</v>
+      </c>
+      <c r="N63" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3925,22 +3892,22 @@
         <v>76</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D64" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E64" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F64" t="s">
         <v>243</v>
       </c>
       <c r="G64" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H64">
         <v>5</v>
@@ -3949,19 +3916,19 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K64">
-        <v>9</v>
+        <v>1016</v>
       </c>
       <c r="L64" s="2">
-        <v>46161.07099537037</v>
+        <v>46179.17900462963</v>
       </c>
       <c r="M64" t="s">
         <v>248</v>
       </c>
-      <c r="N64" t="s">
-        <v>256</v>
+      <c r="N64" s="2">
+        <v>46171</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -3969,22 +3936,22 @@
         <v>77</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C65" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D65" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E65" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G65" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H65">
         <v>5</v>
@@ -3993,19 +3960,19 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K65">
-        <v>264</v>
+        <v>828</v>
       </c>
       <c r="L65" s="2">
-        <v>46161.07105324074</v>
+        <v>46179.17902777778</v>
       </c>
       <c r="M65" t="s">
-        <v>247</v>
-      </c>
-      <c r="N65" t="s">
-        <v>253</v>
+        <v>248</v>
+      </c>
+      <c r="N65" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -4013,22 +3980,22 @@
         <v>78</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C66" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D66" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E66" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F66" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G66" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H66">
         <v>5</v>
@@ -4040,16 +4007,16 @@
         <v>10</v>
       </c>
       <c r="K66">
-        <v>204</v>
+        <v>621</v>
       </c>
       <c r="L66" s="2">
-        <v>46161.07106481482</v>
+        <v>46179.17905092592</v>
       </c>
       <c r="M66" t="s">
-        <v>247</v>
-      </c>
-      <c r="N66" t="s">
-        <v>213</v>
+        <v>248</v>
+      </c>
+      <c r="N66" s="2">
+        <v>46163</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -4057,22 +4024,22 @@
         <v>79</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C67" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D67" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E67" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F67" t="s">
         <v>243</v>
       </c>
       <c r="G67" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H67">
         <v>5</v>
@@ -4081,19 +4048,19 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K67">
-        <v>9</v>
+        <v>580</v>
       </c>
       <c r="L67" s="2">
-        <v>46161.07107638889</v>
+        <v>46179.17907407408</v>
       </c>
       <c r="M67" t="s">
         <v>248</v>
       </c>
-      <c r="N67" t="s">
-        <v>257</v>
+      <c r="N67" s="2">
+        <v>46161</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -4101,22 +4068,22 @@
         <v>80</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C68" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D68" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E68" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G68" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H68">
         <v>5</v>
@@ -4125,19 +4092,19 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K68">
-        <v>9</v>
+        <v>1632</v>
       </c>
       <c r="L68" s="2">
-        <v>46161.07108796296</v>
+        <v>46179.17909722222</v>
       </c>
       <c r="M68" t="s">
         <v>248</v>
       </c>
       <c r="N68" s="2">
-        <v>46155</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -4145,22 +4112,22 @@
         <v>81</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C69" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D69" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E69" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F69" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G69" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H69">
         <v>5</v>
@@ -4169,19 +4136,19 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K69">
-        <v>399</v>
+        <v>1537</v>
       </c>
       <c r="L69" s="2">
-        <v>46161.07114583333</v>
+        <v>46179.17912037037</v>
       </c>
       <c r="M69" t="s">
-        <v>247</v>
-      </c>
-      <c r="N69" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N69" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -4189,22 +4156,22 @@
         <v>82</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C70" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D70" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E70" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F70" t="s">
         <v>243</v>
       </c>
       <c r="G70" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H70">
         <v>5</v>
@@ -4213,19 +4180,19 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K70">
-        <v>202</v>
+        <v>296</v>
       </c>
       <c r="L70" s="2">
-        <v>46161.07123842592</v>
+        <v>46179.17914351852</v>
       </c>
       <c r="M70" t="s">
-        <v>247</v>
-      </c>
-      <c r="N70" t="s">
-        <v>208</v>
+        <v>249</v>
+      </c>
+      <c r="N70" s="2">
+        <v>46161</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -4233,22 +4200,22 @@
         <v>83</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C71" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D71" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E71" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F71" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G71" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H71">
         <v>5</v>
@@ -4257,19 +4224,19 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K71">
-        <v>202</v>
+        <v>100</v>
       </c>
       <c r="L71" s="2">
-        <v>46161.07130787037</v>
+        <v>46179.17915509259</v>
       </c>
       <c r="M71" t="s">
-        <v>247</v>
-      </c>
-      <c r="N71" t="s">
-        <v>208</v>
+        <v>249</v>
+      </c>
+      <c r="N71" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -4277,22 +4244,22 @@
         <v>84</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C72" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D72" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E72" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F72" t="s">
         <v>243</v>
       </c>
       <c r="G72" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H72">
         <v>5</v>
@@ -4301,19 +4268,19 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K72">
-        <v>260</v>
+        <v>1539</v>
       </c>
       <c r="L72" s="2">
-        <v>46161.07133101852</v>
+        <v>46179.17917824074</v>
       </c>
       <c r="M72" t="s">
-        <v>247</v>
-      </c>
-      <c r="N72" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N72" s="2">
+        <v>46113</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -4321,22 +4288,22 @@
         <v>85</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C73" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D73" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E73" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F73" t="s">
         <v>243</v>
       </c>
       <c r="G73" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H73">
         <v>5</v>
@@ -4345,19 +4312,19 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K73">
-        <v>9</v>
+        <v>930</v>
       </c>
       <c r="L73" s="2">
-        <v>46161.07137731482</v>
+        <v>46179.17918981481</v>
       </c>
       <c r="M73" t="s">
         <v>248</v>
       </c>
-      <c r="N73" t="s">
-        <v>258</v>
+      <c r="N73" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -4365,22 +4332,22 @@
         <v>86</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D74" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E74" t="s">
         <v>241</v>
       </c>
       <c r="F74" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G74" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H74">
         <v>5</v>
@@ -4389,19 +4356,19 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K74">
-        <v>260</v>
+        <v>56</v>
       </c>
       <c r="L74" s="2">
-        <v>46161.07141203704</v>
+        <v>46179.17922453704</v>
       </c>
       <c r="M74" t="s">
-        <v>247</v>
-      </c>
-      <c r="N74" t="s">
-        <v>208</v>
+        <v>249</v>
+      </c>
+      <c r="N74" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -4409,22 +4376,22 @@
         <v>87</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C75" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D75" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E75" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F75" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G75" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H75">
         <v>5</v>
@@ -4433,19 +4400,19 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K75">
-        <v>260</v>
+        <v>1521</v>
       </c>
       <c r="L75" s="2">
-        <v>46161.07142361111</v>
+        <v>46179.17925925926</v>
       </c>
       <c r="M75" t="s">
-        <v>247</v>
-      </c>
-      <c r="N75" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N75" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -4453,22 +4420,22 @@
         <v>88</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C76" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D76" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E76" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F76" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H76">
         <v>5</v>
@@ -4477,19 +4444,19 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K76">
-        <v>295</v>
+        <v>1521</v>
       </c>
       <c r="L76" s="2">
-        <v>46161.07144675926</v>
+        <v>46179.17928240741</v>
       </c>
       <c r="M76" t="s">
-        <v>247</v>
-      </c>
-      <c r="N76" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N76" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -4497,22 +4464,22 @@
         <v>89</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C77" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D77" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E77" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F77" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G77" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H77">
         <v>5</v>
@@ -4521,19 +4488,19 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K77">
-        <v>260</v>
+        <v>1521</v>
       </c>
       <c r="L77" s="2">
-        <v>46161.07145833333</v>
+        <v>46179.17930555555</v>
       </c>
       <c r="M77" t="s">
-        <v>247</v>
-      </c>
-      <c r="N77" t="s">
-        <v>208</v>
+        <v>248</v>
+      </c>
+      <c r="N77" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -4541,22 +4508,22 @@
         <v>90</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C78" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D78" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E78" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F78" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G78" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H78">
         <v>5</v>
@@ -4565,19 +4532,19 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K78">
-        <v>9</v>
+        <v>1521</v>
       </c>
       <c r="L78" s="2">
-        <v>46161.07149305556</v>
+        <v>46179.17931712963</v>
       </c>
       <c r="M78" t="s">
         <v>248</v>
       </c>
-      <c r="N78" t="s">
-        <v>259</v>
+      <c r="N78" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -4585,13 +4552,13 @@
         <v>91</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C79" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D79" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E79" t="s">
         <v>242</v>
@@ -4600,7 +4567,7 @@
         <v>243</v>
       </c>
       <c r="G79" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H79">
         <v>5</v>
@@ -4609,19 +4576,19 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K79">
-        <v>9</v>
+        <v>1556</v>
       </c>
       <c r="L79" s="2">
-        <v>46161.0715162037</v>
+        <v>46179.17934027778</v>
       </c>
       <c r="M79" t="s">
         <v>248</v>
       </c>
-      <c r="N79" t="s">
-        <v>259</v>
+      <c r="N79" s="2">
+        <v>46165</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -4629,13 +4596,13 @@
         <v>92</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C80" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D80" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E80" t="s">
         <v>242</v>
@@ -4644,7 +4611,7 @@
         <v>243</v>
       </c>
       <c r="G80" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H80">
         <v>5</v>
@@ -4653,19 +4620,19 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K80">
-        <v>9</v>
+        <v>1521</v>
       </c>
       <c r="L80" s="2">
-        <v>46161.07153935185</v>
+        <v>46179.17935185185</v>
       </c>
       <c r="M80" t="s">
         <v>248</v>
       </c>
-      <c r="N80" t="s">
-        <v>260</v>
+      <c r="N80" s="2">
+        <v>46166</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -4673,22 +4640,22 @@
         <v>93</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C81" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D81" t="s">
         <v>220</v>
       </c>
       <c r="E81" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="F81" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G81" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H81">
         <v>5</v>
@@ -4697,19 +4664,19 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K81">
-        <v>635</v>
+        <v>1521</v>
       </c>
       <c r="L81" s="2">
-        <v>46161.07157407407</v>
+        <v>46179.179375</v>
       </c>
       <c r="M81" t="s">
-        <v>247</v>
-      </c>
-      <c r="N81" t="s">
-        <v>203</v>
+        <v>248</v>
+      </c>
+      <c r="N81" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -4717,22 +4684,22 @@
         <v>94</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C82" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D82" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E82" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="F82" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G82" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H82">
         <v>5</v>
@@ -4741,19 +4708,19 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K82">
-        <v>287</v>
+        <v>1521</v>
       </c>
       <c r="L82" s="2">
-        <v>46161.07159722222</v>
+        <v>46179.17939814815</v>
       </c>
       <c r="M82" t="s">
-        <v>247</v>
-      </c>
-      <c r="N82" t="s">
-        <v>213</v>
+        <v>248</v>
+      </c>
+      <c r="N82" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -4761,22 +4728,22 @@
         <v>95</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C83" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D83" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E83" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F83" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G83" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H83">
         <v>5</v>
@@ -4788,16 +4755,16 @@
         <v>1</v>
       </c>
       <c r="K83">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="L83" s="2">
-        <v>46161.07162037037</v>
+        <v>46179.1794212963</v>
       </c>
       <c r="M83" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N83" s="2">
-        <v>46154</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -4805,22 +4772,22 @@
         <v>96</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C84" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D84" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E84" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F84" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G84" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H84">
         <v>5</v>
@@ -4832,16 +4799,16 @@
         <v>1</v>
       </c>
       <c r="K84">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="L84" s="2">
-        <v>46161.07163194445</v>
+        <v>46179.17945601852</v>
       </c>
       <c r="M84" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N84" s="2">
-        <v>46154</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -4849,22 +4816,22 @@
         <v>97</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C85" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D85" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="E85" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F85" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G85" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H85">
         <v>5</v>
@@ -4873,19 +4840,19 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K85">
-        <v>220</v>
+        <v>56</v>
       </c>
       <c r="L85" s="2">
-        <v>46161.07164351852</v>
+        <v>46179.17947916667</v>
       </c>
       <c r="M85" t="s">
-        <v>247</v>
-      </c>
-      <c r="N85" t="s">
         <v>249</v>
+      </c>
+      <c r="N85" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -4893,22 +4860,22 @@
         <v>98</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C86" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D86" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="E86" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F86" t="s">
         <v>243</v>
       </c>
       <c r="G86" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H86">
         <v>5</v>
@@ -4917,16 +4884,19 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="K86">
-        <v>175</v>
+        <v>1536</v>
       </c>
       <c r="L86" s="2">
-        <v>46161.07166666666</v>
+        <v>46179.17950231482</v>
       </c>
       <c r="M86" t="s">
         <v>248</v>
+      </c>
+      <c r="N86" s="2">
+        <v>46168</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -4934,22 +4904,22 @@
         <v>99</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C87" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D87" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="E87" t="s">
         <v>233</v>
       </c>
       <c r="F87" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G87" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H87">
         <v>5</v>
@@ -4961,13 +4931,16 @@
         <v>1</v>
       </c>
       <c r="K87">
-        <v>192</v>
+        <v>56</v>
       </c>
       <c r="L87" s="2">
-        <v>46161.07167824074</v>
+        <v>46179.17952546296</v>
       </c>
       <c r="M87" t="s">
-        <v>248</v>
+        <v>249</v>
+      </c>
+      <c r="N87" s="2">
+        <v>46154</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -4975,13 +4948,13 @@
         <v>100</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C88" t="s">
         <v>202</v>
       </c>
       <c r="D88" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E88" t="s">
         <v>233</v>
@@ -4994,21 +4967,6 @@
       </c>
       <c r="H88">
         <v>5</v>
-      </c>
-      <c r="I88">
-        <v>1</v>
-      </c>
-      <c r="J88">
-        <v>20</v>
-      </c>
-      <c r="K88">
-        <v>220</v>
-      </c>
-      <c r="L88" s="2">
-        <v>46161.07171296296</v>
-      </c>
-      <c r="M88" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -5016,25 +4974,28 @@
         <v>101</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C89" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D89" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E89" t="s">
         <v>233</v>
       </c>
       <c r="F89" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G89" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H89">
         <v>5</v>
+      </c>
+      <c r="N89" s="2">
+        <v>46154</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -5042,25 +5003,43 @@
         <v>102</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C90" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D90" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E90" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F90" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G90" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H90">
         <v>5</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>10</v>
+      </c>
+      <c r="K90">
+        <v>930</v>
+      </c>
+      <c r="L90" s="2">
+        <v>46179.17953703704</v>
+      </c>
+      <c r="M90" t="s">
+        <v>248</v>
+      </c>
+      <c r="N90" s="2">
+        <v>46164</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -5068,22 +5047,22 @@
         <v>103</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C91" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D91" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E91" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F91" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G91" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H91">
         <v>5</v>
@@ -5092,16 +5071,19 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K91">
-        <v>260</v>
+        <v>783</v>
       </c>
       <c r="L91" s="2">
-        <v>46161.07173611111</v>
+        <v>46179.17965277778</v>
       </c>
       <c r="M91" t="s">
-        <v>247</v>
+        <v>248</v>
+      </c>
+      <c r="N91" s="2">
+        <v>46163</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -5109,22 +5091,22 @@
         <v>104</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D92" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E92" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F92" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G92" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -5133,98 +5115,19 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K92">
-        <v>260</v>
+        <v>792</v>
       </c>
       <c r="L92" s="2">
-        <v>46161.07174768519</v>
+        <v>46179.17976851852</v>
       </c>
       <c r="M92" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14">
-      <c r="A93" t="s">
-        <v>105</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C93" t="s">
-        <v>208</v>
-      </c>
-      <c r="D93" t="s">
-        <v>222</v>
-      </c>
-      <c r="E93" t="s">
-        <v>241</v>
-      </c>
-      <c r="F93" t="s">
-        <v>243</v>
-      </c>
-      <c r="G93" t="s">
-        <v>244</v>
-      </c>
-      <c r="H93">
-        <v>5</v>
-      </c>
-      <c r="I93">
-        <v>1</v>
-      </c>
-      <c r="J93">
-        <v>20</v>
-      </c>
-      <c r="K93">
-        <v>260</v>
-      </c>
-      <c r="L93" s="2">
-        <v>46161.07177083333</v>
-      </c>
-      <c r="M93" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14">
-      <c r="A94" t="s">
-        <v>106</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C94" t="s">
-        <v>208</v>
-      </c>
-      <c r="D94" t="s">
-        <v>222</v>
-      </c>
-      <c r="E94" t="s">
-        <v>241</v>
-      </c>
-      <c r="F94" t="s">
-        <v>243</v>
-      </c>
-      <c r="G94" t="s">
-        <v>244</v>
-      </c>
-      <c r="H94">
-        <v>5</v>
-      </c>
-      <c r="I94">
-        <v>1</v>
-      </c>
-      <c r="J94">
-        <v>20</v>
-      </c>
-      <c r="K94">
-        <v>260</v>
-      </c>
-      <c r="L94" s="2">
-        <v>46161.07179398148</v>
-      </c>
-      <c r="M94" t="s">
-        <v>247</v>
+        <v>248</v>
+      </c>
+      <c r="N92" s="2">
+        <v>46164</v>
       </c>
     </row>
   </sheetData>
@@ -5320,8 +5223,6 @@
     <hyperlink ref="B90" r:id="rId89"/>
     <hyperlink ref="B91" r:id="rId90"/>
     <hyperlink ref="B92" r:id="rId91"/>
-    <hyperlink ref="B93" r:id="rId92"/>
-    <hyperlink ref="B94" r:id="rId93"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="265">
   <si>
     <t>site_name</t>
   </si>
@@ -229,16 +229,16 @@
     <t>22.입법지원센터(정부입법현황)</t>
   </si>
   <si>
-    <t>10.관세법령(행정예고)</t>
-  </si>
-  <si>
-    <t>11.관세법령(최신법령)</t>
-  </si>
-  <si>
-    <t>2.유니패스(행정규칙</t>
-  </si>
-  <si>
-    <t>3.유니패스(판례)</t>
+    <t>4-1.유니패스(행정예고)</t>
+  </si>
+  <si>
+    <t>10.유니패스(최신법령)</t>
+  </si>
+  <si>
+    <t>11.유니패스(행정규칙</t>
+  </si>
+  <si>
+    <t>12.유니패스(판례)</t>
   </si>
   <si>
     <t>4.유니패스(공지사항)</t>
@@ -797,9 +797,6 @@
   </si>
   <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>FAIL</t>
   </si>
   <si>
     <t>N</t>
@@ -1272,7 +1269,7 @@
         <v>1795</v>
       </c>
       <c r="L2" s="2">
-        <v>46185.23859953704</v>
+        <v>46230.21296296296</v>
       </c>
       <c r="M2" t="s">
         <v>258</v>
@@ -1281,13 +1278,13 @@
         <v>253</v>
       </c>
       <c r="O2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W2" s="2">
         <v>46155</v>
@@ -1331,7 +1328,7 @@
         <v>1752</v>
       </c>
       <c r="L3" s="2">
-        <v>46185.23859953704</v>
+        <v>46230.21296296296</v>
       </c>
       <c r="M3" t="s">
         <v>258</v>
@@ -1340,13 +1337,13 @@
         <v>253</v>
       </c>
       <c r="O3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W3" s="2">
         <v>46087</v>
@@ -1390,7 +1387,7 @@
         <v>1533</v>
       </c>
       <c r="L4" s="2">
-        <v>46185.23859953704</v>
+        <v>46230.21296296296</v>
       </c>
       <c r="M4" t="s">
         <v>258</v>
@@ -1399,13 +1396,13 @@
         <v>253</v>
       </c>
       <c r="O4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W4" s="2">
         <v>46168</v>
@@ -1449,7 +1446,7 @@
         <v>324</v>
       </c>
       <c r="L5" s="2">
-        <v>46185.23859953704</v>
+        <v>46230.21296296296</v>
       </c>
       <c r="M5" t="s">
         <v>258</v>
@@ -1458,13 +1455,13 @@
         <v>253</v>
       </c>
       <c r="O5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W5" s="2">
         <v>46161</v>
@@ -1505,10 +1502,10 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="L6" s="2">
-        <v>46185.23861111111</v>
+        <v>46230.21296296296</v>
       </c>
       <c r="M6" t="s">
         <v>259</v>
@@ -1517,13 +1514,13 @@
         <v>254</v>
       </c>
       <c r="O6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W6" s="2">
         <v>46168</v>
@@ -1567,7 +1564,7 @@
         <v>65</v>
       </c>
       <c r="L7" s="2">
-        <v>46185.23861111111</v>
+        <v>46230.21297453704</v>
       </c>
       <c r="M7" t="s">
         <v>258</v>
@@ -1576,13 +1573,13 @@
         <v>253</v>
       </c>
       <c r="O7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W7" s="2">
         <v>46164</v>
@@ -1626,7 +1623,7 @@
         <v>65</v>
       </c>
       <c r="L8" s="2">
-        <v>46185.23861111111</v>
+        <v>46230.21297453704</v>
       </c>
       <c r="M8" t="s">
         <v>258</v>
@@ -1635,13 +1632,13 @@
         <v>253</v>
       </c>
       <c r="O8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W8" s="2">
         <v>46155</v>
@@ -1685,7 +1682,7 @@
         <v>1901</v>
       </c>
       <c r="L9" s="2">
-        <v>46185.23861111111</v>
+        <v>46230.21297453704</v>
       </c>
       <c r="M9" t="s">
         <v>258</v>
@@ -1694,13 +1691,13 @@
         <v>253</v>
       </c>
       <c r="O9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W9" s="2">
         <v>46045</v>
@@ -1744,7 +1741,7 @@
         <v>1704</v>
       </c>
       <c r="L10" s="2">
-        <v>46185.23861111111</v>
+        <v>46230.21297453704</v>
       </c>
       <c r="M10" t="s">
         <v>258</v>
@@ -1753,13 +1750,13 @@
         <v>253</v>
       </c>
       <c r="O10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W10" s="2">
         <v>46045</v>
@@ -1803,7 +1800,7 @@
         <v>1675</v>
       </c>
       <c r="L11" s="2">
-        <v>46185.23861111111</v>
+        <v>46230.21297453704</v>
       </c>
       <c r="M11" t="s">
         <v>258</v>
@@ -1812,13 +1809,13 @@
         <v>253</v>
       </c>
       <c r="O11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W11" s="2">
         <v>46129</v>
@@ -1862,7 +1859,7 @@
         <v>405</v>
       </c>
       <c r="L12" s="2">
-        <v>46185.23861111111</v>
+        <v>46230.21297453704</v>
       </c>
       <c r="M12" t="s">
         <v>258</v>
@@ -1871,13 +1868,13 @@
         <v>253</v>
       </c>
       <c r="O12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W12" s="2">
         <v>46164</v>
@@ -1918,10 +1915,10 @@
         <v>1</v>
       </c>
       <c r="K13">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="L13" s="2">
-        <v>46185.2386574074</v>
+        <v>46230.21299768519</v>
       </c>
       <c r="M13" t="s">
         <v>259</v>
@@ -1930,13 +1927,13 @@
         <v>254</v>
       </c>
       <c r="O13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W13" s="2">
         <v>46168</v>
@@ -1977,10 +1974,10 @@
         <v>30</v>
       </c>
       <c r="K14">
-        <v>1941</v>
+        <v>3775</v>
       </c>
       <c r="L14" s="2">
-        <v>46185.23869212963</v>
+        <v>46230.21302083333</v>
       </c>
       <c r="M14" t="s">
         <v>260</v>
@@ -1989,13 +1986,13 @@
         <v>254</v>
       </c>
       <c r="O14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W14" s="2">
         <v>46168</v>
@@ -2033,10 +2030,10 @@
         <v>30</v>
       </c>
       <c r="K15">
-        <v>1941</v>
+        <v>3775</v>
       </c>
       <c r="L15" s="2">
-        <v>46185.23871527778</v>
+        <v>46230.21304398148</v>
       </c>
       <c r="M15" t="s">
         <v>260</v>
@@ -2045,13 +2042,13 @@
         <v>254</v>
       </c>
       <c r="O15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W15" s="2">
         <v>46168</v>
@@ -2089,10 +2086,10 @@
         <v>30</v>
       </c>
       <c r="K16">
-        <v>1941</v>
+        <v>3775</v>
       </c>
       <c r="L16" s="2">
-        <v>46185.23872685185</v>
+        <v>46230.21305555556</v>
       </c>
       <c r="M16" t="s">
         <v>260</v>
@@ -2101,13 +2098,13 @@
         <v>254</v>
       </c>
       <c r="O16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W16" s="2">
         <v>46164</v>
@@ -2148,7 +2145,7 @@
         <v>1809</v>
       </c>
       <c r="L17" s="2">
-        <v>46185.23873842593</v>
+        <v>46230.21306712963</v>
       </c>
       <c r="M17" t="s">
         <v>258</v>
@@ -2157,13 +2154,13 @@
         <v>253</v>
       </c>
       <c r="O17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W17" s="2">
         <v>46113</v>
@@ -2201,10 +2198,10 @@
         <v>30</v>
       </c>
       <c r="K18">
-        <v>1941</v>
+        <v>3891</v>
       </c>
       <c r="L18" s="2">
-        <v>46185.23875</v>
+        <v>46230.21306712963</v>
       </c>
       <c r="M18" t="s">
         <v>260</v>
@@ -2213,13 +2210,13 @@
         <v>254</v>
       </c>
       <c r="O18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W18" s="2">
         <v>46168</v>
@@ -2260,7 +2257,7 @@
         <v>65</v>
       </c>
       <c r="L19" s="2">
-        <v>46185.23875</v>
+        <v>46230.2130787037</v>
       </c>
       <c r="M19" t="s">
         <v>258</v>
@@ -2269,13 +2266,13 @@
         <v>253</v>
       </c>
       <c r="O19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W19" s="2">
         <v>46163</v>
@@ -2316,7 +2313,7 @@
         <v>1826</v>
       </c>
       <c r="L20" s="2">
-        <v>46185.23875</v>
+        <v>46230.2130787037</v>
       </c>
       <c r="M20" t="s">
         <v>258</v>
@@ -2325,13 +2322,13 @@
         <v>253</v>
       </c>
       <c r="O20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W20" s="2">
         <v>46165</v>
@@ -2372,7 +2369,7 @@
         <v>1791</v>
       </c>
       <c r="L21" s="2">
-        <v>46185.23875</v>
+        <v>46230.2130787037</v>
       </c>
       <c r="M21" t="s">
         <v>258</v>
@@ -2381,13 +2378,13 @@
         <v>253</v>
       </c>
       <c r="O21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W21" s="2">
         <v>46166</v>
@@ -2425,10 +2422,10 @@
         <v>30</v>
       </c>
       <c r="K22">
-        <v>1941</v>
+        <v>3891</v>
       </c>
       <c r="L22" s="2">
-        <v>46185.23877314815</v>
+        <v>46230.21309027778</v>
       </c>
       <c r="M22" t="s">
         <v>260</v>
@@ -2437,13 +2434,13 @@
         <v>254</v>
       </c>
       <c r="O22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W22" s="2">
         <v>46168</v>
@@ -2481,10 +2478,10 @@
         <v>30</v>
       </c>
       <c r="K23">
-        <v>1941</v>
+        <v>3891</v>
       </c>
       <c r="L23" s="2">
-        <v>46185.23878472222</v>
+        <v>46230.21310185185</v>
       </c>
       <c r="M23" t="s">
         <v>260</v>
@@ -2493,13 +2490,13 @@
         <v>254</v>
       </c>
       <c r="O23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W23" s="2">
         <v>46168</v>
@@ -2537,10 +2534,10 @@
         <v>1</v>
       </c>
       <c r="K24">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="L24" s="2">
-        <v>46185.23881944444</v>
+        <v>46230.213125</v>
       </c>
       <c r="M24" t="s">
         <v>259</v>
@@ -2549,13 +2546,13 @@
         <v>254</v>
       </c>
       <c r="O24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W24" s="2">
         <v>46168</v>
@@ -2593,10 +2590,10 @@
         <v>1</v>
       </c>
       <c r="K25">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="L25" s="2">
-        <v>46185.23884259259</v>
+        <v>46230.21314814815</v>
       </c>
       <c r="M25" t="s">
         <v>259</v>
@@ -2605,13 +2602,13 @@
         <v>254</v>
       </c>
       <c r="O25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W25" s="2">
         <v>46167</v>
@@ -2649,10 +2646,10 @@
         <v>1</v>
       </c>
       <c r="K26">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="L26" s="2">
-        <v>46185.23886574074</v>
+        <v>46230.21317129629</v>
       </c>
       <c r="M26" t="s">
         <v>259</v>
@@ -2661,13 +2658,13 @@
         <v>254</v>
       </c>
       <c r="O26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W26" s="2">
         <v>46168</v>
@@ -2708,7 +2705,7 @@
         <v>2166</v>
       </c>
       <c r="L27" s="2">
-        <v>46185.23886574074</v>
+        <v>46230.21317129629</v>
       </c>
       <c r="M27" t="s">
         <v>258</v>
@@ -2717,13 +2714,13 @@
         <v>253</v>
       </c>
       <c r="O27" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P27" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q27" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W27" s="2">
         <v>46172</v>
@@ -2764,7 +2761,7 @@
         <v>2204</v>
       </c>
       <c r="L28" s="2">
-        <v>46185.23886574074</v>
+        <v>46230.21317129629</v>
       </c>
       <c r="M28" t="s">
         <v>258</v>
@@ -2773,13 +2770,13 @@
         <v>253</v>
       </c>
       <c r="O28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W28" s="2">
         <v>46164</v>
@@ -2820,7 +2817,7 @@
         <v>1797</v>
       </c>
       <c r="L29" s="2">
-        <v>46185.23886574074</v>
+        <v>46230.21317129629</v>
       </c>
       <c r="M29" t="s">
         <v>258</v>
@@ -2829,13 +2826,13 @@
         <v>253</v>
       </c>
       <c r="O29" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P29" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q29" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W29" s="2">
         <v>46168</v>
@@ -2876,7 +2873,7 @@
         <v>1321</v>
       </c>
       <c r="L30" s="2">
-        <v>46185.23886574074</v>
+        <v>46230.21317129629</v>
       </c>
       <c r="M30" t="s">
         <v>258</v>
@@ -2885,13 +2882,13 @@
         <v>253</v>
       </c>
       <c r="O30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W30" s="2">
         <v>46168</v>
@@ -2932,7 +2929,7 @@
         <v>1205</v>
       </c>
       <c r="L31" s="2">
-        <v>46185.23886574074</v>
+        <v>46230.21317129629</v>
       </c>
       <c r="M31" t="s">
         <v>258</v>
@@ -2941,13 +2938,13 @@
         <v>253</v>
       </c>
       <c r="O31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P31" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W31" s="2">
         <v>46168</v>
@@ -2982,28 +2979,28 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="K32">
-        <v>3380</v>
+        <v>6062</v>
       </c>
       <c r="L32" s="2">
-        <v>46185.2390162037</v>
+        <v>46230.21334490741</v>
       </c>
       <c r="M32" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N32" t="s">
         <v>254</v>
       </c>
       <c r="O32" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q32" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W32" s="2">
         <v>46160</v>
@@ -3044,7 +3041,7 @@
         <v>520</v>
       </c>
       <c r="L33" s="2">
-        <v>46185.2390162037</v>
+        <v>46230.21334490741</v>
       </c>
       <c r="M33" t="s">
         <v>258</v>
@@ -3053,13 +3050,13 @@
         <v>253</v>
       </c>
       <c r="O33" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P33" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q33" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W33" s="2">
         <v>46168</v>
@@ -3100,7 +3097,7 @@
         <v>541</v>
       </c>
       <c r="L34" s="2">
-        <v>46185.2390162037</v>
+        <v>46230.21334490741</v>
       </c>
       <c r="M34" t="s">
         <v>258</v>
@@ -3109,13 +3106,13 @@
         <v>253</v>
       </c>
       <c r="O34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P34" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W34" s="2">
         <v>46168</v>
@@ -3153,10 +3150,10 @@
         <v>30</v>
       </c>
       <c r="K35">
-        <v>1941</v>
+        <v>3891</v>
       </c>
       <c r="L35" s="2">
-        <v>46185.23903935185</v>
+        <v>46230.21335648148</v>
       </c>
       <c r="M35" t="s">
         <v>260</v>
@@ -3165,13 +3162,13 @@
         <v>254</v>
       </c>
       <c r="O35" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q35" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W35" s="2">
         <v>46157</v>
@@ -3209,10 +3206,10 @@
         <v>30</v>
       </c>
       <c r="K36">
-        <v>1941</v>
+        <v>3891</v>
       </c>
       <c r="L36" s="2">
-        <v>46185.23905092593</v>
+        <v>46230.21336805556</v>
       </c>
       <c r="M36" t="s">
         <v>260</v>
@@ -3221,13 +3218,13 @@
         <v>254</v>
       </c>
       <c r="O36" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P36" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q36" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W36" s="2">
         <v>46168</v>
@@ -3262,28 +3259,28 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K37">
-        <v>176</v>
+        <v>2126</v>
       </c>
       <c r="L37" s="2">
-        <v>46185.2390625</v>
+        <v>46230.21337962963</v>
       </c>
       <c r="M37" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N37" t="s">
         <v>254</v>
       </c>
       <c r="O37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P37" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W37" s="2">
         <v>46132</v>
@@ -3318,28 +3315,28 @@
         <v>1</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K38">
-        <v>1287</v>
+        <v>3237</v>
       </c>
       <c r="L38" s="2">
-        <v>46185.23907407407</v>
+        <v>46230.2133912037</v>
       </c>
       <c r="M38" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N38" t="s">
         <v>254</v>
       </c>
       <c r="O38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P38" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W38" s="2">
         <v>46113</v>
@@ -3377,10 +3374,10 @@
         <v>30</v>
       </c>
       <c r="K39">
-        <v>1526</v>
+        <v>3476</v>
       </c>
       <c r="L39" s="2">
-        <v>46185.23909722222</v>
+        <v>46230.21340277778</v>
       </c>
       <c r="M39" t="s">
         <v>260</v>
@@ -3389,13 +3386,13 @@
         <v>254</v>
       </c>
       <c r="O39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P39" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W39" s="2">
         <v>46140</v>
@@ -3433,10 +3430,10 @@
         <v>30</v>
       </c>
       <c r="K40">
-        <v>1478</v>
+        <v>3428</v>
       </c>
       <c r="L40" s="2">
-        <v>46185.2391087963</v>
+        <v>46230.21341435185</v>
       </c>
       <c r="M40" t="s">
         <v>260</v>
@@ -3445,13 +3442,13 @@
         <v>254</v>
       </c>
       <c r="O40" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P40" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q40" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W40" s="2">
         <v>46024</v>
@@ -3489,10 +3486,10 @@
         <v>30</v>
       </c>
       <c r="K41">
-        <v>1892</v>
+        <v>3842</v>
       </c>
       <c r="L41" s="2">
-        <v>46185.23912037037</v>
+        <v>46230.21342592593</v>
       </c>
       <c r="M41" t="s">
         <v>260</v>
@@ -3501,13 +3498,13 @@
         <v>254</v>
       </c>
       <c r="O41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P41" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W41" s="2">
         <v>46168</v>
@@ -3545,10 +3542,10 @@
         <v>30</v>
       </c>
       <c r="K42">
-        <v>1883</v>
+        <v>3833</v>
       </c>
       <c r="L42" s="2">
-        <v>46185.23913194444</v>
+        <v>46230.2134375</v>
       </c>
       <c r="M42" t="s">
         <v>260</v>
@@ -3557,13 +3554,13 @@
         <v>254</v>
       </c>
       <c r="O42" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P42" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q42" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W42" s="2">
         <v>46164</v>
@@ -3601,10 +3598,10 @@
         <v>30</v>
       </c>
       <c r="K43">
-        <v>1863</v>
+        <v>3813</v>
       </c>
       <c r="L43" s="2">
-        <v>46185.23915509259</v>
+        <v>46230.21344907407</v>
       </c>
       <c r="M43" t="s">
         <v>260</v>
@@ -3613,13 +3610,13 @@
         <v>254</v>
       </c>
       <c r="O43" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P43" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q43" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W43" s="2">
         <v>46112</v>
@@ -3660,7 +3657,7 @@
         <v>1124</v>
       </c>
       <c r="L44" s="2">
-        <v>46185.23915509259</v>
+        <v>46230.21346064815</v>
       </c>
       <c r="M44" t="s">
         <v>258</v>
@@ -3669,13 +3666,13 @@
         <v>253</v>
       </c>
       <c r="O44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W44" s="2">
         <v>46171</v>
@@ -3713,10 +3710,10 @@
         <v>20</v>
       </c>
       <c r="K45">
-        <v>1756</v>
+        <v>3020</v>
       </c>
       <c r="L45" s="2">
-        <v>46185.23916666667</v>
+        <v>46230.21346064815</v>
       </c>
       <c r="M45" t="s">
         <v>260</v>
@@ -3725,13 +3722,13 @@
         <v>254</v>
       </c>
       <c r="O45" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P45" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q45" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W45" s="2">
         <v>46168</v>
@@ -3769,10 +3766,10 @@
         <v>20</v>
       </c>
       <c r="K46">
-        <v>1901</v>
+        <v>3196</v>
       </c>
       <c r="L46" s="2">
-        <v>46185.23920138889</v>
+        <v>46230.21348379629</v>
       </c>
       <c r="M46" t="s">
         <v>260</v>
@@ -3781,13 +3778,13 @@
         <v>254</v>
       </c>
       <c r="O46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W46" s="2">
         <v>46168</v>
@@ -3825,10 +3822,10 @@
         <v>20</v>
       </c>
       <c r="K47">
-        <v>1952</v>
+        <v>3252</v>
       </c>
       <c r="L47" s="2">
-        <v>46185.23922453704</v>
+        <v>46230.21350694444</v>
       </c>
       <c r="M47" t="s">
         <v>260</v>
@@ -3837,13 +3834,13 @@
         <v>254</v>
       </c>
       <c r="O47" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q47" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W47" s="2">
         <v>46168</v>
@@ -3878,13 +3875,13 @@
         <v>1</v>
       </c>
       <c r="J48">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K48">
-        <v>1279</v>
+        <v>2489</v>
       </c>
       <c r="L48" s="2">
-        <v>46185.23925925926</v>
+        <v>46230.21353009259</v>
       </c>
       <c r="M48" t="s">
         <v>260</v>
@@ -3893,13 +3890,13 @@
         <v>254</v>
       </c>
       <c r="O48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P48" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W48" s="2">
         <v>46168</v>
@@ -3937,10 +3934,10 @@
         <v>10</v>
       </c>
       <c r="K49">
-        <v>923</v>
+        <v>1573</v>
       </c>
       <c r="L49" s="2">
-        <v>46185.23936342593</v>
+        <v>46230.21364583333</v>
       </c>
       <c r="M49" t="s">
         <v>260</v>
@@ -3949,13 +3946,13 @@
         <v>254</v>
       </c>
       <c r="O49" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P49" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q49" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W49" s="2">
         <v>46163</v>
@@ -3993,10 +3990,10 @@
         <v>10</v>
       </c>
       <c r="K50">
-        <v>932</v>
+        <v>1564</v>
       </c>
       <c r="L50" s="2">
-        <v>46185.23947916667</v>
+        <v>46230.21375</v>
       </c>
       <c r="M50" t="s">
         <v>260</v>
@@ -4005,13 +4002,13 @@
         <v>254</v>
       </c>
       <c r="O50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P50" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W50" s="2">
         <v>46164</v>
@@ -4049,10 +4046,10 @@
         <v>10</v>
       </c>
       <c r="K51">
-        <v>932</v>
+        <v>1564</v>
       </c>
       <c r="L51" s="2">
-        <v>46185.23959490741</v>
+        <v>46230.21386574074</v>
       </c>
       <c r="M51" t="s">
         <v>260</v>
@@ -4061,13 +4058,13 @@
         <v>254</v>
       </c>
       <c r="O51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W51" s="2">
         <v>46160</v>
@@ -4105,10 +4102,10 @@
         <v>10</v>
       </c>
       <c r="K52">
-        <v>916</v>
+        <v>1548</v>
       </c>
       <c r="L52" s="2">
-        <v>46185.23971064815</v>
+        <v>46230.21396990741</v>
       </c>
       <c r="M52" t="s">
         <v>260</v>
@@ -4117,13 +4114,13 @@
         <v>254</v>
       </c>
       <c r="O52" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P52" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q52" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W52" s="2">
         <v>46142</v>
@@ -4161,10 +4158,10 @@
         <v>15</v>
       </c>
       <c r="K53">
-        <v>1071</v>
+        <v>2080</v>
       </c>
       <c r="L53" s="2">
-        <v>46185.23987268518</v>
+        <v>46230.21409722222</v>
       </c>
       <c r="M53" t="s">
         <v>260</v>
@@ -4173,13 +4170,13 @@
         <v>254</v>
       </c>
       <c r="O53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P53" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W53" s="2">
         <v>46168</v>
@@ -4217,10 +4214,10 @@
         <v>10</v>
       </c>
       <c r="K54">
-        <v>761</v>
+        <v>1411</v>
       </c>
       <c r="L54" s="2">
-        <v>46185.23989583334</v>
+        <v>46230.21412037037</v>
       </c>
       <c r="M54" t="s">
         <v>260</v>
@@ -4229,13 +4226,13 @@
         <v>254</v>
       </c>
       <c r="O54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W54" s="2">
         <v>46163</v>
@@ -4273,10 +4270,10 @@
         <v>10</v>
       </c>
       <c r="K55">
-        <v>968</v>
+        <v>1616</v>
       </c>
       <c r="L55" s="2">
-        <v>46185.23993055556</v>
+        <v>46230.21414351852</v>
       </c>
       <c r="M55" t="s">
         <v>260</v>
@@ -4285,13 +4282,13 @@
         <v>254</v>
       </c>
       <c r="O55" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q55" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W55" s="2">
         <v>46168</v>
@@ -4332,7 +4329,7 @@
         <v>661</v>
       </c>
       <c r="L56" s="2">
-        <v>46185.23993055556</v>
+        <v>46230.2141550926</v>
       </c>
       <c r="M56" t="s">
         <v>258</v>
@@ -4341,13 +4338,13 @@
         <v>253</v>
       </c>
       <c r="O56" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P56" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q56" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W56" s="2">
         <v>46161</v>
@@ -4385,10 +4382,10 @@
         <v>30</v>
       </c>
       <c r="K57">
-        <v>2052</v>
+        <v>4002</v>
       </c>
       <c r="L57" s="2">
-        <v>46185.23994212963</v>
+        <v>46230.2141550926</v>
       </c>
       <c r="M57" t="s">
         <v>260</v>
@@ -4397,13 +4394,13 @@
         <v>254</v>
       </c>
       <c r="O57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P57" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W57" s="2">
         <v>46164</v>
@@ -4444,7 +4441,7 @@
         <v>982</v>
       </c>
       <c r="L58" s="2">
-        <v>46185.23995370371</v>
+        <v>46230.21416666666</v>
       </c>
       <c r="M58" t="s">
         <v>258</v>
@@ -4453,13 +4450,13 @@
         <v>253</v>
       </c>
       <c r="O58" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P58" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q58" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W58" s="2">
         <v>46148</v>
@@ -4500,7 +4497,7 @@
         <v>982</v>
       </c>
       <c r="L59" s="2">
-        <v>46185.23995370371</v>
+        <v>46230.21416666666</v>
       </c>
       <c r="M59" t="s">
         <v>258</v>
@@ -4509,13 +4506,13 @@
         <v>253</v>
       </c>
       <c r="O59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P59" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W59" s="2">
         <v>46168</v>
@@ -4556,7 +4553,7 @@
         <v>886</v>
       </c>
       <c r="L60" s="2">
-        <v>46185.23995370371</v>
+        <v>46230.21416666666</v>
       </c>
       <c r="M60" t="s">
         <v>258</v>
@@ -4565,13 +4562,13 @@
         <v>253</v>
       </c>
       <c r="O60" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P60" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q60" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W60" s="2">
         <v>46164</v>
@@ -4612,7 +4609,7 @@
         <v>1020</v>
       </c>
       <c r="L61" s="2">
-        <v>46185.23995370371</v>
+        <v>46230.21416666666</v>
       </c>
       <c r="M61" t="s">
         <v>258</v>
@@ -4621,13 +4618,13 @@
         <v>253</v>
       </c>
       <c r="O61" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P61" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q61" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W61" s="2">
         <v>46168</v>
@@ -4665,10 +4662,10 @@
         <v>10</v>
       </c>
       <c r="K62">
-        <v>1070</v>
+        <v>1720</v>
       </c>
       <c r="L62" s="2">
-        <v>46185.23997685185</v>
+        <v>46230.21416666666</v>
       </c>
       <c r="M62" t="s">
         <v>260</v>
@@ -4677,13 +4674,13 @@
         <v>254</v>
       </c>
       <c r="O62" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P62" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q62" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W62" s="2">
         <v>46164</v>
@@ -4724,7 +4721,7 @@
         <v>2005</v>
       </c>
       <c r="L63" s="2">
-        <v>46185.23998842593</v>
+        <v>46230.21417824074</v>
       </c>
       <c r="M63" t="s">
         <v>258</v>
@@ -4733,13 +4730,13 @@
         <v>253</v>
       </c>
       <c r="O63" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P63" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q63" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W63" s="2">
         <v>46164</v>
@@ -4762,7 +4759,7 @@
         <v>251</v>
       </c>
       <c r="F64" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G64" t="s">
         <v>255</v>
@@ -4774,28 +4771,28 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64">
-        <v>496</v>
+        <v>958</v>
       </c>
       <c r="L64" s="2">
-        <v>46185.23998842593</v>
+        <v>46230.21417824074</v>
       </c>
       <c r="M64" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N64" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P64" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W64" s="2">
         <v>46168</v>
@@ -4833,10 +4830,10 @@
         <v>30</v>
       </c>
       <c r="K65">
-        <v>1353</v>
+        <v>3303</v>
       </c>
       <c r="L65" s="2">
-        <v>46185.24012731481</v>
+        <v>46230.21429398148</v>
       </c>
       <c r="M65" t="s">
         <v>260</v>
@@ -4845,13 +4842,13 @@
         <v>254</v>
       </c>
       <c r="O65" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P65" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q65" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W65" s="2">
         <v>46168</v>
@@ -4889,10 +4886,10 @@
         <v>30</v>
       </c>
       <c r="K66">
-        <v>1387</v>
+        <v>3337</v>
       </c>
       <c r="L66" s="2">
-        <v>46185.24028935185</v>
+        <v>46230.2144212963</v>
       </c>
       <c r="M66" t="s">
         <v>260</v>
@@ -4901,13 +4898,13 @@
         <v>254</v>
       </c>
       <c r="O66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P66" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W66" s="2">
         <v>46160</v>
@@ -4942,13 +4939,13 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K67">
-        <v>936</v>
+        <v>1682</v>
       </c>
       <c r="L67" s="2">
-        <v>46185.24030092593</v>
+        <v>46230.21443287037</v>
       </c>
       <c r="M67" t="s">
         <v>260</v>
@@ -4957,13 +4954,13 @@
         <v>254</v>
       </c>
       <c r="O67" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P67" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q67" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W67" s="2">
         <v>46168</v>
@@ -5001,10 +4998,10 @@
         <v>30</v>
       </c>
       <c r="K68">
-        <v>1396</v>
+        <v>3317</v>
       </c>
       <c r="L68" s="2">
-        <v>46185.24043981481</v>
+        <v>46230.21457175926</v>
       </c>
       <c r="M68" t="s">
         <v>260</v>
@@ -5013,13 +5010,13 @@
         <v>254</v>
       </c>
       <c r="O68" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P68" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q68" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W68" s="2">
         <v>46168</v>
@@ -5057,10 +5054,10 @@
         <v>30</v>
       </c>
       <c r="K69">
-        <v>1396</v>
+        <v>3346</v>
       </c>
       <c r="L69" s="2">
-        <v>46185.24059027778</v>
+        <v>46230.21471064815</v>
       </c>
       <c r="M69" t="s">
         <v>260</v>
@@ -5069,13 +5066,13 @@
         <v>254</v>
       </c>
       <c r="O69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P69" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W69" s="2">
         <v>46168</v>
@@ -5110,13 +5107,13 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K70">
-        <v>1194</v>
+        <v>2104</v>
       </c>
       <c r="L70" s="2">
-        <v>46185.24060185185</v>
+        <v>46230.21472222222</v>
       </c>
       <c r="M70" t="s">
         <v>260</v>
@@ -5125,13 +5122,13 @@
         <v>254</v>
       </c>
       <c r="O70" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P70" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q70" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W70" s="2">
         <v>46168</v>
@@ -5166,13 +5163,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K71">
-        <v>1179</v>
+        <v>2085</v>
       </c>
       <c r="L71" s="2">
-        <v>46185.24061342593</v>
+        <v>46230.21474537037</v>
       </c>
       <c r="M71" t="s">
         <v>260</v>
@@ -5181,13 +5178,13 @@
         <v>254</v>
       </c>
       <c r="O71" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P71" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q71" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W71" s="2">
         <v>46168</v>
@@ -5228,7 +5225,7 @@
         <v>112</v>
       </c>
       <c r="L72" s="2">
-        <v>46185.24061342593</v>
+        <v>46230.21474537037</v>
       </c>
       <c r="M72" t="s">
         <v>258</v>
@@ -5237,13 +5234,13 @@
         <v>253</v>
       </c>
       <c r="O72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P72" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W72" s="2">
         <v>46164</v>
@@ -5278,28 +5275,28 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K73">
-        <v>605</v>
+        <v>1385</v>
       </c>
       <c r="L73" s="2">
-        <v>46185.240625</v>
+        <v>46230.21476851852</v>
       </c>
       <c r="M73" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N73" t="s">
         <v>254</v>
       </c>
       <c r="O73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P73" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W73" s="2">
         <v>46164</v>
@@ -5334,28 +5331,28 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K74">
-        <v>789</v>
+        <v>1569</v>
       </c>
       <c r="L74" s="2">
-        <v>46185.24063657408</v>
+        <v>46230.21479166667</v>
       </c>
       <c r="M74" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N74" t="s">
         <v>254</v>
       </c>
       <c r="O74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W74" s="2">
         <v>46185</v>
@@ -5393,10 +5390,10 @@
         <v>12</v>
       </c>
       <c r="K75">
-        <v>820</v>
+        <v>1600</v>
       </c>
       <c r="L75" s="2">
-        <v>46185.24064814814</v>
+        <v>46230.21480324074</v>
       </c>
       <c r="M75" t="s">
         <v>260</v>
@@ -5405,13 +5402,13 @@
         <v>254</v>
       </c>
       <c r="O75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P75" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W75" s="2">
         <v>46149</v>
@@ -5449,10 +5446,10 @@
         <v>12</v>
       </c>
       <c r="K76">
-        <v>864</v>
+        <v>1644</v>
       </c>
       <c r="L76" s="2">
-        <v>46185.2406712963</v>
+        <v>46230.21482638889</v>
       </c>
       <c r="M76" t="s">
         <v>260</v>
@@ -5461,13 +5458,13 @@
         <v>254</v>
       </c>
       <c r="O76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P76" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W76" s="2">
         <v>46149</v>
@@ -5505,10 +5502,10 @@
         <v>12</v>
       </c>
       <c r="K77">
-        <v>877</v>
+        <v>1657</v>
       </c>
       <c r="L77" s="2">
-        <v>46185.24068287037</v>
+        <v>46230.21484953703</v>
       </c>
       <c r="M77" t="s">
         <v>260</v>
@@ -5517,13 +5514,13 @@
         <v>254</v>
       </c>
       <c r="O77" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P77" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q77" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W77" s="2">
         <v>46168</v>
@@ -5561,10 +5558,10 @@
         <v>12</v>
       </c>
       <c r="K78">
-        <v>877</v>
+        <v>1657</v>
       </c>
       <c r="L78" s="2">
-        <v>46185.24070601852</v>
+        <v>46230.21487268519</v>
       </c>
       <c r="M78" t="s">
         <v>260</v>
@@ -5573,13 +5570,13 @@
         <v>254</v>
       </c>
       <c r="O78" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P78" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q78" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W78" s="2">
         <v>46160</v>
@@ -5617,10 +5614,10 @@
         <v>12</v>
       </c>
       <c r="K79">
-        <v>890</v>
+        <v>1670</v>
       </c>
       <c r="L79" s="2">
-        <v>46185.24072916667</v>
+        <v>46230.21489583333</v>
       </c>
       <c r="M79" t="s">
         <v>260</v>
@@ -5629,13 +5626,13 @@
         <v>254</v>
       </c>
       <c r="O79" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P79" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q79" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W79" s="2">
         <v>46168</v>
@@ -5673,10 +5670,10 @@
         <v>10</v>
       </c>
       <c r="K80">
-        <v>795</v>
+        <v>1441</v>
       </c>
       <c r="L80" s="2">
-        <v>46185.24074074074</v>
+        <v>46230.2149074074</v>
       </c>
       <c r="M80" t="s">
         <v>260</v>
@@ -5685,13 +5682,13 @@
         <v>254</v>
       </c>
       <c r="O80" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P80" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q80" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W80" s="2">
         <v>46164</v>
@@ -5729,10 +5726,10 @@
         <v>30</v>
       </c>
       <c r="K81">
-        <v>1941</v>
+        <v>3891</v>
       </c>
       <c r="L81" s="2">
-        <v>46185.24075231481</v>
+        <v>46230.21493055556</v>
       </c>
       <c r="M81" t="s">
         <v>260</v>
@@ -5741,13 +5738,13 @@
         <v>254</v>
       </c>
       <c r="O81" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P81" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q81" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W81" s="2">
         <v>46160</v>
@@ -5788,7 +5785,7 @@
         <v>2077</v>
       </c>
       <c r="L82" s="2">
-        <v>46185.24076388889</v>
+        <v>46230.21493055556</v>
       </c>
       <c r="M82" t="s">
         <v>258</v>
@@ -5797,13 +5794,13 @@
         <v>253</v>
       </c>
       <c r="O82" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P82" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q82" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W82" s="2">
         <v>46161</v>
@@ -5844,7 +5841,7 @@
         <v>476</v>
       </c>
       <c r="L83" s="2">
-        <v>46185.24076388889</v>
+        <v>46230.21493055556</v>
       </c>
       <c r="M83" t="s">
         <v>258</v>
@@ -5853,13 +5850,13 @@
         <v>253</v>
       </c>
       <c r="O83" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P83" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q83" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W83" s="2">
         <v>46168</v>
@@ -5900,7 +5897,7 @@
         <v>412</v>
       </c>
       <c r="L84" s="2">
-        <v>46185.24076388889</v>
+        <v>46230.21493055556</v>
       </c>
       <c r="M84" t="s">
         <v>258</v>
@@ -5909,13 +5906,13 @@
         <v>253</v>
       </c>
       <c r="O84" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P84" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q84" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W84" s="2">
         <v>46164</v>
@@ -5956,7 +5953,7 @@
         <v>721</v>
       </c>
       <c r="L85" s="2">
-        <v>46185.24076388889</v>
+        <v>46230.21493055556</v>
       </c>
       <c r="M85" t="s">
         <v>258</v>
@@ -5965,13 +5962,13 @@
         <v>253</v>
       </c>
       <c r="O85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P85" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W85" s="2">
         <v>46168</v>
@@ -6009,10 +6006,10 @@
         <v>2</v>
       </c>
       <c r="K86">
-        <v>542</v>
+        <v>672</v>
       </c>
       <c r="L86" s="2">
-        <v>46185.24077546296</v>
+        <v>46230.2149537037</v>
       </c>
       <c r="M86" t="s">
         <v>259</v>
@@ -6021,13 +6018,13 @@
         <v>254</v>
       </c>
       <c r="O86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P86" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W86" s="2">
         <v>46164</v>
@@ -6065,10 +6062,10 @@
         <v>30</v>
       </c>
       <c r="K87">
-        <v>1957</v>
+        <v>3907</v>
       </c>
       <c r="L87" s="2">
-        <v>46185.24079861111</v>
+        <v>46230.21497685185</v>
       </c>
       <c r="M87" t="s">
         <v>260</v>
@@ -6077,13 +6074,13 @@
         <v>254</v>
       </c>
       <c r="O87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P87" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W87" s="2">
         <v>46168</v>
@@ -6121,10 +6118,10 @@
         <v>30</v>
       </c>
       <c r="K88">
-        <v>1901</v>
+        <v>3851</v>
       </c>
       <c r="L88" s="2">
-        <v>46185.24084490741</v>
+        <v>46230.21502314815</v>
       </c>
       <c r="M88" t="s">
         <v>260</v>
@@ -6133,13 +6130,13 @@
         <v>254</v>
       </c>
       <c r="O88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P88" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W88" s="2">
         <v>46163</v>
@@ -6174,13 +6171,13 @@
         <v>253</v>
       </c>
       <c r="O89" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P89" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q89" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="90" spans="1:23">
@@ -6215,10 +6212,10 @@
         <v>1</v>
       </c>
       <c r="K90">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="L90" s="2">
-        <v>46185.24086805555</v>
+        <v>46230.2150462963</v>
       </c>
       <c r="M90" t="s">
         <v>259</v>
@@ -6227,13 +6224,13 @@
         <v>254</v>
       </c>
       <c r="O90" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P90" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q90" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W90" s="2">
         <v>46154</v>
@@ -6268,13 +6265,13 @@
         <v>254</v>
       </c>
       <c r="O91" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P91" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q91" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W91" s="2">
         <v>46154</v>
@@ -6315,7 +6312,7 @@
         <v>65</v>
       </c>
       <c r="L92" s="2">
-        <v>46185.24087962963</v>
+        <v>46230.2150462963</v>
       </c>
       <c r="M92" t="s">
         <v>258</v>
@@ -6324,13 +6321,13 @@
         <v>253</v>
       </c>
       <c r="O92" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P92" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q92" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W92" s="2">
         <v>46164</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="267">
   <si>
     <t>site_name</t>
   </si>
@@ -58,6 +58,9 @@
     <t>track</t>
   </si>
   <si>
+    <t>owner_step</t>
+  </si>
+  <si>
     <t>official_flag</t>
   </si>
   <si>
@@ -76,9 +79,6 @@
     <t>crawl_scope</t>
   </si>
   <si>
-    <t>owner_step</t>
-  </si>
-  <si>
     <t>memo</t>
   </si>
   <si>
@@ -775,12 +775,12 @@
     <t>🇺🇸</t>
   </si>
   <si>
+    <t>regulation</t>
+  </si>
+  <si>
     <t>news</t>
   </si>
   <si>
-    <t>regulation</t>
-  </si>
-  <si>
     <t>customs</t>
   </si>
   <si>
@@ -790,13 +790,19 @@
     <t>customs_tax</t>
   </si>
   <si>
-    <t>SKIP_NEWS_MOVED_TO_STEP2_3</t>
+    <t>OK</t>
   </si>
   <si>
     <t>CHECK</t>
   </si>
   <si>
-    <t>OK</t>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>STEP2-3</t>
+  </si>
+  <si>
+    <t>STEP1</t>
   </si>
   <si>
     <t>N</t>
@@ -1263,19 +1269,19 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K2">
-        <v>1795</v>
+        <v>1855</v>
       </c>
       <c r="L2" s="2">
-        <v>46230.21296296296</v>
+        <v>46243.50512731481</v>
       </c>
       <c r="M2" t="s">
         <v>258</v>
       </c>
       <c r="N2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O2" t="s">
         <v>261</v>
@@ -1284,7 +1290,10 @@
         <v>263</v>
       </c>
       <c r="Q2" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R2" t="s">
+        <v>263</v>
       </c>
       <c r="W2" s="2">
         <v>46155</v>
@@ -1322,19 +1331,19 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K3">
-        <v>1752</v>
+        <v>1812</v>
       </c>
       <c r="L3" s="2">
-        <v>46230.21296296296</v>
+        <v>46243.50516203704</v>
       </c>
       <c r="M3" t="s">
         <v>258</v>
       </c>
       <c r="N3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O3" t="s">
         <v>261</v>
@@ -1343,7 +1352,10 @@
         <v>263</v>
       </c>
       <c r="Q3" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R3" t="s">
+        <v>263</v>
       </c>
       <c r="W3" s="2">
         <v>46087</v>
@@ -1381,19 +1393,19 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K4">
-        <v>1533</v>
+        <v>1581</v>
       </c>
       <c r="L4" s="2">
-        <v>46230.21296296296</v>
+        <v>46243.50517361111</v>
       </c>
       <c r="M4" t="s">
         <v>258</v>
       </c>
       <c r="N4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O4" t="s">
         <v>261</v>
@@ -1402,7 +1414,10 @@
         <v>263</v>
       </c>
       <c r="Q4" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R4" t="s">
+        <v>263</v>
       </c>
       <c r="W4" s="2">
         <v>46168</v>
@@ -1440,19 +1455,19 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L5" s="2">
-        <v>46230.21296296296</v>
+        <v>46243.50518518518</v>
       </c>
       <c r="M5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O5" t="s">
         <v>261</v>
@@ -1461,7 +1476,10 @@
         <v>263</v>
       </c>
       <c r="Q5" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R5" t="s">
+        <v>263</v>
       </c>
       <c r="W5" s="2">
         <v>46161</v>
@@ -1487,7 +1505,7 @@
         <v>244</v>
       </c>
       <c r="F6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G6" t="s">
         <v>255</v>
@@ -1499,19 +1517,19 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46230.21296296296</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O6" t="s">
         <v>262</v>
@@ -1520,7 +1538,10 @@
         <v>264</v>
       </c>
       <c r="Q6" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R6" t="s">
+        <v>264</v>
       </c>
       <c r="W6" s="2">
         <v>46168</v>
@@ -1558,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L7" s="2">
-        <v>46230.21297453704</v>
+        <v>46243.50520833334</v>
       </c>
       <c r="M7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O7" t="s">
         <v>261</v>
@@ -1579,7 +1600,10 @@
         <v>263</v>
       </c>
       <c r="Q7" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R7" t="s">
+        <v>263</v>
       </c>
       <c r="W7" s="2">
         <v>46164</v>
@@ -1617,19 +1641,19 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L8" s="2">
-        <v>46230.21297453704</v>
+        <v>46243.50521990741</v>
       </c>
       <c r="M8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O8" t="s">
         <v>261</v>
@@ -1638,7 +1662,10 @@
         <v>263</v>
       </c>
       <c r="Q8" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R8" t="s">
+        <v>263</v>
       </c>
       <c r="W8" s="2">
         <v>46155</v>
@@ -1676,19 +1703,19 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K9">
-        <v>1901</v>
+        <v>1961</v>
       </c>
       <c r="L9" s="2">
-        <v>46230.21297453704</v>
+        <v>46243.50527777777</v>
       </c>
       <c r="M9" t="s">
         <v>258</v>
       </c>
       <c r="N9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O9" t="s">
         <v>261</v>
@@ -1697,7 +1724,10 @@
         <v>263</v>
       </c>
       <c r="Q9" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R9" t="s">
+        <v>263</v>
       </c>
       <c r="W9" s="2">
         <v>46045</v>
@@ -1735,19 +1765,19 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K10">
-        <v>1704</v>
+        <v>1764</v>
       </c>
       <c r="L10" s="2">
-        <v>46230.21297453704</v>
+        <v>46243.50550925926</v>
       </c>
       <c r="M10" t="s">
         <v>258</v>
       </c>
       <c r="N10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O10" t="s">
         <v>261</v>
@@ -1756,7 +1786,10 @@
         <v>263</v>
       </c>
       <c r="Q10" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R10" t="s">
+        <v>263</v>
       </c>
       <c r="W10" s="2">
         <v>46045</v>
@@ -1794,19 +1827,19 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K11">
-        <v>1675</v>
+        <v>1735</v>
       </c>
       <c r="L11" s="2">
-        <v>46230.21297453704</v>
+        <v>46243.50556712963</v>
       </c>
       <c r="M11" t="s">
         <v>258</v>
       </c>
       <c r="N11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O11" t="s">
         <v>261</v>
@@ -1815,7 +1848,10 @@
         <v>263</v>
       </c>
       <c r="Q11" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R11" t="s">
+        <v>263</v>
       </c>
       <c r="W11" s="2">
         <v>46129</v>
@@ -1853,19 +1889,19 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="L12" s="2">
-        <v>46230.21297453704</v>
+        <v>46243.50557870371</v>
       </c>
       <c r="M12" t="s">
         <v>258</v>
       </c>
       <c r="N12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O12" t="s">
         <v>261</v>
@@ -1874,7 +1910,10 @@
         <v>263</v>
       </c>
       <c r="Q12" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R12" t="s">
+        <v>263</v>
       </c>
       <c r="W12" s="2">
         <v>46164</v>
@@ -1900,7 +1939,7 @@
         <v>247</v>
       </c>
       <c r="F13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G13" t="s">
         <v>255</v>
@@ -1912,19 +1951,19 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="L13" s="2">
-        <v>46230.21299768519</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O13" t="s">
         <v>262</v>
@@ -1933,7 +1972,10 @@
         <v>264</v>
       </c>
       <c r="Q13" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R13" t="s">
+        <v>264</v>
       </c>
       <c r="W13" s="2">
         <v>46168</v>
@@ -1959,7 +2001,7 @@
         <v>247</v>
       </c>
       <c r="F14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G14" t="s">
         <v>255</v>
@@ -1971,19 +2013,19 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>3775</v>
+        <v>3475</v>
       </c>
       <c r="L14" s="2">
-        <v>46230.21302083333</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M14" t="s">
         <v>260</v>
       </c>
       <c r="N14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O14" t="s">
         <v>262</v>
@@ -1992,7 +2034,10 @@
         <v>264</v>
       </c>
       <c r="Q14" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R14" t="s">
+        <v>264</v>
       </c>
       <c r="W14" s="2">
         <v>46168</v>
@@ -2015,7 +2060,7 @@
         <v>247</v>
       </c>
       <c r="F15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G15" t="s">
         <v>255</v>
@@ -2027,19 +2072,19 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>3775</v>
+        <v>3475</v>
       </c>
       <c r="L15" s="2">
-        <v>46230.21304398148</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M15" t="s">
         <v>260</v>
       </c>
       <c r="N15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O15" t="s">
         <v>262</v>
@@ -2048,7 +2093,10 @@
         <v>264</v>
       </c>
       <c r="Q15" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R15" t="s">
+        <v>264</v>
       </c>
       <c r="W15" s="2">
         <v>46168</v>
@@ -2071,7 +2119,7 @@
         <v>247</v>
       </c>
       <c r="F16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G16" t="s">
         <v>255</v>
@@ -2083,19 +2131,19 @@
         <v>1</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>3775</v>
+        <v>3475</v>
       </c>
       <c r="L16" s="2">
-        <v>46230.21305555556</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M16" t="s">
         <v>260</v>
       </c>
       <c r="N16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O16" t="s">
         <v>262</v>
@@ -2104,7 +2152,10 @@
         <v>264</v>
       </c>
       <c r="Q16" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R16" t="s">
+        <v>264</v>
       </c>
       <c r="W16" s="2">
         <v>46164</v>
@@ -2139,19 +2190,19 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K17">
-        <v>1809</v>
+        <v>1869</v>
       </c>
       <c r="L17" s="2">
-        <v>46230.21306712963</v>
+        <v>46243.50569444444</v>
       </c>
       <c r="M17" t="s">
         <v>258</v>
       </c>
       <c r="N17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O17" t="s">
         <v>261</v>
@@ -2160,7 +2211,10 @@
         <v>263</v>
       </c>
       <c r="Q17" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R17" t="s">
+        <v>263</v>
       </c>
       <c r="W17" s="2">
         <v>46113</v>
@@ -2183,7 +2237,7 @@
         <v>248</v>
       </c>
       <c r="F18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G18" t="s">
         <v>255</v>
@@ -2195,19 +2249,19 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>3891</v>
+        <v>3599</v>
       </c>
       <c r="L18" s="2">
-        <v>46230.21306712963</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O18" t="s">
         <v>262</v>
@@ -2216,10 +2270,13 @@
         <v>264</v>
       </c>
       <c r="Q18" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R18" t="s">
+        <v>264</v>
       </c>
       <c r="W18" s="2">
-        <v>46168</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -2251,19 +2308,19 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K19">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="L19" s="2">
-        <v>46230.2130787037</v>
+        <v>46243.50572916667</v>
       </c>
       <c r="M19" t="s">
         <v>258</v>
       </c>
       <c r="N19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O19" t="s">
         <v>261</v>
@@ -2272,7 +2329,10 @@
         <v>263</v>
       </c>
       <c r="Q19" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R19" t="s">
+        <v>263</v>
       </c>
       <c r="W19" s="2">
         <v>46163</v>
@@ -2307,19 +2367,19 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K20">
-        <v>1826</v>
+        <v>1886</v>
       </c>
       <c r="L20" s="2">
-        <v>46230.2130787037</v>
+        <v>46243.50575231481</v>
       </c>
       <c r="M20" t="s">
         <v>258</v>
       </c>
       <c r="N20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O20" t="s">
         <v>261</v>
@@ -2328,7 +2388,10 @@
         <v>263</v>
       </c>
       <c r="Q20" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R20" t="s">
+        <v>263</v>
       </c>
       <c r="W20" s="2">
         <v>46165</v>
@@ -2363,19 +2426,19 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K21">
-        <v>1791</v>
+        <v>1851</v>
       </c>
       <c r="L21" s="2">
-        <v>46230.2130787037</v>
+        <v>46243.50576388889</v>
       </c>
       <c r="M21" t="s">
         <v>258</v>
       </c>
       <c r="N21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O21" t="s">
         <v>261</v>
@@ -2384,7 +2447,10 @@
         <v>263</v>
       </c>
       <c r="Q21" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R21" t="s">
+        <v>263</v>
       </c>
       <c r="W21" s="2">
         <v>46166</v>
@@ -2407,7 +2473,7 @@
         <v>249</v>
       </c>
       <c r="F22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G22" t="s">
         <v>255</v>
@@ -2419,19 +2485,19 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>3891</v>
+        <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46230.21309027778</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M22" t="s">
         <v>260</v>
       </c>
       <c r="N22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O22" t="s">
         <v>262</v>
@@ -2440,7 +2506,10 @@
         <v>264</v>
       </c>
       <c r="Q22" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R22" t="s">
+        <v>264</v>
       </c>
       <c r="W22" s="2">
         <v>46168</v>
@@ -2463,7 +2532,7 @@
         <v>249</v>
       </c>
       <c r="F23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G23" t="s">
         <v>255</v>
@@ -2475,19 +2544,19 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>3891</v>
+        <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46230.21310185185</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M23" t="s">
         <v>260</v>
       </c>
       <c r="N23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O23" t="s">
         <v>262</v>
@@ -2496,7 +2565,10 @@
         <v>264</v>
       </c>
       <c r="Q23" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R23" t="s">
+        <v>264</v>
       </c>
       <c r="W23" s="2">
         <v>46168</v>
@@ -2519,7 +2591,7 @@
         <v>249</v>
       </c>
       <c r="F24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G24" t="s">
         <v>255</v>
@@ -2531,19 +2603,19 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="L24" s="2">
-        <v>46230.213125</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M24" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O24" t="s">
         <v>262</v>
@@ -2552,7 +2624,10 @@
         <v>264</v>
       </c>
       <c r="Q24" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R24" t="s">
+        <v>264</v>
       </c>
       <c r="W24" s="2">
         <v>46168</v>
@@ -2575,7 +2650,7 @@
         <v>249</v>
       </c>
       <c r="F25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G25" t="s">
         <v>255</v>
@@ -2587,19 +2662,19 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="L25" s="2">
-        <v>46230.21314814815</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O25" t="s">
         <v>262</v>
@@ -2608,7 +2683,10 @@
         <v>264</v>
       </c>
       <c r="Q25" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R25" t="s">
+        <v>264</v>
       </c>
       <c r="W25" s="2">
         <v>46167</v>
@@ -2631,7 +2709,7 @@
         <v>249</v>
       </c>
       <c r="F26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G26" t="s">
         <v>255</v>
@@ -2643,19 +2721,19 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="L26" s="2">
-        <v>46230.21317129629</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O26" t="s">
         <v>262</v>
@@ -2664,7 +2742,10 @@
         <v>264</v>
       </c>
       <c r="Q26" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R26" t="s">
+        <v>264</v>
       </c>
       <c r="W26" s="2">
         <v>46168</v>
@@ -2699,19 +2780,19 @@
         <v>1</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K27">
-        <v>2166</v>
+        <v>2226</v>
       </c>
       <c r="L27" s="2">
-        <v>46230.21317129629</v>
+        <v>46243.50589120371</v>
       </c>
       <c r="M27" t="s">
         <v>258</v>
       </c>
       <c r="N27" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O27" t="s">
         <v>261</v>
@@ -2720,7 +2801,10 @@
         <v>263</v>
       </c>
       <c r="Q27" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R27" t="s">
+        <v>263</v>
       </c>
       <c r="W27" s="2">
         <v>46172</v>
@@ -2755,19 +2839,19 @@
         <v>1</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K28">
-        <v>2204</v>
+        <v>2264</v>
       </c>
       <c r="L28" s="2">
-        <v>46230.21317129629</v>
+        <v>46243.50591435185</v>
       </c>
       <c r="M28" t="s">
         <v>258</v>
       </c>
       <c r="N28" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O28" t="s">
         <v>261</v>
@@ -2776,7 +2860,10 @@
         <v>263</v>
       </c>
       <c r="Q28" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R28" t="s">
+        <v>263</v>
       </c>
       <c r="W28" s="2">
         <v>46164</v>
@@ -2811,19 +2898,19 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K29">
-        <v>1797</v>
+        <v>1855</v>
       </c>
       <c r="L29" s="2">
-        <v>46230.21317129629</v>
+        <v>46243.50592592593</v>
       </c>
       <c r="M29" t="s">
         <v>258</v>
       </c>
       <c r="N29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O29" t="s">
         <v>261</v>
@@ -2832,7 +2919,10 @@
         <v>263</v>
       </c>
       <c r="Q29" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R29" t="s">
+        <v>263</v>
       </c>
       <c r="W29" s="2">
         <v>46168</v>
@@ -2867,19 +2957,19 @@
         <v>1</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K30">
-        <v>1321</v>
+        <v>1361</v>
       </c>
       <c r="L30" s="2">
-        <v>46230.21317129629</v>
+        <v>46243.50594907408</v>
       </c>
       <c r="M30" t="s">
         <v>258</v>
       </c>
       <c r="N30" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O30" t="s">
         <v>261</v>
@@ -2888,7 +2978,10 @@
         <v>263</v>
       </c>
       <c r="Q30" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R30" t="s">
+        <v>263</v>
       </c>
       <c r="W30" s="2">
         <v>46168</v>
@@ -2923,19 +3016,19 @@
         <v>1</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K31">
-        <v>1205</v>
+        <v>1223</v>
       </c>
       <c r="L31" s="2">
-        <v>46230.21317129629</v>
+        <v>46243.50596064814</v>
       </c>
       <c r="M31" t="s">
         <v>258</v>
       </c>
       <c r="N31" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O31" t="s">
         <v>261</v>
@@ -2944,7 +3037,10 @@
         <v>263</v>
       </c>
       <c r="Q31" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R31" t="s">
+        <v>263</v>
       </c>
       <c r="W31" s="2">
         <v>46168</v>
@@ -2967,7 +3063,7 @@
         <v>251</v>
       </c>
       <c r="F32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G32" t="s">
         <v>255</v>
@@ -2979,19 +3075,19 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="K32">
-        <v>6062</v>
+        <v>5921</v>
       </c>
       <c r="L32" s="2">
-        <v>46230.21334490741</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M32" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O32" t="s">
         <v>262</v>
@@ -3000,10 +3096,13 @@
         <v>264</v>
       </c>
       <c r="Q32" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R32" t="s">
+        <v>264</v>
       </c>
       <c r="W32" s="2">
-        <v>46160</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="33" spans="1:23">
@@ -3035,19 +3134,19 @@
         <v>1</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="L33" s="2">
-        <v>46230.21334490741</v>
+        <v>46243.50614583334</v>
       </c>
       <c r="M33" t="s">
         <v>258</v>
       </c>
       <c r="N33" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O33" t="s">
         <v>261</v>
@@ -3056,7 +3155,10 @@
         <v>263</v>
       </c>
       <c r="Q33" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R33" t="s">
+        <v>263</v>
       </c>
       <c r="W33" s="2">
         <v>46168</v>
@@ -3091,19 +3193,19 @@
         <v>1</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="L34" s="2">
-        <v>46230.21334490741</v>
+        <v>46243.50615740741</v>
       </c>
       <c r="M34" t="s">
         <v>258</v>
       </c>
       <c r="N34" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O34" t="s">
         <v>261</v>
@@ -3112,7 +3214,10 @@
         <v>263</v>
       </c>
       <c r="Q34" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R34" t="s">
+        <v>263</v>
       </c>
       <c r="W34" s="2">
         <v>46168</v>
@@ -3135,7 +3240,7 @@
         <v>251</v>
       </c>
       <c r="F35" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G35" t="s">
         <v>255</v>
@@ -3147,19 +3252,19 @@
         <v>1</v>
       </c>
       <c r="J35">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>3891</v>
+        <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46230.21335648148</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M35" t="s">
         <v>260</v>
       </c>
       <c r="N35" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O35" t="s">
         <v>262</v>
@@ -3168,7 +3273,10 @@
         <v>264</v>
       </c>
       <c r="Q35" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R35" t="s">
+        <v>264</v>
       </c>
       <c r="W35" s="2">
         <v>46157</v>
@@ -3191,7 +3299,7 @@
         <v>251</v>
       </c>
       <c r="F36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G36" t="s">
         <v>255</v>
@@ -3203,19 +3311,19 @@
         <v>1</v>
       </c>
       <c r="J36">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>3891</v>
+        <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46230.21336805556</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M36" t="s">
         <v>260</v>
       </c>
       <c r="N36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O36" t="s">
         <v>262</v>
@@ -3224,7 +3332,10 @@
         <v>264</v>
       </c>
       <c r="Q36" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R36" t="s">
+        <v>264</v>
       </c>
       <c r="W36" s="2">
         <v>46168</v>
@@ -3247,7 +3358,7 @@
         <v>251</v>
       </c>
       <c r="F37" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G37" t="s">
         <v>255</v>
@@ -3259,19 +3370,19 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>2126</v>
+        <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46230.21337962963</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M37" t="s">
         <v>260</v>
       </c>
       <c r="N37" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O37" t="s">
         <v>262</v>
@@ -3280,7 +3391,10 @@
         <v>264</v>
       </c>
       <c r="Q37" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R37" t="s">
+        <v>264</v>
       </c>
       <c r="W37" s="2">
         <v>46132</v>
@@ -3303,7 +3417,7 @@
         <v>251</v>
       </c>
       <c r="F38" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G38" t="s">
         <v>255</v>
@@ -3315,19 +3429,19 @@
         <v>1</v>
       </c>
       <c r="J38">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>3237</v>
+        <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46230.2133912037</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M38" t="s">
         <v>260</v>
       </c>
       <c r="N38" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O38" t="s">
         <v>262</v>
@@ -3336,7 +3450,10 @@
         <v>264</v>
       </c>
       <c r="Q38" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R38" t="s">
+        <v>264</v>
       </c>
       <c r="W38" s="2">
         <v>46113</v>
@@ -3359,7 +3476,7 @@
         <v>251</v>
       </c>
       <c r="F39" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G39" t="s">
         <v>255</v>
@@ -3371,19 +3488,19 @@
         <v>1</v>
       </c>
       <c r="J39">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>3476</v>
+        <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46230.21340277778</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M39" t="s">
         <v>260</v>
       </c>
       <c r="N39" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O39" t="s">
         <v>262</v>
@@ -3392,7 +3509,10 @@
         <v>264</v>
       </c>
       <c r="Q39" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R39" t="s">
+        <v>264</v>
       </c>
       <c r="W39" s="2">
         <v>46140</v>
@@ -3415,7 +3535,7 @@
         <v>251</v>
       </c>
       <c r="F40" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G40" t="s">
         <v>255</v>
@@ -3427,19 +3547,19 @@
         <v>1</v>
       </c>
       <c r="J40">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>3428</v>
+        <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46230.21341435185</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M40" t="s">
         <v>260</v>
       </c>
       <c r="N40" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O40" t="s">
         <v>262</v>
@@ -3448,7 +3568,10 @@
         <v>264</v>
       </c>
       <c r="Q40" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R40" t="s">
+        <v>264</v>
       </c>
       <c r="W40" s="2">
         <v>46024</v>
@@ -3471,7 +3594,7 @@
         <v>251</v>
       </c>
       <c r="F41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G41" t="s">
         <v>255</v>
@@ -3483,19 +3606,19 @@
         <v>1</v>
       </c>
       <c r="J41">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>3842</v>
+        <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46230.21342592593</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M41" t="s">
         <v>260</v>
       </c>
       <c r="N41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O41" t="s">
         <v>262</v>
@@ -3504,7 +3627,10 @@
         <v>264</v>
       </c>
       <c r="Q41" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R41" t="s">
+        <v>264</v>
       </c>
       <c r="W41" s="2">
         <v>46168</v>
@@ -3527,7 +3653,7 @@
         <v>251</v>
       </c>
       <c r="F42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G42" t="s">
         <v>255</v>
@@ -3539,19 +3665,19 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>3833</v>
+        <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46230.2134375</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M42" t="s">
         <v>260</v>
       </c>
       <c r="N42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O42" t="s">
         <v>262</v>
@@ -3560,7 +3686,10 @@
         <v>264</v>
       </c>
       <c r="Q42" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R42" t="s">
+        <v>264</v>
       </c>
       <c r="W42" s="2">
         <v>46164</v>
@@ -3583,7 +3712,7 @@
         <v>251</v>
       </c>
       <c r="F43" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G43" t="s">
         <v>255</v>
@@ -3595,19 +3724,19 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>3813</v>
+        <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46230.21344907407</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M43" t="s">
         <v>260</v>
       </c>
       <c r="N43" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O43" t="s">
         <v>262</v>
@@ -3616,7 +3745,10 @@
         <v>264</v>
       </c>
       <c r="Q43" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R43" t="s">
+        <v>264</v>
       </c>
       <c r="W43" s="2">
         <v>46112</v>
@@ -3651,19 +3783,19 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K44">
-        <v>1124</v>
+        <v>1148</v>
       </c>
       <c r="L44" s="2">
-        <v>46230.21346064815</v>
+        <v>46243.50630787037</v>
       </c>
       <c r="M44" t="s">
         <v>258</v>
       </c>
       <c r="N44" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O44" t="s">
         <v>261</v>
@@ -3672,7 +3804,10 @@
         <v>263</v>
       </c>
       <c r="Q44" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R44" t="s">
+        <v>263</v>
       </c>
       <c r="W44" s="2">
         <v>46171</v>
@@ -3695,7 +3830,7 @@
         <v>251</v>
       </c>
       <c r="F45" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G45" t="s">
         <v>255</v>
@@ -3707,19 +3842,19 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K45">
-        <v>3020</v>
+        <v>2873</v>
       </c>
       <c r="L45" s="2">
-        <v>46230.21346064815</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M45" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N45" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O45" t="s">
         <v>262</v>
@@ -3728,10 +3863,13 @@
         <v>264</v>
       </c>
       <c r="Q45" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R45" t="s">
+        <v>264</v>
       </c>
       <c r="W45" s="2">
-        <v>46168</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="46" spans="1:23">
@@ -3751,7 +3889,7 @@
         <v>251</v>
       </c>
       <c r="F46" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G46" t="s">
         <v>255</v>
@@ -3766,16 +3904,16 @@
         <v>20</v>
       </c>
       <c r="K46">
-        <v>3196</v>
+        <v>3157</v>
       </c>
       <c r="L46" s="2">
-        <v>46230.21348379629</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M46" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N46" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O46" t="s">
         <v>262</v>
@@ -3784,10 +3922,13 @@
         <v>264</v>
       </c>
       <c r="Q46" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R46" t="s">
+        <v>264</v>
       </c>
       <c r="W46" s="2">
-        <v>46168</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="47" spans="1:23">
@@ -3807,7 +3948,7 @@
         <v>251</v>
       </c>
       <c r="F47" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G47" t="s">
         <v>255</v>
@@ -3819,19 +3960,19 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K47">
-        <v>3252</v>
+        <v>3188</v>
       </c>
       <c r="L47" s="2">
-        <v>46230.21350694444</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M47" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N47" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O47" t="s">
         <v>262</v>
@@ -3840,10 +3981,13 @@
         <v>264</v>
       </c>
       <c r="Q47" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R47" t="s">
+        <v>264</v>
       </c>
       <c r="W47" s="2">
-        <v>46168</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="48" spans="1:23">
@@ -3863,7 +4007,7 @@
         <v>251</v>
       </c>
       <c r="F48" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G48" t="s">
         <v>255</v>
@@ -3875,19 +4019,19 @@
         <v>1</v>
       </c>
       <c r="J48">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K48">
-        <v>2489</v>
+        <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46230.21353009259</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M48" t="s">
         <v>260</v>
       </c>
       <c r="N48" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O48" t="s">
         <v>262</v>
@@ -3896,7 +4040,10 @@
         <v>264</v>
       </c>
       <c r="Q48" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R48" t="s">
+        <v>264</v>
       </c>
       <c r="W48" s="2">
         <v>46168</v>
@@ -3919,7 +4066,7 @@
         <v>251</v>
       </c>
       <c r="F49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G49" t="s">
         <v>255</v>
@@ -3931,19 +4078,19 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>1573</v>
+        <v>1481</v>
       </c>
       <c r="L49" s="2">
-        <v>46230.21364583333</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M49" t="s">
         <v>260</v>
       </c>
       <c r="N49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O49" t="s">
         <v>262</v>
@@ -3952,10 +4099,13 @@
         <v>264</v>
       </c>
       <c r="Q49" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R49" t="s">
+        <v>264</v>
       </c>
       <c r="W49" s="2">
-        <v>46163</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="50" spans="1:23">
@@ -3975,7 +4125,7 @@
         <v>251</v>
       </c>
       <c r="F50" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G50" t="s">
         <v>255</v>
@@ -3987,19 +4137,19 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>1564</v>
+        <v>1475</v>
       </c>
       <c r="L50" s="2">
-        <v>46230.21375</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M50" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N50" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O50" t="s">
         <v>262</v>
@@ -4008,10 +4158,13 @@
         <v>264</v>
       </c>
       <c r="Q50" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R50" t="s">
+        <v>264</v>
       </c>
       <c r="W50" s="2">
-        <v>46164</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="51" spans="1:23">
@@ -4031,7 +4184,7 @@
         <v>251</v>
       </c>
       <c r="F51" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G51" t="s">
         <v>255</v>
@@ -4043,19 +4196,19 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>1564</v>
+        <v>1464</v>
       </c>
       <c r="L51" s="2">
-        <v>46230.21386574074</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M51" t="s">
         <v>260</v>
       </c>
       <c r="N51" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O51" t="s">
         <v>262</v>
@@ -4064,7 +4217,10 @@
         <v>264</v>
       </c>
       <c r="Q51" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R51" t="s">
+        <v>264</v>
       </c>
       <c r="W51" s="2">
         <v>46160</v>
@@ -4087,7 +4243,7 @@
         <v>251</v>
       </c>
       <c r="F52" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G52" t="s">
         <v>255</v>
@@ -4099,19 +4255,19 @@
         <v>1</v>
       </c>
       <c r="J52">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>1548</v>
+        <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46230.21396990741</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M52" t="s">
         <v>260</v>
       </c>
       <c r="N52" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O52" t="s">
         <v>262</v>
@@ -4120,7 +4276,10 @@
         <v>264</v>
       </c>
       <c r="Q52" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R52" t="s">
+        <v>264</v>
       </c>
       <c r="W52" s="2">
         <v>46142</v>
@@ -4143,7 +4302,7 @@
         <v>251</v>
       </c>
       <c r="F53" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G53" t="s">
         <v>255</v>
@@ -4155,19 +4314,19 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K53">
-        <v>2080</v>
+        <v>1928</v>
       </c>
       <c r="L53" s="2">
-        <v>46230.21409722222</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M53" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N53" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O53" t="s">
         <v>262</v>
@@ -4176,10 +4335,13 @@
         <v>264</v>
       </c>
       <c r="Q53" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R53" t="s">
+        <v>264</v>
       </c>
       <c r="W53" s="2">
-        <v>46168</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="54" spans="1:23">
@@ -4199,7 +4361,7 @@
         <v>251</v>
       </c>
       <c r="F54" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G54" t="s">
         <v>255</v>
@@ -4211,19 +4373,19 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>1411</v>
+        <v>1311</v>
       </c>
       <c r="L54" s="2">
-        <v>46230.21412037037</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M54" t="s">
         <v>260</v>
       </c>
       <c r="N54" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O54" t="s">
         <v>262</v>
@@ -4232,7 +4394,10 @@
         <v>264</v>
       </c>
       <c r="Q54" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R54" t="s">
+        <v>264</v>
       </c>
       <c r="W54" s="2">
         <v>46163</v>
@@ -4255,7 +4420,7 @@
         <v>251</v>
       </c>
       <c r="F55" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G55" t="s">
         <v>255</v>
@@ -4270,16 +4435,16 @@
         <v>10</v>
       </c>
       <c r="K55">
-        <v>1616</v>
+        <v>1579</v>
       </c>
       <c r="L55" s="2">
-        <v>46230.21414351852</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M55" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N55" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O55" t="s">
         <v>262</v>
@@ -4288,10 +4453,13 @@
         <v>264</v>
       </c>
       <c r="Q55" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R55" t="s">
+        <v>264</v>
       </c>
       <c r="W55" s="2">
-        <v>46168</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="56" spans="1:23">
@@ -4323,19 +4491,19 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K56">
-        <v>661</v>
+        <v>679</v>
       </c>
       <c r="L56" s="2">
-        <v>46230.2141550926</v>
+        <v>46243.50703703704</v>
       </c>
       <c r="M56" t="s">
         <v>258</v>
       </c>
       <c r="N56" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O56" t="s">
         <v>261</v>
@@ -4344,7 +4512,10 @@
         <v>263</v>
       </c>
       <c r="Q56" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R56" t="s">
+        <v>263</v>
       </c>
       <c r="W56" s="2">
         <v>46161</v>
@@ -4367,7 +4538,7 @@
         <v>251</v>
       </c>
       <c r="F57" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G57" t="s">
         <v>255</v>
@@ -4379,19 +4550,19 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="K57">
-        <v>4002</v>
+        <v>3714</v>
       </c>
       <c r="L57" s="2">
-        <v>46230.2141550926</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M57" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N57" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O57" t="s">
         <v>262</v>
@@ -4400,10 +4571,13 @@
         <v>264</v>
       </c>
       <c r="Q57" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R57" t="s">
+        <v>264</v>
       </c>
       <c r="W57" s="2">
-        <v>46164</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="58" spans="1:23">
@@ -4435,19 +4609,19 @@
         <v>1</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K58">
-        <v>982</v>
+        <v>1002</v>
       </c>
       <c r="L58" s="2">
-        <v>46230.21416666666</v>
+        <v>46243.50706018518</v>
       </c>
       <c r="M58" t="s">
         <v>258</v>
       </c>
       <c r="N58" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O58" t="s">
         <v>261</v>
@@ -4456,7 +4630,10 @@
         <v>263</v>
       </c>
       <c r="Q58" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R58" t="s">
+        <v>263</v>
       </c>
       <c r="W58" s="2">
         <v>46148</v>
@@ -4491,19 +4668,19 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K59">
-        <v>982</v>
+        <v>1002</v>
       </c>
       <c r="L59" s="2">
-        <v>46230.21416666666</v>
+        <v>46243.50706018518</v>
       </c>
       <c r="M59" t="s">
         <v>258</v>
       </c>
       <c r="N59" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O59" t="s">
         <v>261</v>
@@ -4512,7 +4689,10 @@
         <v>263</v>
       </c>
       <c r="Q59" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R59" t="s">
+        <v>263</v>
       </c>
       <c r="W59" s="2">
         <v>46168</v>
@@ -4547,19 +4727,19 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K60">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="L60" s="2">
-        <v>46230.21416666666</v>
+        <v>46243.50707175926</v>
       </c>
       <c r="M60" t="s">
         <v>258</v>
       </c>
       <c r="N60" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O60" t="s">
         <v>261</v>
@@ -4568,7 +4748,10 @@
         <v>263</v>
       </c>
       <c r="Q60" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R60" t="s">
+        <v>263</v>
       </c>
       <c r="W60" s="2">
         <v>46164</v>
@@ -4603,19 +4786,19 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K61">
-        <v>1020</v>
+        <v>1040</v>
       </c>
       <c r="L61" s="2">
-        <v>46230.21416666666</v>
+        <v>46243.50708333333</v>
       </c>
       <c r="M61" t="s">
         <v>258</v>
       </c>
       <c r="N61" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O61" t="s">
         <v>261</v>
@@ -4624,7 +4807,10 @@
         <v>263</v>
       </c>
       <c r="Q61" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R61" t="s">
+        <v>263</v>
       </c>
       <c r="W61" s="2">
         <v>46168</v>
@@ -4647,7 +4833,7 @@
         <v>251</v>
       </c>
       <c r="F62" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G62" t="s">
         <v>255</v>
@@ -4659,19 +4845,19 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K62">
-        <v>1720</v>
+        <v>1628</v>
       </c>
       <c r="L62" s="2">
-        <v>46230.21416666666</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M62" t="s">
         <v>260</v>
       </c>
       <c r="N62" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O62" t="s">
         <v>262</v>
@@ -4680,10 +4866,13 @@
         <v>264</v>
       </c>
       <c r="Q62" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R62" t="s">
+        <v>264</v>
       </c>
       <c r="W62" s="2">
-        <v>46164</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="63" spans="1:23">
@@ -4715,19 +4904,19 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K63">
-        <v>2005</v>
+        <v>2065</v>
       </c>
       <c r="L63" s="2">
-        <v>46230.21417824074</v>
+        <v>46243.50712962963</v>
       </c>
       <c r="M63" t="s">
         <v>258</v>
       </c>
       <c r="N63" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O63" t="s">
         <v>261</v>
@@ -4736,7 +4925,10 @@
         <v>263</v>
       </c>
       <c r="Q63" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R63" t="s">
+        <v>263</v>
       </c>
       <c r="W63" s="2">
         <v>46164</v>
@@ -4771,28 +4963,31 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K64">
-        <v>958</v>
+        <v>1000</v>
       </c>
       <c r="L64" s="2">
-        <v>46230.21417824074</v>
+        <v>46243.50715277778</v>
       </c>
       <c r="M64" t="s">
         <v>258</v>
       </c>
       <c r="N64" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O64" t="s">
         <v>261</v>
       </c>
       <c r="P64" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q64" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R64" t="s">
+        <v>264</v>
       </c>
       <c r="W64" s="2">
         <v>46168</v>
@@ -4815,7 +5010,7 @@
         <v>251</v>
       </c>
       <c r="F65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G65" t="s">
         <v>255</v>
@@ -4827,19 +5022,19 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K65">
-        <v>3303</v>
+        <v>3107</v>
       </c>
       <c r="L65" s="2">
-        <v>46230.21429398148</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M65" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O65" t="s">
         <v>262</v>
@@ -4848,10 +5043,13 @@
         <v>264</v>
       </c>
       <c r="Q65" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R65" t="s">
+        <v>264</v>
       </c>
       <c r="W65" s="2">
-        <v>46168</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="66" spans="1:23">
@@ -4871,7 +5069,7 @@
         <v>251</v>
       </c>
       <c r="F66" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G66" t="s">
         <v>255</v>
@@ -4883,19 +5081,19 @@
         <v>1</v>
       </c>
       <c r="J66">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K66">
-        <v>3337</v>
+        <v>3037</v>
       </c>
       <c r="L66" s="2">
-        <v>46230.2144212963</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M66" t="s">
         <v>260</v>
       </c>
       <c r="N66" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O66" t="s">
         <v>262</v>
@@ -4904,7 +5102,10 @@
         <v>264</v>
       </c>
       <c r="Q66" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R66" t="s">
+        <v>264</v>
       </c>
       <c r="W66" s="2">
         <v>46160</v>
@@ -4927,7 +5128,7 @@
         <v>251</v>
       </c>
       <c r="F67" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G67" t="s">
         <v>255</v>
@@ -4939,19 +5140,19 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K67">
-        <v>1682</v>
+        <v>1603</v>
       </c>
       <c r="L67" s="2">
-        <v>46230.21443287037</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M67" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N67" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O67" t="s">
         <v>262</v>
@@ -4960,10 +5161,13 @@
         <v>264</v>
       </c>
       <c r="Q67" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R67" t="s">
+        <v>264</v>
       </c>
       <c r="W67" s="2">
-        <v>46168</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="68" spans="1:23">
@@ -4983,7 +5187,7 @@
         <v>251</v>
       </c>
       <c r="F68" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G68" t="s">
         <v>255</v>
@@ -4995,19 +5199,19 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="K68">
-        <v>3317</v>
+        <v>3054</v>
       </c>
       <c r="L68" s="2">
-        <v>46230.21457175926</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M68" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N68" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O68" t="s">
         <v>262</v>
@@ -5016,10 +5220,13 @@
         <v>264</v>
       </c>
       <c r="Q68" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R68" t="s">
+        <v>264</v>
       </c>
       <c r="W68" s="2">
-        <v>46168</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="69" spans="1:23">
@@ -5039,7 +5246,7 @@
         <v>251</v>
       </c>
       <c r="F69" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G69" t="s">
         <v>255</v>
@@ -5051,19 +5258,19 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K69">
-        <v>3346</v>
+        <v>3046</v>
       </c>
       <c r="L69" s="2">
-        <v>46230.21471064815</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M69" t="s">
         <v>260</v>
       </c>
       <c r="N69" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O69" t="s">
         <v>262</v>
@@ -5072,7 +5279,10 @@
         <v>264</v>
       </c>
       <c r="Q69" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R69" t="s">
+        <v>264</v>
       </c>
       <c r="W69" s="2">
         <v>46168</v>
@@ -5095,7 +5305,7 @@
         <v>251</v>
       </c>
       <c r="F70" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G70" t="s">
         <v>255</v>
@@ -5107,19 +5317,19 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K70">
-        <v>2104</v>
+        <v>1981</v>
       </c>
       <c r="L70" s="2">
-        <v>46230.21472222222</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M70" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N70" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O70" t="s">
         <v>262</v>
@@ -5128,10 +5338,13 @@
         <v>264</v>
       </c>
       <c r="Q70" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R70" t="s">
+        <v>264</v>
       </c>
       <c r="W70" s="2">
-        <v>46168</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="71" spans="1:23">
@@ -5151,7 +5364,7 @@
         <v>251</v>
       </c>
       <c r="F71" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G71" t="s">
         <v>255</v>
@@ -5163,19 +5376,19 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K71">
-        <v>2085</v>
+        <v>1950</v>
       </c>
       <c r="L71" s="2">
-        <v>46230.21474537037</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M71" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N71" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O71" t="s">
         <v>262</v>
@@ -5184,10 +5397,13 @@
         <v>264</v>
       </c>
       <c r="Q71" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R71" t="s">
+        <v>264</v>
       </c>
       <c r="W71" s="2">
-        <v>46168</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="72" spans="1:23">
@@ -5219,19 +5435,19 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K72">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="L72" s="2">
-        <v>46230.21474537037</v>
+        <v>46243.50783564815</v>
       </c>
       <c r="M72" t="s">
         <v>258</v>
       </c>
       <c r="N72" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O72" t="s">
         <v>261</v>
@@ -5240,7 +5456,10 @@
         <v>263</v>
       </c>
       <c r="Q72" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R72" t="s">
+        <v>263</v>
       </c>
       <c r="W72" s="2">
         <v>46164</v>
@@ -5263,7 +5482,7 @@
         <v>251</v>
       </c>
       <c r="F73" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G73" t="s">
         <v>255</v>
@@ -5275,19 +5494,19 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K73">
-        <v>1385</v>
+        <v>1273</v>
       </c>
       <c r="L73" s="2">
-        <v>46230.21476851852</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M73" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="N73" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O73" t="s">
         <v>262</v>
@@ -5296,10 +5515,13 @@
         <v>264</v>
       </c>
       <c r="Q73" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R73" t="s">
+        <v>264</v>
       </c>
       <c r="W73" s="2">
-        <v>46164</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="74" spans="1:23">
@@ -5319,7 +5541,7 @@
         <v>251</v>
       </c>
       <c r="F74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G74" t="s">
         <v>255</v>
@@ -5331,19 +5553,19 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>1569</v>
+        <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46230.21479166667</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M74" t="s">
         <v>260</v>
       </c>
       <c r="N74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O74" t="s">
         <v>262</v>
@@ -5352,7 +5574,10 @@
         <v>264</v>
       </c>
       <c r="Q74" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R74" t="s">
+        <v>264</v>
       </c>
       <c r="W74" s="2">
         <v>46185</v>
@@ -5375,7 +5600,7 @@
         <v>251</v>
       </c>
       <c r="F75" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G75" t="s">
         <v>255</v>
@@ -5387,19 +5612,19 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K75">
-        <v>1600</v>
+        <v>1480</v>
       </c>
       <c r="L75" s="2">
-        <v>46230.21480324074</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M75" t="s">
         <v>260</v>
       </c>
       <c r="N75" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O75" t="s">
         <v>262</v>
@@ -5408,7 +5633,10 @@
         <v>264</v>
       </c>
       <c r="Q75" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R75" t="s">
+        <v>264</v>
       </c>
       <c r="W75" s="2">
         <v>46149</v>
@@ -5431,7 +5659,7 @@
         <v>251</v>
       </c>
       <c r="F76" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G76" t="s">
         <v>255</v>
@@ -5443,19 +5671,19 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K76">
-        <v>1644</v>
+        <v>1524</v>
       </c>
       <c r="L76" s="2">
-        <v>46230.21482638889</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M76" t="s">
         <v>260</v>
       </c>
       <c r="N76" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O76" t="s">
         <v>262</v>
@@ -5464,7 +5692,10 @@
         <v>264</v>
       </c>
       <c r="Q76" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R76" t="s">
+        <v>264</v>
       </c>
       <c r="W76" s="2">
         <v>46149</v>
@@ -5487,7 +5718,7 @@
         <v>251</v>
       </c>
       <c r="F77" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G77" t="s">
         <v>255</v>
@@ -5499,19 +5730,19 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K77">
-        <v>1657</v>
+        <v>1537</v>
       </c>
       <c r="L77" s="2">
-        <v>46230.21484953703</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M77" t="s">
         <v>260</v>
       </c>
       <c r="N77" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O77" t="s">
         <v>262</v>
@@ -5520,7 +5751,10 @@
         <v>264</v>
       </c>
       <c r="Q77" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R77" t="s">
+        <v>264</v>
       </c>
       <c r="W77" s="2">
         <v>46168</v>
@@ -5543,7 +5777,7 @@
         <v>251</v>
       </c>
       <c r="F78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G78" t="s">
         <v>255</v>
@@ -5555,19 +5789,19 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K78">
-        <v>1657</v>
+        <v>1537</v>
       </c>
       <c r="L78" s="2">
-        <v>46230.21487268519</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M78" t="s">
         <v>260</v>
       </c>
       <c r="N78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O78" t="s">
         <v>262</v>
@@ -5576,7 +5810,10 @@
         <v>264</v>
       </c>
       <c r="Q78" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R78" t="s">
+        <v>264</v>
       </c>
       <c r="W78" s="2">
         <v>46160</v>
@@ -5599,7 +5836,7 @@
         <v>251</v>
       </c>
       <c r="F79" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G79" t="s">
         <v>255</v>
@@ -5611,19 +5848,19 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K79">
-        <v>1670</v>
+        <v>1550</v>
       </c>
       <c r="L79" s="2">
-        <v>46230.21489583333</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M79" t="s">
         <v>260</v>
       </c>
       <c r="N79" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O79" t="s">
         <v>262</v>
@@ -5632,7 +5869,10 @@
         <v>264</v>
       </c>
       <c r="Q79" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R79" t="s">
+        <v>264</v>
       </c>
       <c r="W79" s="2">
         <v>46168</v>
@@ -5655,7 +5895,7 @@
         <v>251</v>
       </c>
       <c r="F80" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G80" t="s">
         <v>255</v>
@@ -5667,19 +5907,19 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K80">
-        <v>1441</v>
+        <v>1345</v>
       </c>
       <c r="L80" s="2">
-        <v>46230.2149074074</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M80" t="s">
         <v>260</v>
       </c>
       <c r="N80" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O80" t="s">
         <v>262</v>
@@ -5688,7 +5928,10 @@
         <v>264</v>
       </c>
       <c r="Q80" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R80" t="s">
+        <v>264</v>
       </c>
       <c r="W80" s="2">
         <v>46164</v>
@@ -5711,7 +5954,7 @@
         <v>251</v>
       </c>
       <c r="F81" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G81" t="s">
         <v>255</v>
@@ -5723,19 +5966,19 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K81">
-        <v>3891</v>
+        <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46230.21493055556</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M81" t="s">
         <v>260</v>
       </c>
       <c r="N81" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O81" t="s">
         <v>262</v>
@@ -5744,7 +5987,10 @@
         <v>264</v>
       </c>
       <c r="Q81" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R81" t="s">
+        <v>264</v>
       </c>
       <c r="W81" s="2">
         <v>46160</v>
@@ -5779,19 +6025,19 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K82">
-        <v>2077</v>
+        <v>2137</v>
       </c>
       <c r="L82" s="2">
-        <v>46230.21493055556</v>
+        <v>46243.50800925926</v>
       </c>
       <c r="M82" t="s">
         <v>258</v>
       </c>
       <c r="N82" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O82" t="s">
         <v>261</v>
@@ -5800,7 +6046,10 @@
         <v>263</v>
       </c>
       <c r="Q82" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R82" t="s">
+        <v>263</v>
       </c>
       <c r="W82" s="2">
         <v>46161</v>
@@ -5835,19 +6084,19 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K83">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="L83" s="2">
-        <v>46230.21493055556</v>
+        <v>46243.50802083333</v>
       </c>
       <c r="M83" t="s">
         <v>258</v>
       </c>
       <c r="N83" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O83" t="s">
         <v>261</v>
@@ -5856,7 +6105,10 @@
         <v>263</v>
       </c>
       <c r="Q83" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R83" t="s">
+        <v>263</v>
       </c>
       <c r="W83" s="2">
         <v>46168</v>
@@ -5891,19 +6143,19 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L84" s="2">
-        <v>46230.21493055556</v>
+        <v>46243.50803240741</v>
       </c>
       <c r="M84" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N84" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O84" t="s">
         <v>261</v>
@@ -5912,7 +6164,10 @@
         <v>263</v>
       </c>
       <c r="Q84" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R84" t="s">
+        <v>263</v>
       </c>
       <c r="W84" s="2">
         <v>46164</v>
@@ -5947,19 +6202,19 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K85">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="L85" s="2">
-        <v>46230.21493055556</v>
+        <v>46243.50804398148</v>
       </c>
       <c r="M85" t="s">
         <v>258</v>
       </c>
       <c r="N85" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O85" t="s">
         <v>261</v>
@@ -5968,7 +6223,10 @@
         <v>263</v>
       </c>
       <c r="Q85" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R85" t="s">
+        <v>263</v>
       </c>
       <c r="W85" s="2">
         <v>46168</v>
@@ -5991,7 +6249,7 @@
         <v>252</v>
       </c>
       <c r="F86" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G86" t="s">
         <v>255</v>
@@ -6003,19 +6261,19 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K86">
-        <v>672</v>
+        <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46230.2149537037</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M86" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N86" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O86" t="s">
         <v>262</v>
@@ -6024,7 +6282,10 @@
         <v>264</v>
       </c>
       <c r="Q86" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R86" t="s">
+        <v>264</v>
       </c>
       <c r="W86" s="2">
         <v>46164</v>
@@ -6047,7 +6308,7 @@
         <v>252</v>
       </c>
       <c r="F87" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G87" t="s">
         <v>255</v>
@@ -6059,19 +6320,19 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K87">
-        <v>3907</v>
+        <v>3607</v>
       </c>
       <c r="L87" s="2">
-        <v>46230.21497685185</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M87" t="s">
         <v>260</v>
       </c>
       <c r="N87" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O87" t="s">
         <v>262</v>
@@ -6080,7 +6341,10 @@
         <v>264</v>
       </c>
       <c r="Q87" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R87" t="s">
+        <v>264</v>
       </c>
       <c r="W87" s="2">
         <v>46168</v>
@@ -6103,7 +6367,7 @@
         <v>252</v>
       </c>
       <c r="F88" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G88" t="s">
         <v>256</v>
@@ -6115,19 +6379,19 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K88">
-        <v>3851</v>
+        <v>3551</v>
       </c>
       <c r="L88" s="2">
-        <v>46230.21502314815</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M88" t="s">
         <v>260</v>
       </c>
       <c r="N88" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O88" t="s">
         <v>262</v>
@@ -6136,7 +6400,10 @@
         <v>264</v>
       </c>
       <c r="Q88" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R88" t="s">
+        <v>264</v>
       </c>
       <c r="W88" s="2">
         <v>46163</v>
@@ -6159,7 +6426,7 @@
         <v>252</v>
       </c>
       <c r="F89" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G89" t="s">
         <v>255</v>
@@ -6168,7 +6435,7 @@
         <v>5</v>
       </c>
       <c r="N89" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O89" t="s">
         <v>261</v>
@@ -6177,7 +6444,10 @@
         <v>263</v>
       </c>
       <c r="Q89" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R89" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="90" spans="1:23">
@@ -6197,7 +6467,7 @@
         <v>252</v>
       </c>
       <c r="F90" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G90" t="s">
         <v>255</v>
@@ -6209,19 +6479,19 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46230.2150462963</v>
+        <v>46246.0112037037</v>
       </c>
       <c r="M90" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N90" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O90" t="s">
         <v>262</v>
@@ -6230,7 +6500,10 @@
         <v>264</v>
       </c>
       <c r="Q90" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R90" t="s">
+        <v>264</v>
       </c>
       <c r="W90" s="2">
         <v>46154</v>
@@ -6253,7 +6526,7 @@
         <v>252</v>
       </c>
       <c r="F91" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G91" t="s">
         <v>255</v>
@@ -6262,7 +6535,7 @@
         <v>5</v>
       </c>
       <c r="N91" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O91" t="s">
         <v>262</v>
@@ -6271,7 +6544,10 @@
         <v>264</v>
       </c>
       <c r="Q91" t="s">
-        <v>262</v>
+        <v>266</v>
+      </c>
+      <c r="R91" t="s">
+        <v>264</v>
       </c>
       <c r="W91" s="2">
         <v>46154</v>
@@ -6306,19 +6582,19 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L92" s="2">
-        <v>46230.2150462963</v>
+        <v>46243.50813657408</v>
       </c>
       <c r="M92" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O92" t="s">
         <v>261</v>
@@ -6327,7 +6603,10 @@
         <v>263</v>
       </c>
       <c r="Q92" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="R92" t="s">
+        <v>263</v>
       </c>
       <c r="W92" s="2">
         <v>46164</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="272">
   <si>
     <t>site_name</t>
   </si>
@@ -88,6 +88,15 @@
     <t>NO</t>
   </si>
   <si>
+    <t>crawl_status</t>
+  </si>
+  <si>
+    <t>content_status</t>
+  </si>
+  <si>
+    <t>status_detail</t>
+  </si>
+  <si>
     <t>68.Brazil Receita</t>
   </si>
   <si>
@@ -796,7 +805,7 @@
     <t>CHECK</t>
   </si>
   <si>
-    <t>FAIL</t>
+    <t>NO_NEW</t>
   </si>
   <si>
     <t>STEP2-3</t>
@@ -815,6 +824,12 @@
   </si>
   <si>
     <t>CORE</t>
+  </si>
+  <si>
+    <t>NEW</t>
+  </si>
+  <si>
+    <t>PRIMARY_PARSER</t>
   </si>
 </sst>
 </file>
@@ -1163,10 +1178,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:AA92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1239,28 +1254,37 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -1278,22 +1302,22 @@
         <v>46243.50512731481</v>
       </c>
       <c r="M2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W2" s="2">
         <v>46155</v>
@@ -1302,27 +1326,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:27">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -1340,22 +1364,22 @@
         <v>46243.50516203704</v>
       </c>
       <c r="M3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W3" s="2">
         <v>46087</v>
@@ -1364,27 +1388,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:27">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1402,22 +1426,22 @@
         <v>46243.50517361111</v>
       </c>
       <c r="M4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W4" s="2">
         <v>46168</v>
@@ -1426,27 +1450,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:27">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -1464,22 +1488,22 @@
         <v>46243.50518518518</v>
       </c>
       <c r="M5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N5" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W5" s="2">
         <v>46161</v>
@@ -1488,27 +1512,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:27">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G6" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -1523,25 +1547,25 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W6" s="2">
         <v>46168</v>
@@ -1549,28 +1573,37 @@
       <c r="X6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:24">
+      <c r="Y6" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -1588,22 +1621,22 @@
         <v>46243.50520833334</v>
       </c>
       <c r="M7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W7" s="2">
         <v>46164</v>
@@ -1612,27 +1645,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:27">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E8" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F8" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G8" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -1650,22 +1683,22 @@
         <v>46243.50521990741</v>
       </c>
       <c r="M8" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N8" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O8" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P8" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R8" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W8" s="2">
         <v>46155</v>
@@ -1674,27 +1707,27 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:27">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D9" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E9" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F9" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -1712,22 +1745,22 @@
         <v>46243.50527777777</v>
       </c>
       <c r="M9" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N9" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O9" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q9" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W9" s="2">
         <v>46045</v>
@@ -1736,27 +1769,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:27">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E10" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F10" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G10" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H10">
         <v>5</v>
@@ -1774,22 +1807,22 @@
         <v>46243.50550925926</v>
       </c>
       <c r="M10" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N10" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O10" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P10" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q10" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R10" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W10" s="2">
         <v>46045</v>
@@ -1798,27 +1831,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:27">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H11">
         <v>5</v>
@@ -1836,22 +1869,22 @@
         <v>46243.50556712963</v>
       </c>
       <c r="M11" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P11" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q11" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R11" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W11" s="2">
         <v>46129</v>
@@ -1860,27 +1893,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:27">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D12" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F12" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1898,22 +1931,22 @@
         <v>46243.50557870371</v>
       </c>
       <c r="M12" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N12" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O12" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P12" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q12" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R12" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W12" s="2">
         <v>46164</v>
@@ -1922,27 +1955,27 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:27">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -1954,57 +1987,66 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="L13" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M13" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O13" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q13" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W13" s="2">
-        <v>46168</v>
+        <v>46252</v>
       </c>
       <c r="X13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:24">
+      <c r="Y13" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D14" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G14" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -2019,51 +2061,60 @@
         <v>3475</v>
       </c>
       <c r="L14" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M14" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P14" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q14" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R14" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W14" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="Y14" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D15" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E15" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F15" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G15" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H15">
         <v>5</v>
@@ -2078,51 +2129,60 @@
         <v>3475</v>
       </c>
       <c r="L15" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M15" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N15" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O15" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P15" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q15" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R15" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W15" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="16" spans="1:24">
+      <c r="Y15" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D16" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F16" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G16" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H16">
         <v>5</v>
@@ -2137,51 +2197,60 @@
         <v>3475</v>
       </c>
       <c r="L16" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M16" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N16" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O16" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P16" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q16" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R16" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W16" s="2">
         <v>46164</v>
       </c>
-    </row>
-    <row r="17" spans="1:23">
+      <c r="Y16" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C17" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E17" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F17" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G17" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H17">
         <v>5</v>
@@ -2199,48 +2268,48 @@
         <v>46243.50569444444</v>
       </c>
       <c r="M17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N17" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P17" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q17" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R17" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W17" s="2">
         <v>46113</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:27">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C18" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D18" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E18" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F18" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G18" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -2249,57 +2318,66 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>3599</v>
+        <v>3606</v>
       </c>
       <c r="L18" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M18" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="N18" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O18" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P18" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q18" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R18" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W18" s="2">
-        <v>46243</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
+        <v>46250</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D19" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E19" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F19" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G19" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -2317,48 +2395,48 @@
         <v>46243.50572916667</v>
       </c>
       <c r="M19" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N19" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P19" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q19" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R19" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W19" s="2">
         <v>46163</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:27">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D20" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E20" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F20" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G20" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -2376,48 +2454,48 @@
         <v>46243.50575231481</v>
       </c>
       <c r="M20" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N20" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O20" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P20" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q20" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R20" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W20" s="2">
         <v>46165</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:27">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D21" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E21" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F21" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G21" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -2435,48 +2513,48 @@
         <v>46243.50576388889</v>
       </c>
       <c r="M21" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N21" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O21" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P21" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q21" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R21" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W21" s="2">
         <v>46166</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:27">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C22" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D22" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E22" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F22" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G22" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H22">
         <v>5</v>
@@ -2491,51 +2569,60 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M22" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N22" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P22" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q22" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R22" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W22" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="Y22" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C23" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D23" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E23" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F23" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G23" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H23">
         <v>5</v>
@@ -2550,51 +2637,60 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M23" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N23" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O23" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P23" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q23" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R23" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W23" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="24" spans="1:23">
+      <c r="Y23" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D24" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E24" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G24" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -2609,51 +2705,60 @@
         <v>125</v>
       </c>
       <c r="L24" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M24" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O24" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P24" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q24" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R24" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W24" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="25" spans="1:23">
+      <c r="Y24" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C25" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D25" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E25" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F25" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G25" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H25">
         <v>5</v>
@@ -2668,51 +2773,60 @@
         <v>125</v>
       </c>
       <c r="L25" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M25" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N25" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P25" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q25" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R25" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W25" s="2">
         <v>46167</v>
       </c>
-    </row>
-    <row r="26" spans="1:23">
+      <c r="Y25" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C26" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D26" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E26" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F26" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G26" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -2727,51 +2841,60 @@
         <v>125</v>
       </c>
       <c r="L26" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M26" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O26" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P26" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q26" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R26" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W26" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="27" spans="1:23">
+      <c r="Y26" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C27" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D27" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E27" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F27" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G27" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -2789,48 +2912,48 @@
         <v>46243.50589120371</v>
       </c>
       <c r="M27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N27" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O27" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P27" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q27" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R27" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W27" s="2">
         <v>46172</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:27">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C28" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D28" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E28" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F28" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G28" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H28">
         <v>5</v>
@@ -2848,48 +2971,48 @@
         <v>46243.50591435185</v>
       </c>
       <c r="M28" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N28" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O28" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P28" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q28" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R28" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W28" s="2">
         <v>46164</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:27">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D29" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E29" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F29" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G29" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -2907,48 +3030,48 @@
         <v>46243.50592592593</v>
       </c>
       <c r="M29" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N29" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O29" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P29" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q29" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R29" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W29" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:27">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C30" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D30" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E30" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F30" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G30" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -2966,48 +3089,48 @@
         <v>46243.50594907408</v>
       </c>
       <c r="M30" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N30" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O30" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P30" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q30" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R30" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W30" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:27">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C31" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D31" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E31" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F31" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G31" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H31">
         <v>5</v>
@@ -3025,48 +3148,48 @@
         <v>46243.50596064814</v>
       </c>
       <c r="M31" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N31" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O31" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q31" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W31" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:27">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C32" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D32" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E32" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F32" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G32" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H32">
         <v>5</v>
@@ -3075,57 +3198,66 @@
         <v>1</v>
       </c>
       <c r="J32">
+        <v>98</v>
+      </c>
+      <c r="K32">
+        <v>6988</v>
+      </c>
+      <c r="L32" s="2">
+        <v>46253.25208333333</v>
+      </c>
+      <c r="M32" t="s">
+        <v>261</v>
+      </c>
+      <c r="N32" t="s">
+        <v>256</v>
+      </c>
+      <c r="O32" t="s">
+        <v>265</v>
+      </c>
+      <c r="P32" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>269</v>
+      </c>
+      <c r="R32" t="s">
+        <v>267</v>
+      </c>
+      <c r="W32" s="2">
+        <v>46253</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27">
+      <c r="A33" t="s">
         <v>58</v>
       </c>
-      <c r="K32">
-        <v>5921</v>
-      </c>
-      <c r="L32" s="2">
-        <v>46246.0112037037</v>
-      </c>
-      <c r="M32" t="s">
-        <v>258</v>
-      </c>
-      <c r="N32" t="s">
-        <v>253</v>
-      </c>
-      <c r="O32" t="s">
-        <v>262</v>
-      </c>
-      <c r="P32" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>266</v>
-      </c>
-      <c r="R32" t="s">
-        <v>264</v>
-      </c>
-      <c r="W32" s="2">
-        <v>46246</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23">
-      <c r="A33" t="s">
-        <v>55</v>
-      </c>
       <c r="B33" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C33" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D33" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E33" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F33" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G33" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H33">
         <v>5</v>
@@ -3143,48 +3275,48 @@
         <v>46243.50614583334</v>
       </c>
       <c r="M33" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N33" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O33" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P33" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q33" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R33" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W33" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:27">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C34" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D34" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E34" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F34" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G34" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -3202,48 +3334,48 @@
         <v>46243.50615740741</v>
       </c>
       <c r="M34" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N34" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O34" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P34" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q34" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R34" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W34" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:27">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C35" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D35" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E35" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F35" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G35" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -3258,51 +3390,60 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M35" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N35" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O35" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P35" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q35" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R35" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W35" s="2">
         <v>46157</v>
       </c>
-    </row>
-    <row r="36" spans="1:23">
+      <c r="Y35" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27">
       <c r="A36" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D36" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E36" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G36" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H36">
         <v>5</v>
@@ -3317,51 +3458,60 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M36" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N36" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O36" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P36" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q36" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R36" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W36" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="37" spans="1:23">
+      <c r="Y36" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C37" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D37" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E37" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F37" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G37" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H37">
         <v>5</v>
@@ -3376,51 +3526,60 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M37" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N37" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O37" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P37" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q37" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R37" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W37" s="2">
         <v>46132</v>
       </c>
-    </row>
-    <row r="38" spans="1:23">
+      <c r="Y37" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C38" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D38" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E38" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F38" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G38" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H38">
         <v>5</v>
@@ -3435,51 +3594,60 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M38" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N38" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O38" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P38" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q38" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R38" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W38" s="2">
         <v>46113</v>
       </c>
-    </row>
-    <row r="39" spans="1:23">
+      <c r="Y38" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C39" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D39" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E39" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F39" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G39" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H39">
         <v>5</v>
@@ -3494,51 +3662,60 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M39" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N39" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O39" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P39" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q39" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R39" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W39" s="2">
         <v>46140</v>
       </c>
-    </row>
-    <row r="40" spans="1:23">
+      <c r="Y39" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C40" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D40" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E40" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F40" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G40" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H40">
         <v>5</v>
@@ -3553,51 +3730,60 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M40" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N40" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O40" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P40" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q40" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R40" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W40" s="2">
         <v>46024</v>
       </c>
-    </row>
-    <row r="41" spans="1:23">
+      <c r="Y40" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C41" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D41" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E41" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F41" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G41" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -3612,51 +3798,60 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M41" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N41" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O41" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P41" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q41" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R41" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W41" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="42" spans="1:23">
+      <c r="Y41" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C42" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D42" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E42" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F42" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G42" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H42">
         <v>5</v>
@@ -3671,51 +3866,60 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M42" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N42" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O42" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P42" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q42" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R42" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W42" s="2">
         <v>46164</v>
       </c>
-    </row>
-    <row r="43" spans="1:23">
+      <c r="Y42" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C43" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D43" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E43" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F43" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G43" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H43">
         <v>5</v>
@@ -3730,51 +3934,60 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M43" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N43" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O43" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P43" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q43" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R43" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W43" s="2">
         <v>46112</v>
       </c>
-    </row>
-    <row r="44" spans="1:23">
+      <c r="Y43" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C44" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D44" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E44" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F44" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G44" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H44">
         <v>5</v>
@@ -3792,48 +4005,48 @@
         <v>46243.50630787037</v>
       </c>
       <c r="M44" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N44" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O44" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P44" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q44" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R44" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W44" s="2">
         <v>46171</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:27">
       <c r="A45" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D45" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E45" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F45" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G45" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H45">
         <v>5</v>
@@ -3842,57 +4055,66 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K45">
-        <v>2873</v>
+        <v>2965</v>
       </c>
       <c r="L45" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M45" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N45" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O45" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P45" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q45" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R45" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W45" s="2">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23">
+        <v>46252</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27">
       <c r="A46" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C46" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D46" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E46" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F46" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G46" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H46">
         <v>5</v>
@@ -3901,57 +4123,66 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K46">
-        <v>3157</v>
+        <v>3411</v>
       </c>
       <c r="L46" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M46" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N46" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O46" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P46" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q46" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R46" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W46" s="2">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23">
+        <v>46252</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27">
       <c r="A47" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C47" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D47" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F47" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G47" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H47">
         <v>5</v>
@@ -3960,57 +4191,66 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K47">
-        <v>3188</v>
+        <v>3398</v>
       </c>
       <c r="L47" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M47" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N47" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O47" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P47" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q47" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R47" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W47" s="2">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23">
+        <v>46252</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D48" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E48" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F48" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G48" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H48">
         <v>5</v>
@@ -4025,51 +4265,60 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M48" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N48" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O48" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P48" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q48" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R48" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W48" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="49" spans="1:23">
+      <c r="Y48" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D49" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E49" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F49" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G49" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H49">
         <v>5</v>
@@ -4081,113 +4330,131 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="L49" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M49" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N49" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O49" t="s">
+        <v>265</v>
+      </c>
+      <c r="P49" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>269</v>
+      </c>
+      <c r="R49" t="s">
+        <v>267</v>
+      </c>
+      <c r="W49" s="2">
+        <v>46246</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27">
+      <c r="A50" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C50" t="s">
+        <v>217</v>
+      </c>
+      <c r="D50" t="s">
+        <v>236</v>
+      </c>
+      <c r="E50" t="s">
+        <v>254</v>
+      </c>
+      <c r="F50" t="s">
+        <v>256</v>
+      </c>
+      <c r="G50" t="s">
+        <v>258</v>
+      </c>
+      <c r="H50">
+        <v>5</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>1516</v>
+      </c>
+      <c r="L50" s="2">
+        <v>46253.25208333333</v>
+      </c>
+      <c r="M50" t="s">
         <v>262</v>
       </c>
-      <c r="P49" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>266</v>
-      </c>
-      <c r="R49" t="s">
-        <v>264</v>
-      </c>
-      <c r="W49" s="2">
-        <v>46241</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23">
-      <c r="A50" t="s">
-        <v>72</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C50" t="s">
-        <v>214</v>
-      </c>
-      <c r="D50" t="s">
-        <v>233</v>
-      </c>
-      <c r="E50" t="s">
-        <v>251</v>
-      </c>
-      <c r="F50" t="s">
-        <v>253</v>
-      </c>
-      <c r="G50" t="s">
-        <v>255</v>
-      </c>
-      <c r="H50">
-        <v>5</v>
-      </c>
-      <c r="I50">
-        <v>1</v>
-      </c>
-      <c r="J50">
-        <v>1</v>
-      </c>
-      <c r="K50">
-        <v>1475</v>
-      </c>
-      <c r="L50" s="2">
-        <v>46246.0112037037</v>
-      </c>
-      <c r="M50" t="s">
-        <v>259</v>
-      </c>
       <c r="N50" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P50" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q50" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R50" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W50" s="2">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23">
+        <v>46252</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C51" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D51" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E51" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F51" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G51" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H51">
         <v>5</v>
@@ -4199,54 +4466,63 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="L51" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M51" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N51" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O51" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P51" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q51" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R51" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W51" s="2">
-        <v>46160</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23">
+        <v>46247</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C52" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D52" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E52" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F52" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G52" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H52">
         <v>5</v>
@@ -4261,51 +4537,60 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M52" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N52" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O52" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P52" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q52" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R52" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W52" s="2">
         <v>46142</v>
       </c>
-    </row>
-    <row r="53" spans="1:23">
+      <c r="Y52" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27">
       <c r="A53" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C53" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D53" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E53" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F53" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G53" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H53">
         <v>5</v>
@@ -4314,57 +4599,66 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>1928</v>
+        <v>1938</v>
       </c>
       <c r="L53" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M53" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="N53" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O53" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P53" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q53" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R53" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W53" s="2">
         <v>46244</v>
       </c>
-    </row>
-    <row r="54" spans="1:23">
+      <c r="Y53" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C54" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D54" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E54" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F54" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G54" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H54">
         <v>5</v>
@@ -4376,54 +4670,63 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="L54" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M54" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N54" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O54" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P54" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q54" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R54" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W54" s="2">
-        <v>46163</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23">
+        <v>46246</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C55" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D55" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E55" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F55" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G55" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H55">
         <v>5</v>
@@ -4435,54 +4738,63 @@
         <v>10</v>
       </c>
       <c r="K55">
-        <v>1579</v>
+        <v>1718</v>
       </c>
       <c r="L55" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M55" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N55" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O55" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P55" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q55" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R55" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W55" s="2">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23">
+        <v>46252</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C56" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D56" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E56" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F56" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G56" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H56">
         <v>5</v>
@@ -4500,48 +4812,48 @@
         <v>46243.50703703704</v>
       </c>
       <c r="M56" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N56" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O56" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P56" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q56" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R56" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W56" s="2">
         <v>46161</v>
       </c>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:27">
       <c r="A57" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C57" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D57" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E57" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F57" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G57" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H57">
         <v>5</v>
@@ -4550,57 +4862,66 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>3714</v>
+        <v>3762</v>
       </c>
       <c r="L57" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M57" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="N57" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O57" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P57" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q57" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R57" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W57" s="2">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="58" spans="1:23">
+        <v>46252</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27">
       <c r="A58" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C58" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D58" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E58" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F58" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G58" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H58">
         <v>5</v>
@@ -4618,48 +4939,48 @@
         <v>46243.50706018518</v>
       </c>
       <c r="M58" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N58" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O58" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P58" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q58" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R58" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W58" s="2">
         <v>46148</v>
       </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:27">
       <c r="A59" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C59" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D59" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E59" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F59" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G59" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -4677,48 +4998,48 @@
         <v>46243.50706018518</v>
       </c>
       <c r="M59" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N59" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O59" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P59" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q59" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R59" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W59" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:27">
       <c r="A60" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D60" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E60" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F60" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G60" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H60">
         <v>5</v>
@@ -4736,48 +5057,48 @@
         <v>46243.50707175926</v>
       </c>
       <c r="M60" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N60" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O60" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P60" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q60" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R60" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W60" s="2">
         <v>46164</v>
       </c>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:27">
       <c r="A61" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C61" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D61" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E61" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F61" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G61" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H61">
         <v>5</v>
@@ -4795,48 +5116,48 @@
         <v>46243.50708333333</v>
       </c>
       <c r="M61" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N61" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O61" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P61" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q61" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R61" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W61" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="62" spans="1:23">
+    <row r="62" spans="1:27">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C62" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D62" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E62" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F62" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G62" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H62">
         <v>5</v>
@@ -4848,54 +5169,63 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="L62" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M62" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N62" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O62" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P62" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q62" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R62" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W62" s="2">
-        <v>46241</v>
-      </c>
-    </row>
-    <row r="63" spans="1:23">
+        <v>46247</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27">
       <c r="A63" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C63" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D63" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E63" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F63" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G63" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -4913,48 +5243,48 @@
         <v>46243.50712962963</v>
       </c>
       <c r="M63" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N63" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O63" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P63" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q63" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R63" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W63" s="2">
         <v>46164</v>
       </c>
     </row>
-    <row r="64" spans="1:23">
+    <row r="64" spans="1:27">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C64" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D64" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E64" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F64" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G64" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H64">
         <v>5</v>
@@ -4972,48 +5302,48 @@
         <v>46243.50715277778</v>
       </c>
       <c r="M64" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N64" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O64" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P64" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q64" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R64" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W64" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="65" spans="1:23">
+    <row r="65" spans="1:27">
       <c r="A65" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C65" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D65" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E65" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F65" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G65" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H65">
         <v>5</v>
@@ -5022,57 +5352,66 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="K65">
-        <v>3107</v>
+        <v>3334</v>
       </c>
       <c r="L65" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M65" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N65" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O65" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P65" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q65" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R65" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W65" s="2">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23">
+        <v>46253</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27">
       <c r="A66" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C66" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D66" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E66" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F66" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G66" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H66">
         <v>5</v>
@@ -5087,51 +5426,60 @@
         <v>3037</v>
       </c>
       <c r="L66" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M66" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N66" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O66" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P66" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q66" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R66" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W66" s="2">
         <v>46160</v>
       </c>
-    </row>
-    <row r="67" spans="1:23">
+      <c r="Y66" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27">
       <c r="A67" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C67" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D67" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E67" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F67" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G67" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H67">
         <v>5</v>
@@ -5140,57 +5488,66 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K67">
-        <v>1603</v>
+        <v>1644</v>
       </c>
       <c r="L67" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M67" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="N67" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O67" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P67" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q67" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R67" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W67" s="2">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23">
+        <v>46252</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C68" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D68" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E68" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F68" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G68" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H68">
         <v>5</v>
@@ -5199,57 +5556,66 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K68">
-        <v>3054</v>
+        <v>3190</v>
       </c>
       <c r="L68" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M68" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N68" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O68" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P68" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q68" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R68" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W68" s="2">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="69" spans="1:23">
+        <v>46252</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27">
       <c r="A69" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C69" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D69" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E69" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F69" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G69" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H69">
         <v>5</v>
@@ -5264,51 +5630,60 @@
         <v>3046</v>
       </c>
       <c r="L69" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25208333333</v>
       </c>
       <c r="M69" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N69" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O69" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P69" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q69" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R69" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W69" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="70" spans="1:23">
+      <c r="Y69" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27">
       <c r="A70" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C70" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D70" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E70" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F70" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G70" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H70">
         <v>5</v>
@@ -5320,54 +5695,63 @@
         <v>5</v>
       </c>
       <c r="K70">
-        <v>1981</v>
+        <v>2063</v>
       </c>
       <c r="L70" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M70" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N70" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O70" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P70" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q70" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R70" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W70" s="2">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23">
+        <v>46252</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27">
       <c r="A71" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C71" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D71" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E71" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F71" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G71" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H71">
         <v>5</v>
@@ -5376,57 +5760,66 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K71">
-        <v>1950</v>
+        <v>2065</v>
       </c>
       <c r="L71" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M71" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N71" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O71" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P71" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q71" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R71" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W71" s="2">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="72" spans="1:23">
+        <v>46253</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>270</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27">
       <c r="A72" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C72" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D72" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E72" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F72" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G72" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H72">
         <v>5</v>
@@ -5444,48 +5837,48 @@
         <v>46243.50783564815</v>
       </c>
       <c r="M72" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N72" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O72" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P72" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q72" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R72" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W72" s="2">
         <v>46164</v>
       </c>
     </row>
-    <row r="73" spans="1:23">
+    <row r="73" spans="1:27">
       <c r="A73" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C73" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D73" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E73" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F73" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G73" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H73">
         <v>5</v>
@@ -5497,54 +5890,63 @@
         <v>1</v>
       </c>
       <c r="K73">
-        <v>1273</v>
+        <v>1285</v>
       </c>
       <c r="L73" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M73" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N73" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O73" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P73" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q73" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R73" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W73" s="2">
-        <v>46244</v>
-      </c>
-    </row>
-    <row r="74" spans="1:23">
+        <v>46252</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27">
       <c r="A74" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C74" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D74" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E74" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F74" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G74" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H74">
         <v>5</v>
@@ -5559,51 +5961,60 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M74" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N74" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O74" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P74" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q74" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R74" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W74" s="2">
         <v>46185</v>
       </c>
-    </row>
-    <row r="75" spans="1:23">
+      <c r="Y74" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27">
       <c r="A75" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C75" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D75" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E75" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F75" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G75" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H75">
         <v>5</v>
@@ -5618,51 +6029,60 @@
         <v>1480</v>
       </c>
       <c r="L75" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M75" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N75" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O75" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P75" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q75" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R75" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W75" s="2">
         <v>46149</v>
       </c>
-    </row>
-    <row r="76" spans="1:23">
+      <c r="Y75" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27">
       <c r="A76" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D76" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E76" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F76" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H76">
         <v>5</v>
@@ -5677,51 +6097,60 @@
         <v>1524</v>
       </c>
       <c r="L76" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M76" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N76" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O76" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P76" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q76" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R76" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W76" s="2">
         <v>46149</v>
       </c>
-    </row>
-    <row r="77" spans="1:23">
+      <c r="Y76" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27">
       <c r="A77" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C77" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D77" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E77" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F77" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G77" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H77">
         <v>5</v>
@@ -5736,51 +6165,60 @@
         <v>1537</v>
       </c>
       <c r="L77" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M77" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N77" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O77" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P77" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q77" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R77" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W77" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="78" spans="1:23">
+      <c r="Y77" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27">
       <c r="A78" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C78" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D78" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E78" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F78" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G78" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H78">
         <v>5</v>
@@ -5795,51 +6233,60 @@
         <v>1537</v>
       </c>
       <c r="L78" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M78" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N78" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O78" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P78" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q78" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R78" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W78" s="2">
         <v>46160</v>
       </c>
-    </row>
-    <row r="79" spans="1:23">
+      <c r="Y78" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27">
       <c r="A79" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C79" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D79" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E79" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F79" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G79" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H79">
         <v>5</v>
@@ -5854,51 +6301,60 @@
         <v>1550</v>
       </c>
       <c r="L79" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M79" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N79" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O79" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P79" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q79" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R79" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W79" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="80" spans="1:23">
+      <c r="Y79" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27">
       <c r="A80" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C80" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D80" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E80" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F80" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G80" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H80">
         <v>5</v>
@@ -5910,54 +6366,63 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="L80" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M80" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N80" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O80" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P80" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q80" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R80" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W80" s="2">
-        <v>46164</v>
-      </c>
-    </row>
-    <row r="81" spans="1:23">
+        <v>46246</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27">
       <c r="A81" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C81" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D81" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E81" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F81" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G81" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H81">
         <v>5</v>
@@ -5972,51 +6437,60 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M81" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N81" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O81" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P81" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q81" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R81" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W81" s="2">
         <v>46160</v>
       </c>
-    </row>
-    <row r="82" spans="1:23">
+      <c r="Y81" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27">
       <c r="A82" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C82" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D82" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E82" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F82" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G82" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H82">
         <v>5</v>
@@ -6034,48 +6508,48 @@
         <v>46243.50800925926</v>
       </c>
       <c r="M82" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N82" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O82" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P82" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q82" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R82" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W82" s="2">
         <v>46161</v>
       </c>
     </row>
-    <row r="83" spans="1:23">
+    <row r="83" spans="1:27">
       <c r="A83" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C83" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D83" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E83" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F83" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G83" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H83">
         <v>5</v>
@@ -6093,48 +6567,48 @@
         <v>46243.50802083333</v>
       </c>
       <c r="M83" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N83" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O83" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P83" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q83" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R83" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W83" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="84" spans="1:23">
+    <row r="84" spans="1:27">
       <c r="A84" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C84" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D84" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E84" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F84" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G84" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H84">
         <v>5</v>
@@ -6152,48 +6626,48 @@
         <v>46243.50803240741</v>
       </c>
       <c r="M84" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N84" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O84" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P84" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q84" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R84" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W84" s="2">
         <v>46164</v>
       </c>
     </row>
-    <row r="85" spans="1:23">
+    <row r="85" spans="1:27">
       <c r="A85" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C85" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D85" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E85" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F85" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G85" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H85">
         <v>5</v>
@@ -6211,48 +6685,48 @@
         <v>46243.50804398148</v>
       </c>
       <c r="M85" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N85" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O85" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P85" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q85" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R85" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W85" s="2">
         <v>46168</v>
       </c>
     </row>
-    <row r="86" spans="1:23">
+    <row r="86" spans="1:27">
       <c r="A86" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C86" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D86" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E86" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F86" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G86" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H86">
         <v>5</v>
@@ -6267,51 +6741,60 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M86" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N86" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O86" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P86" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q86" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R86" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W86" s="2">
         <v>46164</v>
       </c>
-    </row>
-    <row r="87" spans="1:23">
+      <c r="Y86" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27">
       <c r="A87" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C87" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D87" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E87" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F87" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G87" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H87">
         <v>5</v>
@@ -6326,51 +6809,60 @@
         <v>3607</v>
       </c>
       <c r="L87" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M87" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N87" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O87" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P87" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q87" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R87" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W87" s="2">
         <v>46168</v>
       </c>
-    </row>
-    <row r="88" spans="1:23">
+      <c r="Y87" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27">
       <c r="A88" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C88" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D88" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E88" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F88" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G88" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H88">
         <v>5</v>
@@ -6385,92 +6877,101 @@
         <v>3551</v>
       </c>
       <c r="L88" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M88" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N88" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O88" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P88" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q88" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R88" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W88" s="2">
         <v>46163</v>
       </c>
-    </row>
-    <row r="89" spans="1:23">
+      <c r="Y88" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27">
       <c r="A89" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C89" t="s">
+        <v>209</v>
+      </c>
+      <c r="D89" t="s">
+        <v>227</v>
+      </c>
+      <c r="E89" t="s">
+        <v>255</v>
+      </c>
+      <c r="F89" t="s">
+        <v>257</v>
+      </c>
+      <c r="G89" t="s">
+        <v>258</v>
+      </c>
+      <c r="H89">
+        <v>5</v>
+      </c>
+      <c r="N89" t="s">
+        <v>257</v>
+      </c>
+      <c r="O89" t="s">
+        <v>264</v>
+      </c>
+      <c r="P89" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>268</v>
+      </c>
+      <c r="R89" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27">
+      <c r="A90" t="s">
+        <v>115</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D89" t="s">
-        <v>224</v>
-      </c>
-      <c r="E89" t="s">
-        <v>252</v>
-      </c>
-      <c r="F89" t="s">
-        <v>254</v>
-      </c>
-      <c r="G89" t="s">
+      <c r="C90" t="s">
+        <v>226</v>
+      </c>
+      <c r="D90" t="s">
+        <v>245</v>
+      </c>
+      <c r="E90" t="s">
         <v>255</v>
       </c>
-      <c r="H89">
-        <v>5</v>
-      </c>
-      <c r="N89" t="s">
-        <v>254</v>
-      </c>
-      <c r="O89" t="s">
-        <v>261</v>
-      </c>
-      <c r="P89" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>265</v>
-      </c>
-      <c r="R89" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="90" spans="1:23">
-      <c r="A90" t="s">
-        <v>112</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C90" t="s">
-        <v>223</v>
-      </c>
-      <c r="D90" t="s">
-        <v>242</v>
-      </c>
-      <c r="E90" t="s">
-        <v>252</v>
-      </c>
       <c r="F90" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G90" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H90">
         <v>5</v>
@@ -6485,95 +6986,104 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46246.0112037037</v>
+        <v>46253.25209490741</v>
       </c>
       <c r="M90" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N90" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O90" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P90" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q90" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R90" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W90" s="2">
         <v>46154</v>
       </c>
-    </row>
-    <row r="91" spans="1:23">
+      <c r="Y90" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27">
       <c r="A91" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C91" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D91" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E91" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F91" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G91" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H91">
         <v>5</v>
       </c>
       <c r="N91" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O91" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P91" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q91" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R91" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="W91" s="2">
         <v>46154</v>
       </c>
     </row>
-    <row r="92" spans="1:23">
+    <row r="92" spans="1:27">
       <c r="A92" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C92" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D92" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E92" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F92" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G92" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -6591,22 +7101,22 @@
         <v>46243.50813657408</v>
       </c>
       <c r="M92" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N92" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O92" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P92" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q92" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R92" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="W92" s="2">
         <v>46164</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="273">
   <si>
     <t>site_name</t>
   </si>
@@ -830,6 +830,9 @@
   </si>
   <si>
     <t>PRIMARY_PARSER</t>
+  </si>
+  <si>
+    <t>feed:https://www.federalregister.gov/api/v1/documents.rss?conditions%5Bsections%5D%5B%5D=world;feed:https://www.federalregister.gov/api/v1/documents.rss?conditions%5Bsections%5D%5B%5D=world&amp;conditions%5Bsignificant%5D=1</t>
   </si>
 </sst>
 </file>
@@ -1547,7 +1550,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1990,7 +1993,7 @@
         <v>165</v>
       </c>
       <c r="L13" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M13" t="s">
         <v>263</v>
@@ -2055,16 +2058,16 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="L14" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N14" t="s">
         <v>256</v>
@@ -2082,7 +2085,7 @@
         <v>267</v>
       </c>
       <c r="W14" s="2">
-        <v>46168</v>
+        <v>46252</v>
       </c>
       <c r="Y14" t="s">
         <v>261</v>
@@ -2129,7 +2132,7 @@
         <v>3475</v>
       </c>
       <c r="L15" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M15" t="s">
         <v>263</v>
@@ -2197,7 +2200,7 @@
         <v>3475</v>
       </c>
       <c r="L16" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M16" t="s">
         <v>263</v>
@@ -2324,7 +2327,7 @@
         <v>3606</v>
       </c>
       <c r="L18" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M18" t="s">
         <v>263</v>
@@ -2569,7 +2572,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2637,7 +2640,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2705,7 +2708,7 @@
         <v>125</v>
       </c>
       <c r="L24" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2773,7 +2776,7 @@
         <v>125</v>
       </c>
       <c r="L25" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M25" t="s">
         <v>263</v>
@@ -2841,7 +2844,7 @@
         <v>125</v>
       </c>
       <c r="L26" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M26" t="s">
         <v>263</v>
@@ -3198,13 +3201,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="K32">
-        <v>6988</v>
+        <v>7065</v>
       </c>
       <c r="L32" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M32" t="s">
         <v>261</v>
@@ -3225,7 +3228,7 @@
         <v>267</v>
       </c>
       <c r="W32" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="Y32" t="s">
         <v>261</v>
@@ -3390,7 +3393,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3458,7 +3461,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3526,7 +3529,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3594,7 +3597,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3662,7 +3665,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3730,7 +3733,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3798,7 +3801,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3866,7 +3869,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3934,7 +3937,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -4055,13 +4058,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K45">
-        <v>2965</v>
+        <v>2971</v>
       </c>
       <c r="L45" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4082,7 +4085,7 @@
         <v>267</v>
       </c>
       <c r="W45" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4123,13 +4126,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K46">
-        <v>3411</v>
+        <v>3431</v>
       </c>
       <c r="L46" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4150,7 +4153,7 @@
         <v>267</v>
       </c>
       <c r="W46" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4191,13 +4194,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K47">
-        <v>3398</v>
+        <v>3418</v>
       </c>
       <c r="L47" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4218,7 +4221,7 @@
         <v>267</v>
       </c>
       <c r="W47" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4265,7 +4268,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4333,7 +4336,7 @@
         <v>1485</v>
       </c>
       <c r="L49" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M49" t="s">
         <v>263</v>
@@ -4398,10 +4401,10 @@
         <v>1</v>
       </c>
       <c r="K50">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="L50" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M50" t="s">
         <v>262</v>
@@ -4469,7 +4472,7 @@
         <v>1468</v>
       </c>
       <c r="L51" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M51" t="s">
         <v>263</v>
@@ -4537,7 +4540,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4605,7 +4608,7 @@
         <v>1938</v>
       </c>
       <c r="L53" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M53" t="s">
         <v>263</v>
@@ -4667,16 +4670,16 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="L54" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N54" t="s">
         <v>256</v>
@@ -4694,7 +4697,7 @@
         <v>267</v>
       </c>
       <c r="W54" s="2">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="Y54" t="s">
         <v>261</v>
@@ -4738,10 +4741,10 @@
         <v>10</v>
       </c>
       <c r="K55">
-        <v>1718</v>
+        <v>1728</v>
       </c>
       <c r="L55" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M55" t="s">
         <v>261</v>
@@ -4762,7 +4765,7 @@
         <v>267</v>
       </c>
       <c r="W55" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="Y55" t="s">
         <v>261</v>
@@ -4865,10 +4868,10 @@
         <v>2</v>
       </c>
       <c r="K57">
-        <v>3762</v>
+        <v>3764</v>
       </c>
       <c r="L57" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M57" t="s">
         <v>262</v>
@@ -5172,7 +5175,7 @@
         <v>1632</v>
       </c>
       <c r="L62" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M62" t="s">
         <v>263</v>
@@ -5352,13 +5355,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K65">
-        <v>3334</v>
+        <v>3350</v>
       </c>
       <c r="L65" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5426,7 +5429,7 @@
         <v>3037</v>
       </c>
       <c r="L66" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5488,13 +5491,13 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="L67" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M67" t="s">
         <v>262</v>
@@ -5556,13 +5559,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K68">
-        <v>3190</v>
+        <v>3202</v>
       </c>
       <c r="L68" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5583,7 +5586,7 @@
         <v>267</v>
       </c>
       <c r="W68" s="2">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="Y68" t="s">
         <v>261</v>
@@ -5630,7 +5633,7 @@
         <v>3046</v>
       </c>
       <c r="L69" s="2">
-        <v>46253.25208333333</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5695,10 +5698,10 @@
         <v>5</v>
       </c>
       <c r="K70">
-        <v>2063</v>
+        <v>2068</v>
       </c>
       <c r="L70" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M70" t="s">
         <v>261</v>
@@ -5763,10 +5766,10 @@
         <v>11</v>
       </c>
       <c r="K71">
-        <v>2065</v>
+        <v>2076</v>
       </c>
       <c r="L71" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5890,10 +5893,10 @@
         <v>1</v>
       </c>
       <c r="K73">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="L73" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M73" t="s">
         <v>262</v>
@@ -5914,7 +5917,7 @@
         <v>267</v>
       </c>
       <c r="W73" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="Y73" t="s">
         <v>261</v>
@@ -5961,7 +5964,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -6029,7 +6032,7 @@
         <v>1480</v>
       </c>
       <c r="L75" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6097,7 +6100,7 @@
         <v>1524</v>
       </c>
       <c r="L76" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M76" t="s">
         <v>263</v>
@@ -6165,7 +6168,7 @@
         <v>1537</v>
       </c>
       <c r="L77" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M77" t="s">
         <v>263</v>
@@ -6233,7 +6236,7 @@
         <v>1537</v>
       </c>
       <c r="L78" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M78" t="s">
         <v>263</v>
@@ -6301,7 +6304,7 @@
         <v>1550</v>
       </c>
       <c r="L79" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M79" t="s">
         <v>263</v>
@@ -6369,7 +6372,7 @@
         <v>1353</v>
       </c>
       <c r="L80" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M80" t="s">
         <v>263</v>
@@ -6437,7 +6440,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6741,7 +6744,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6809,7 +6812,7 @@
         <v>3607</v>
       </c>
       <c r="L87" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6871,16 +6874,16 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K88">
-        <v>3551</v>
+        <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N88" t="s">
         <v>256</v>
@@ -6898,7 +6901,7 @@
         <v>267</v>
       </c>
       <c r="W88" s="2">
-        <v>46163</v>
+        <v>46253.16666666666</v>
       </c>
       <c r="Y88" t="s">
         <v>261</v>
@@ -6907,7 +6910,7 @@
         <v>263</v>
       </c>
       <c r="AA88" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -6986,7 +6989,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46253.25209490741</v>
+        <v>46254.04091435186</v>
       </c>
       <c r="M90" t="s">
         <v>263</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -829,10 +829,10 @@
     <t>NEW</t>
   </si>
   <si>
+    <t>selenium:detail_date</t>
+  </si>
+  <si>
     <t>PRIMARY_PARSER</t>
-  </si>
-  <si>
-    <t>feed:https://www.federalregister.gov/api/v1/documents.rss?conditions%5Bsections%5D%5B%5D=world;feed:https://www.federalregister.gov/api/v1/documents.rss?conditions%5Bsections%5D%5B%5D=world&amp;conditions%5Bsignificant%5D=1</t>
   </si>
 </sst>
 </file>
@@ -1550,7 +1550,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1987,16 +1987,16 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N13" t="s">
         <v>256</v>
@@ -2014,7 +2014,7 @@
         <v>267</v>
       </c>
       <c r="W13" s="2">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="X13">
         <v>12</v>
@@ -2026,7 +2026,7 @@
         <v>270</v>
       </c>
       <c r="AA13" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -2058,16 +2058,16 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>3476</v>
+        <v>3497</v>
       </c>
       <c r="L14" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N14" t="s">
         <v>256</v>
@@ -2085,7 +2085,7 @@
         <v>267</v>
       </c>
       <c r="W14" s="2">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="Y14" t="s">
         <v>261</v>
@@ -2094,7 +2094,7 @@
         <v>263</v>
       </c>
       <c r="AA14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -2126,16 +2126,16 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>3475</v>
+        <v>3480</v>
       </c>
       <c r="L15" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N15" t="s">
         <v>256</v>
@@ -2153,7 +2153,7 @@
         <v>267</v>
       </c>
       <c r="W15" s="2">
-        <v>46168</v>
+        <v>46254</v>
       </c>
       <c r="Y15" t="s">
         <v>261</v>
@@ -2162,7 +2162,7 @@
         <v>263</v>
       </c>
       <c r="AA15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -2194,16 +2194,16 @@
         <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>3475</v>
+        <v>3478</v>
       </c>
       <c r="L16" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N16" t="s">
         <v>256</v>
@@ -2221,7 +2221,7 @@
         <v>267</v>
       </c>
       <c r="W16" s="2">
-        <v>46164</v>
+        <v>46255</v>
       </c>
       <c r="Y16" t="s">
         <v>261</v>
@@ -2230,7 +2230,7 @@
         <v>263</v>
       </c>
       <c r="AA16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -2321,16 +2321,16 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>3606</v>
+        <v>3608</v>
       </c>
       <c r="L18" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N18" t="s">
         <v>256</v>
@@ -2348,7 +2348,7 @@
         <v>267</v>
       </c>
       <c r="W18" s="2">
-        <v>46250</v>
+        <v>46257</v>
       </c>
       <c r="Y18" t="s">
         <v>261</v>
@@ -2357,7 +2357,7 @@
         <v>270</v>
       </c>
       <c r="AA18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -2572,7 +2572,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2602,7 +2602,7 @@
         <v>263</v>
       </c>
       <c r="AA22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -2640,7 +2640,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2670,7 +2670,7 @@
         <v>263</v>
       </c>
       <c r="AA23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -2702,16 +2702,16 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="L24" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N24" t="s">
         <v>256</v>
@@ -2729,7 +2729,7 @@
         <v>267</v>
       </c>
       <c r="W24" s="2">
-        <v>46168</v>
+        <v>46257</v>
       </c>
       <c r="Y24" t="s">
         <v>261</v>
@@ -2738,7 +2738,7 @@
         <v>263</v>
       </c>
       <c r="AA24" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -2770,16 +2770,16 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L25" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N25" t="s">
         <v>256</v>
@@ -2797,7 +2797,7 @@
         <v>267</v>
       </c>
       <c r="W25" s="2">
-        <v>46167</v>
+        <v>46256</v>
       </c>
       <c r="Y25" t="s">
         <v>261</v>
@@ -2806,7 +2806,7 @@
         <v>263</v>
       </c>
       <c r="AA25" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -2838,16 +2838,16 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L26" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s">
         <v>256</v>
@@ -2865,7 +2865,7 @@
         <v>267</v>
       </c>
       <c r="W26" s="2">
-        <v>46168</v>
+        <v>46254</v>
       </c>
       <c r="Y26" t="s">
         <v>261</v>
@@ -2874,7 +2874,7 @@
         <v>263</v>
       </c>
       <c r="AA26" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -3201,16 +3201,16 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>7065</v>
+        <v>7327</v>
       </c>
       <c r="L32" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M32" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N32" t="s">
         <v>256</v>
@@ -3228,7 +3228,7 @@
         <v>267</v>
       </c>
       <c r="W32" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="Y32" t="s">
         <v>261</v>
@@ -3237,7 +3237,7 @@
         <v>270</v>
       </c>
       <c r="AA32" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -3393,7 +3393,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3423,7 +3423,7 @@
         <v>263</v>
       </c>
       <c r="AA35" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -3461,7 +3461,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3491,7 +3491,7 @@
         <v>263</v>
       </c>
       <c r="AA36" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -3529,7 +3529,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3559,7 +3559,7 @@
         <v>263</v>
       </c>
       <c r="AA37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -3597,7 +3597,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3627,7 +3627,7 @@
         <v>263</v>
       </c>
       <c r="AA38" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -3665,7 +3665,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3695,7 +3695,7 @@
         <v>263</v>
       </c>
       <c r="AA39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -3733,7 +3733,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3763,7 +3763,7 @@
         <v>263</v>
       </c>
       <c r="AA40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -3801,7 +3801,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3831,7 +3831,7 @@
         <v>263</v>
       </c>
       <c r="AA41" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:27">
@@ -3869,7 +3869,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3899,7 +3899,7 @@
         <v>263</v>
       </c>
       <c r="AA42" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:27">
@@ -3937,7 +3937,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -3967,7 +3967,7 @@
         <v>263</v>
       </c>
       <c r="AA43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:27">
@@ -4058,13 +4058,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K45">
-        <v>2971</v>
+        <v>3000</v>
       </c>
       <c r="L45" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4085,7 +4085,7 @@
         <v>267</v>
       </c>
       <c r="W45" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4094,7 +4094,7 @@
         <v>263</v>
       </c>
       <c r="AA45" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:27">
@@ -4126,13 +4126,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K46">
-        <v>3431</v>
+        <v>3528</v>
       </c>
       <c r="L46" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4153,7 +4153,7 @@
         <v>267</v>
       </c>
       <c r="W46" s="2">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4162,7 +4162,7 @@
         <v>263</v>
       </c>
       <c r="AA46" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:27">
@@ -4194,13 +4194,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K47">
-        <v>3418</v>
+        <v>3510</v>
       </c>
       <c r="L47" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4221,7 +4221,7 @@
         <v>267</v>
       </c>
       <c r="W47" s="2">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4230,7 +4230,7 @@
         <v>263</v>
       </c>
       <c r="AA47" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4268,7 +4268,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4298,7 +4298,7 @@
         <v>263</v>
       </c>
       <c r="AA48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4336,7 +4336,7 @@
         <v>1485</v>
       </c>
       <c r="L49" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M49" t="s">
         <v>263</v>
@@ -4366,7 +4366,7 @@
         <v>263</v>
       </c>
       <c r="AA49" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -4398,13 +4398,13 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50">
-        <v>1517</v>
+        <v>1525</v>
       </c>
       <c r="L50" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M50" t="s">
         <v>262</v>
@@ -4425,7 +4425,7 @@
         <v>267</v>
       </c>
       <c r="W50" s="2">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="Y50" t="s">
         <v>261</v>
@@ -4434,7 +4434,7 @@
         <v>263</v>
       </c>
       <c r="AA50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -4472,7 +4472,7 @@
         <v>1468</v>
       </c>
       <c r="L51" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M51" t="s">
         <v>263</v>
@@ -4502,7 +4502,7 @@
         <v>263</v>
       </c>
       <c r="AA51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -4540,7 +4540,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4570,7 +4570,7 @@
         <v>263</v>
       </c>
       <c r="AA52" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:27">
@@ -4608,7 +4608,7 @@
         <v>1938</v>
       </c>
       <c r="L53" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M53" t="s">
         <v>263</v>
@@ -4638,7 +4638,7 @@
         <v>263</v>
       </c>
       <c r="AA53" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:27">
@@ -4670,16 +4670,16 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="L54" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M54" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N54" t="s">
         <v>256</v>
@@ -4706,7 +4706,7 @@
         <v>263</v>
       </c>
       <c r="AA54" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:27">
@@ -4741,10 +4741,10 @@
         <v>10</v>
       </c>
       <c r="K55">
-        <v>1728</v>
+        <v>1778</v>
       </c>
       <c r="L55" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M55" t="s">
         <v>261</v>
@@ -4765,7 +4765,7 @@
         <v>267</v>
       </c>
       <c r="W55" s="2">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="Y55" t="s">
         <v>261</v>
@@ -4774,7 +4774,7 @@
         <v>270</v>
       </c>
       <c r="AA55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:27">
@@ -4865,16 +4865,16 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>3764</v>
+        <v>3770</v>
       </c>
       <c r="L57" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M57" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N57" t="s">
         <v>256</v>
@@ -4892,7 +4892,7 @@
         <v>267</v>
       </c>
       <c r="W57" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="Y57" t="s">
         <v>261</v>
@@ -4901,7 +4901,7 @@
         <v>263</v>
       </c>
       <c r="AA57" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:27">
@@ -5175,7 +5175,7 @@
         <v>1632</v>
       </c>
       <c r="L62" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M62" t="s">
         <v>263</v>
@@ -5205,7 +5205,7 @@
         <v>263</v>
       </c>
       <c r="AA62" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:27">
@@ -5355,13 +5355,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K65">
-        <v>3350</v>
+        <v>3446</v>
       </c>
       <c r="L65" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5382,7 +5382,7 @@
         <v>267</v>
       </c>
       <c r="W65" s="2">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="Y65" t="s">
         <v>261</v>
@@ -5391,7 +5391,7 @@
         <v>270</v>
       </c>
       <c r="AA65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" spans="1:27">
@@ -5429,7 +5429,7 @@
         <v>3037</v>
       </c>
       <c r="L66" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5459,7 +5459,7 @@
         <v>263</v>
       </c>
       <c r="AA66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="1:27">
@@ -5491,16 +5491,16 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="L67" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M67" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N67" t="s">
         <v>256</v>
@@ -5527,7 +5527,7 @@
         <v>270</v>
       </c>
       <c r="AA67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:27">
@@ -5559,13 +5559,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K68">
-        <v>3202</v>
+        <v>3271</v>
       </c>
       <c r="L68" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5586,7 +5586,7 @@
         <v>267</v>
       </c>
       <c r="W68" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="Y68" t="s">
         <v>261</v>
@@ -5595,7 +5595,7 @@
         <v>270</v>
       </c>
       <c r="AA68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="1:27">
@@ -5633,7 +5633,7 @@
         <v>3046</v>
       </c>
       <c r="L69" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5663,7 +5663,7 @@
         <v>263</v>
       </c>
       <c r="AA69" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -5695,13 +5695,13 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K70">
-        <v>2068</v>
+        <v>2086</v>
       </c>
       <c r="L70" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M70" t="s">
         <v>261</v>
@@ -5722,7 +5722,7 @@
         <v>267</v>
       </c>
       <c r="W70" s="2">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="Y70" t="s">
         <v>261</v>
@@ -5731,7 +5731,7 @@
         <v>270</v>
       </c>
       <c r="AA70" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -5763,16 +5763,16 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K71">
-        <v>2076</v>
+        <v>2105</v>
       </c>
       <c r="L71" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M71" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N71" t="s">
         <v>256</v>
@@ -5790,7 +5790,7 @@
         <v>267</v>
       </c>
       <c r="W71" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="Y71" t="s">
         <v>261</v>
@@ -5799,7 +5799,7 @@
         <v>270</v>
       </c>
       <c r="AA71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -5893,10 +5893,10 @@
         <v>1</v>
       </c>
       <c r="K73">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="L73" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M73" t="s">
         <v>262</v>
@@ -5917,7 +5917,7 @@
         <v>267</v>
       </c>
       <c r="W73" s="2">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="Y73" t="s">
         <v>261</v>
@@ -5926,7 +5926,7 @@
         <v>263</v>
       </c>
       <c r="AA73" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -5964,7 +5964,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -5994,7 +5994,7 @@
         <v>263</v>
       </c>
       <c r="AA74" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -6032,7 +6032,7 @@
         <v>1480</v>
       </c>
       <c r="L75" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6062,7 +6062,7 @@
         <v>263</v>
       </c>
       <c r="AA75" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -6100,7 +6100,7 @@
         <v>1524</v>
       </c>
       <c r="L76" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M76" t="s">
         <v>263</v>
@@ -6130,7 +6130,7 @@
         <v>263</v>
       </c>
       <c r="AA76" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -6168,7 +6168,7 @@
         <v>1537</v>
       </c>
       <c r="L77" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M77" t="s">
         <v>263</v>
@@ -6198,7 +6198,7 @@
         <v>263</v>
       </c>
       <c r="AA77" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -6236,7 +6236,7 @@
         <v>1537</v>
       </c>
       <c r="L78" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M78" t="s">
         <v>263</v>
@@ -6266,7 +6266,7 @@
         <v>263</v>
       </c>
       <c r="AA78" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -6304,7 +6304,7 @@
         <v>1550</v>
       </c>
       <c r="L79" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M79" t="s">
         <v>263</v>
@@ -6334,7 +6334,7 @@
         <v>263</v>
       </c>
       <c r="AA79" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -6366,16 +6366,16 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K80">
-        <v>1353</v>
+        <v>1383</v>
       </c>
       <c r="L80" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M80" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N80" t="s">
         <v>256</v>
@@ -6393,7 +6393,7 @@
         <v>267</v>
       </c>
       <c r="W80" s="2">
-        <v>46246</v>
+        <v>46255</v>
       </c>
       <c r="Y80" t="s">
         <v>261</v>
@@ -6402,7 +6402,7 @@
         <v>263</v>
       </c>
       <c r="AA80" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -6440,7 +6440,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6470,7 +6470,7 @@
         <v>263</v>
       </c>
       <c r="AA81" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -6744,7 +6744,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6774,7 +6774,7 @@
         <v>263</v>
       </c>
       <c r="AA86" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -6809,10 +6809,10 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>3607</v>
+        <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6833,7 +6833,7 @@
         <v>267</v>
       </c>
       <c r="W87" s="2">
-        <v>46168</v>
+        <v>46248</v>
       </c>
       <c r="Y87" t="s">
         <v>261</v>
@@ -6842,7 +6842,7 @@
         <v>263</v>
       </c>
       <c r="AA87" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -6874,16 +6874,16 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K88">
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N88" t="s">
         <v>256</v>
@@ -6989,7 +6989,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46254.04091435186</v>
+        <v>46257.67733796296</v>
       </c>
       <c r="M90" t="s">
         <v>263</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -829,10 +829,10 @@
     <t>NEW</t>
   </si>
   <si>
+    <t>PRIMARY_PARSER</t>
+  </si>
+  <si>
     <t>selenium:detail_date</t>
-  </si>
-  <si>
-    <t>PRIMARY_PARSER</t>
   </si>
 </sst>
 </file>
@@ -1550,7 +1550,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1987,16 +1987,16 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N13" t="s">
         <v>256</v>
@@ -2026,7 +2026,7 @@
         <v>270</v>
       </c>
       <c r="AA13" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -2058,13 +2058,13 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>3497</v>
+        <v>3520</v>
       </c>
       <c r="L14" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M14" t="s">
         <v>261</v>
@@ -2085,7 +2085,7 @@
         <v>267</v>
       </c>
       <c r="W14" s="2">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="Y14" t="s">
         <v>261</v>
@@ -2094,7 +2094,7 @@
         <v>263</v>
       </c>
       <c r="AA14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -2126,13 +2126,13 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>3480</v>
+        <v>3486</v>
       </c>
       <c r="L15" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M15" t="s">
         <v>262</v>
@@ -2162,7 +2162,7 @@
         <v>263</v>
       </c>
       <c r="AA15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -2194,13 +2194,13 @@
         <v>1</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16">
-        <v>3478</v>
+        <v>3483</v>
       </c>
       <c r="L16" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2221,7 +2221,7 @@
         <v>267</v>
       </c>
       <c r="W16" s="2">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="Y16" t="s">
         <v>261</v>
@@ -2230,7 +2230,7 @@
         <v>263</v>
       </c>
       <c r="AA16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -2321,16 +2321,16 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>3608</v>
+        <v>3611</v>
       </c>
       <c r="L18" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N18" t="s">
         <v>256</v>
@@ -2357,7 +2357,7 @@
         <v>270</v>
       </c>
       <c r="AA18" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -2572,7 +2572,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2602,7 +2602,7 @@
         <v>263</v>
       </c>
       <c r="AA22" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -2640,7 +2640,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2670,7 +2670,7 @@
         <v>263</v>
       </c>
       <c r="AA23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -2705,10 +2705,10 @@
         <v>2</v>
       </c>
       <c r="K24">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M24" t="s">
         <v>262</v>
@@ -2738,7 +2738,7 @@
         <v>263</v>
       </c>
       <c r="AA24" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -2770,16 +2770,16 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L25" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N25" t="s">
         <v>256</v>
@@ -2806,7 +2806,7 @@
         <v>263</v>
       </c>
       <c r="AA25" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -2838,16 +2838,16 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>128</v>
       </c>
       <c r="L26" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s">
         <v>256</v>
@@ -2874,7 +2874,7 @@
         <v>263</v>
       </c>
       <c r="AA26" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -3201,16 +3201,16 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="K32">
-        <v>7327</v>
+        <v>7712</v>
       </c>
       <c r="L32" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M32" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N32" t="s">
         <v>256</v>
@@ -3228,7 +3228,7 @@
         <v>267</v>
       </c>
       <c r="W32" s="2">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="Y32" t="s">
         <v>261</v>
@@ -3237,7 +3237,7 @@
         <v>270</v>
       </c>
       <c r="AA32" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -3393,7 +3393,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3423,7 +3423,7 @@
         <v>263</v>
       </c>
       <c r="AA35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -3461,7 +3461,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3491,7 +3491,7 @@
         <v>263</v>
       </c>
       <c r="AA36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -3529,7 +3529,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3559,7 +3559,7 @@
         <v>263</v>
       </c>
       <c r="AA37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -3597,7 +3597,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3627,7 +3627,7 @@
         <v>263</v>
       </c>
       <c r="AA38" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -3665,7 +3665,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3695,7 +3695,7 @@
         <v>263</v>
       </c>
       <c r="AA39" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -3733,7 +3733,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3763,7 +3763,7 @@
         <v>263</v>
       </c>
       <c r="AA40" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -3801,7 +3801,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3831,7 +3831,7 @@
         <v>263</v>
       </c>
       <c r="AA41" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:27">
@@ -3869,7 +3869,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3899,7 +3899,7 @@
         <v>263</v>
       </c>
       <c r="AA42" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="43" spans="1:27">
@@ -3937,7 +3937,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -3967,7 +3967,7 @@
         <v>263</v>
       </c>
       <c r="AA43" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="44" spans="1:27">
@@ -4058,13 +4058,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K45">
-        <v>3000</v>
+        <v>3012</v>
       </c>
       <c r="L45" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4085,7 +4085,7 @@
         <v>267</v>
       </c>
       <c r="W45" s="2">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4094,7 +4094,7 @@
         <v>263</v>
       </c>
       <c r="AA45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="46" spans="1:27">
@@ -4126,13 +4126,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K46">
-        <v>3528</v>
+        <v>3606</v>
       </c>
       <c r="L46" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4153,7 +4153,7 @@
         <v>267</v>
       </c>
       <c r="W46" s="2">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4162,7 +4162,7 @@
         <v>263</v>
       </c>
       <c r="AA46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="47" spans="1:27">
@@ -4194,13 +4194,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K47">
-        <v>3510</v>
+        <v>3564</v>
       </c>
       <c r="L47" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4221,7 +4221,7 @@
         <v>267</v>
       </c>
       <c r="W47" s="2">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4230,7 +4230,7 @@
         <v>263</v>
       </c>
       <c r="AA47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4268,7 +4268,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4298,7 +4298,7 @@
         <v>263</v>
       </c>
       <c r="AA48" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4336,7 +4336,7 @@
         <v>1485</v>
       </c>
       <c r="L49" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M49" t="s">
         <v>263</v>
@@ -4366,7 +4366,7 @@
         <v>263</v>
       </c>
       <c r="AA49" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -4398,16 +4398,16 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K50">
-        <v>1525</v>
+        <v>1533</v>
       </c>
       <c r="L50" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N50" t="s">
         <v>256</v>
@@ -4425,7 +4425,7 @@
         <v>267</v>
       </c>
       <c r="W50" s="2">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="Y50" t="s">
         <v>261</v>
@@ -4434,7 +4434,7 @@
         <v>263</v>
       </c>
       <c r="AA50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -4472,7 +4472,7 @@
         <v>1468</v>
       </c>
       <c r="L51" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M51" t="s">
         <v>263</v>
@@ -4502,7 +4502,7 @@
         <v>263</v>
       </c>
       <c r="AA51" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -4540,7 +4540,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4570,7 +4570,7 @@
         <v>263</v>
       </c>
       <c r="AA52" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" spans="1:27">
@@ -4602,16 +4602,16 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K53">
-        <v>1938</v>
+        <v>1944</v>
       </c>
       <c r="L53" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M53" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N53" t="s">
         <v>256</v>
@@ -4629,7 +4629,7 @@
         <v>267</v>
       </c>
       <c r="W53" s="2">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="Y53" t="s">
         <v>261</v>
@@ -4638,7 +4638,7 @@
         <v>263</v>
       </c>
       <c r="AA53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="54" spans="1:27">
@@ -4676,7 +4676,7 @@
         <v>1325</v>
       </c>
       <c r="L54" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M54" t="s">
         <v>263</v>
@@ -4706,7 +4706,7 @@
         <v>263</v>
       </c>
       <c r="AA54" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="55" spans="1:27">
@@ -4741,10 +4741,10 @@
         <v>10</v>
       </c>
       <c r="K55">
-        <v>1778</v>
+        <v>1816</v>
       </c>
       <c r="L55" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M55" t="s">
         <v>261</v>
@@ -4765,7 +4765,7 @@
         <v>267</v>
       </c>
       <c r="W55" s="2">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="Y55" t="s">
         <v>261</v>
@@ -4774,7 +4774,7 @@
         <v>270</v>
       </c>
       <c r="AA55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="56" spans="1:27">
@@ -4865,16 +4865,16 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K57">
-        <v>3770</v>
+        <v>3773</v>
       </c>
       <c r="L57" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M57" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N57" t="s">
         <v>256</v>
@@ -4892,7 +4892,7 @@
         <v>267</v>
       </c>
       <c r="W57" s="2">
-        <v>46253</v>
+        <v>46259</v>
       </c>
       <c r="Y57" t="s">
         <v>261</v>
@@ -4901,7 +4901,7 @@
         <v>263</v>
       </c>
       <c r="AA57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="58" spans="1:27">
@@ -5175,7 +5175,7 @@
         <v>1632</v>
       </c>
       <c r="L62" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M62" t="s">
         <v>263</v>
@@ -5205,7 +5205,7 @@
         <v>263</v>
       </c>
       <c r="AA62" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:27">
@@ -5355,13 +5355,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K65">
-        <v>3446</v>
+        <v>3488</v>
       </c>
       <c r="L65" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5382,7 +5382,7 @@
         <v>267</v>
       </c>
       <c r="W65" s="2">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="Y65" t="s">
         <v>261</v>
@@ -5391,7 +5391,7 @@
         <v>270</v>
       </c>
       <c r="AA65" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="66" spans="1:27">
@@ -5429,7 +5429,7 @@
         <v>3037</v>
       </c>
       <c r="L66" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5459,7 +5459,7 @@
         <v>263</v>
       </c>
       <c r="AA66" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="67" spans="1:27">
@@ -5491,16 +5491,16 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K67">
-        <v>1647</v>
+        <v>1657</v>
       </c>
       <c r="L67" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M67" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N67" t="s">
         <v>256</v>
@@ -5518,7 +5518,7 @@
         <v>267</v>
       </c>
       <c r="W67" s="2">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="Y67" t="s">
         <v>261</v>
@@ -5527,7 +5527,7 @@
         <v>270</v>
       </c>
       <c r="AA67" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="68" spans="1:27">
@@ -5559,13 +5559,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K68">
-        <v>3271</v>
+        <v>3294</v>
       </c>
       <c r="L68" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5586,7 +5586,7 @@
         <v>267</v>
       </c>
       <c r="W68" s="2">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="Y68" t="s">
         <v>261</v>
@@ -5595,7 +5595,7 @@
         <v>270</v>
       </c>
       <c r="AA68" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="69" spans="1:27">
@@ -5630,10 +5630,10 @@
         <v>0</v>
       </c>
       <c r="K69">
-        <v>3046</v>
+        <v>3058</v>
       </c>
       <c r="L69" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5654,7 +5654,7 @@
         <v>267</v>
       </c>
       <c r="W69" s="2">
-        <v>46168</v>
+        <v>46259</v>
       </c>
       <c r="Y69" t="s">
         <v>261</v>
@@ -5663,7 +5663,7 @@
         <v>263</v>
       </c>
       <c r="AA69" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -5695,13 +5695,13 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K70">
-        <v>2086</v>
+        <v>2124</v>
       </c>
       <c r="L70" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M70" t="s">
         <v>261</v>
@@ -5722,7 +5722,7 @@
         <v>267</v>
       </c>
       <c r="W70" s="2">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="Y70" t="s">
         <v>261</v>
@@ -5731,7 +5731,7 @@
         <v>270</v>
       </c>
       <c r="AA70" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -5763,16 +5763,16 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K71">
-        <v>2105</v>
+        <v>2125</v>
       </c>
       <c r="L71" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M71" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N71" t="s">
         <v>256</v>
@@ -5790,7 +5790,7 @@
         <v>267</v>
       </c>
       <c r="W71" s="2">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="Y71" t="s">
         <v>261</v>
@@ -5799,7 +5799,7 @@
         <v>270</v>
       </c>
       <c r="AA71" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -5893,10 +5893,10 @@
         <v>1</v>
       </c>
       <c r="K73">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="L73" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M73" t="s">
         <v>262</v>
@@ -5917,7 +5917,7 @@
         <v>267</v>
       </c>
       <c r="W73" s="2">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="Y73" t="s">
         <v>261</v>
@@ -5926,7 +5926,7 @@
         <v>263</v>
       </c>
       <c r="AA73" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -5964,7 +5964,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -5994,7 +5994,7 @@
         <v>263</v>
       </c>
       <c r="AA74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -6032,7 +6032,7 @@
         <v>1480</v>
       </c>
       <c r="L75" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6062,7 +6062,7 @@
         <v>263</v>
       </c>
       <c r="AA75" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -6100,7 +6100,7 @@
         <v>1524</v>
       </c>
       <c r="L76" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M76" t="s">
         <v>263</v>
@@ -6130,7 +6130,7 @@
         <v>263</v>
       </c>
       <c r="AA76" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -6168,7 +6168,7 @@
         <v>1537</v>
       </c>
       <c r="L77" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M77" t="s">
         <v>263</v>
@@ -6198,7 +6198,7 @@
         <v>263</v>
       </c>
       <c r="AA77" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -6236,7 +6236,7 @@
         <v>1537</v>
       </c>
       <c r="L78" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M78" t="s">
         <v>263</v>
@@ -6266,7 +6266,7 @@
         <v>263</v>
       </c>
       <c r="AA78" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -6304,7 +6304,7 @@
         <v>1550</v>
       </c>
       <c r="L79" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M79" t="s">
         <v>263</v>
@@ -6334,7 +6334,7 @@
         <v>263</v>
       </c>
       <c r="AA79" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -6366,16 +6366,16 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K80">
-        <v>1383</v>
+        <v>1403</v>
       </c>
       <c r="L80" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M80" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N80" t="s">
         <v>256</v>
@@ -6402,7 +6402,7 @@
         <v>263</v>
       </c>
       <c r="AA80" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -6440,7 +6440,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6470,7 +6470,7 @@
         <v>263</v>
       </c>
       <c r="AA81" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -6744,7 +6744,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6774,7 +6774,7 @@
         <v>263</v>
       </c>
       <c r="AA86" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -6812,7 +6812,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6842,7 +6842,7 @@
         <v>263</v>
       </c>
       <c r="AA87" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -6880,7 +6880,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6910,7 +6910,7 @@
         <v>263</v>
       </c>
       <c r="AA88" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -6989,7 +6989,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46257.67733796296</v>
+        <v>46260.22043981482</v>
       </c>
       <c r="M90" t="s">
         <v>263</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -832,7 +832,7 @@
     <t>PRIMARY_PARSER</t>
   </si>
   <si>
-    <t>selenium:detail_date</t>
+    <t>static:detail_date</t>
   </si>
 </sst>
 </file>
@@ -1550,7 +1550,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1993,7 +1993,7 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M13" t="s">
         <v>263</v>
@@ -2058,16 +2058,16 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>3520</v>
+        <v>3532</v>
       </c>
       <c r="L14" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N14" t="s">
         <v>256</v>
@@ -2126,16 +2126,16 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>3486</v>
       </c>
       <c r="L15" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N15" t="s">
         <v>256</v>
@@ -2197,10 +2197,10 @@
         <v>2</v>
       </c>
       <c r="K16">
-        <v>3483</v>
+        <v>3491</v>
       </c>
       <c r="L16" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2221,7 +2221,7 @@
         <v>267</v>
       </c>
       <c r="W16" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="Y16" t="s">
         <v>261</v>
@@ -2321,16 +2321,16 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>3611</v>
+        <v>3613</v>
       </c>
       <c r="L18" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N18" t="s">
         <v>256</v>
@@ -2348,7 +2348,7 @@
         <v>267</v>
       </c>
       <c r="W18" s="2">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="Y18" t="s">
         <v>261</v>
@@ -2572,7 +2572,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2640,7 +2640,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2702,16 +2702,16 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24">
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s">
         <v>256</v>
@@ -2738,7 +2738,7 @@
         <v>263</v>
       </c>
       <c r="AA24" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -2776,7 +2776,7 @@
         <v>135</v>
       </c>
       <c r="L25" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M25" t="s">
         <v>263</v>
@@ -2844,7 +2844,7 @@
         <v>128</v>
       </c>
       <c r="L26" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M26" t="s">
         <v>263</v>
@@ -3201,13 +3201,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="K32">
-        <v>7712</v>
+        <v>8182</v>
       </c>
       <c r="L32" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M32" t="s">
         <v>261</v>
@@ -3228,7 +3228,7 @@
         <v>267</v>
       </c>
       <c r="W32" s="2">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="Y32" t="s">
         <v>261</v>
@@ -3393,7 +3393,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3461,7 +3461,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3529,7 +3529,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3597,7 +3597,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3665,7 +3665,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3733,7 +3733,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3801,7 +3801,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3869,7 +3869,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3937,7 +3937,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -4058,13 +4058,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K45">
-        <v>3012</v>
+        <v>3039</v>
       </c>
       <c r="L45" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4085,7 +4085,7 @@
         <v>267</v>
       </c>
       <c r="W45" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4129,10 +4129,10 @@
         <v>20</v>
       </c>
       <c r="K46">
-        <v>3606</v>
+        <v>3666</v>
       </c>
       <c r="L46" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4153,7 +4153,7 @@
         <v>267</v>
       </c>
       <c r="W46" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4194,13 +4194,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K47">
-        <v>3564</v>
+        <v>3612</v>
       </c>
       <c r="L47" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4221,7 +4221,7 @@
         <v>267</v>
       </c>
       <c r="W47" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4268,7 +4268,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4336,7 +4336,7 @@
         <v>1485</v>
       </c>
       <c r="L49" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M49" t="s">
         <v>263</v>
@@ -4398,16 +4398,16 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K50">
-        <v>1533</v>
+        <v>1547</v>
       </c>
       <c r="L50" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N50" t="s">
         <v>256</v>
@@ -4425,7 +4425,7 @@
         <v>267</v>
       </c>
       <c r="W50" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="Y50" t="s">
         <v>261</v>
@@ -4472,7 +4472,7 @@
         <v>1468</v>
       </c>
       <c r="L51" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M51" t="s">
         <v>263</v>
@@ -4540,7 +4540,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4605,10 +4605,10 @@
         <v>3</v>
       </c>
       <c r="K53">
-        <v>1944</v>
+        <v>1957</v>
       </c>
       <c r="L53" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M53" t="s">
         <v>261</v>
@@ -4629,7 +4629,7 @@
         <v>267</v>
       </c>
       <c r="W53" s="2">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="Y53" t="s">
         <v>261</v>
@@ -4676,7 +4676,7 @@
         <v>1325</v>
       </c>
       <c r="L54" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M54" t="s">
         <v>263</v>
@@ -4738,13 +4738,13 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K55">
-        <v>1816</v>
+        <v>1849</v>
       </c>
       <c r="L55" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M55" t="s">
         <v>261</v>
@@ -4765,7 +4765,7 @@
         <v>267</v>
       </c>
       <c r="W55" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="Y55" t="s">
         <v>261</v>
@@ -4865,16 +4865,16 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>3773</v>
+        <v>3783</v>
       </c>
       <c r="L57" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M57" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N57" t="s">
         <v>256</v>
@@ -4892,7 +4892,7 @@
         <v>267</v>
       </c>
       <c r="W57" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="Y57" t="s">
         <v>261</v>
@@ -5169,16 +5169,16 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="L62" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M62" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N62" t="s">
         <v>256</v>
@@ -5196,7 +5196,7 @@
         <v>267</v>
       </c>
       <c r="W62" s="2">
-        <v>46247</v>
+        <v>46262</v>
       </c>
       <c r="Y62" t="s">
         <v>261</v>
@@ -5355,13 +5355,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K65">
-        <v>3488</v>
+        <v>3548</v>
       </c>
       <c r="L65" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5382,7 +5382,7 @@
         <v>267</v>
       </c>
       <c r="W65" s="2">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="Y65" t="s">
         <v>261</v>
@@ -5429,7 +5429,7 @@
         <v>3037</v>
       </c>
       <c r="L66" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5491,16 +5491,16 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K67">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="L67" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M67" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N67" t="s">
         <v>256</v>
@@ -5559,13 +5559,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K68">
-        <v>3294</v>
+        <v>3398</v>
       </c>
       <c r="L68" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5586,7 +5586,7 @@
         <v>267</v>
       </c>
       <c r="W68" s="2">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="Y68" t="s">
         <v>261</v>
@@ -5633,7 +5633,7 @@
         <v>3058</v>
       </c>
       <c r="L69" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5695,13 +5695,13 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>2124</v>
+        <v>2150</v>
       </c>
       <c r="L70" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M70" t="s">
         <v>261</v>
@@ -5722,7 +5722,7 @@
         <v>267</v>
       </c>
       <c r="W70" s="2">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="Y70" t="s">
         <v>261</v>
@@ -5763,13 +5763,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K71">
-        <v>2125</v>
+        <v>2173</v>
       </c>
       <c r="L71" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5790,7 +5790,7 @@
         <v>267</v>
       </c>
       <c r="W71" s="2">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="Y71" t="s">
         <v>261</v>
@@ -5799,7 +5799,7 @@
         <v>270</v>
       </c>
       <c r="AA71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -5893,10 +5893,10 @@
         <v>1</v>
       </c>
       <c r="K73">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="L73" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M73" t="s">
         <v>262</v>
@@ -5917,7 +5917,7 @@
         <v>267</v>
       </c>
       <c r="W73" s="2">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="Y73" t="s">
         <v>261</v>
@@ -5964,7 +5964,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -6032,7 +6032,7 @@
         <v>1480</v>
       </c>
       <c r="L75" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6100,7 +6100,7 @@
         <v>1524</v>
       </c>
       <c r="L76" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M76" t="s">
         <v>263</v>
@@ -6168,7 +6168,7 @@
         <v>1537</v>
       </c>
       <c r="L77" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M77" t="s">
         <v>263</v>
@@ -6236,7 +6236,7 @@
         <v>1537</v>
       </c>
       <c r="L78" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M78" t="s">
         <v>263</v>
@@ -6304,7 +6304,7 @@
         <v>1550</v>
       </c>
       <c r="L79" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M79" t="s">
         <v>263</v>
@@ -6369,10 +6369,10 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>1403</v>
+        <v>1429</v>
       </c>
       <c r="L80" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M80" t="s">
         <v>263</v>
@@ -6393,7 +6393,7 @@
         <v>267</v>
       </c>
       <c r="W80" s="2">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="Y80" t="s">
         <v>261</v>
@@ -6440,7 +6440,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6744,7 +6744,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6812,7 +6812,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6880,7 +6880,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6989,7 +6989,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46260.22043981482</v>
+        <v>46265.21172453704</v>
       </c>
       <c r="M90" t="s">
         <v>263</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="272">
   <si>
     <t>site_name</t>
   </si>
@@ -830,9 +830,6 @@
   </si>
   <si>
     <t>PRIMARY_PARSER</t>
-  </si>
-  <si>
-    <t>static:detail_date</t>
   </si>
 </sst>
 </file>
@@ -1550,7 +1547,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1993,7 +1990,7 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M13" t="s">
         <v>263</v>
@@ -2058,16 +2055,16 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>3532</v>
+        <v>3534</v>
       </c>
       <c r="L14" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N14" t="s">
         <v>256</v>
@@ -2126,16 +2123,16 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>3486</v>
+        <v>3490</v>
       </c>
       <c r="L15" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N15" t="s">
         <v>256</v>
@@ -2153,7 +2150,7 @@
         <v>267</v>
       </c>
       <c r="W15" s="2">
-        <v>46254</v>
+        <v>46266</v>
       </c>
       <c r="Y15" t="s">
         <v>261</v>
@@ -2197,10 +2194,10 @@
         <v>2</v>
       </c>
       <c r="K16">
-        <v>3491</v>
+        <v>3507</v>
       </c>
       <c r="L16" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2221,7 +2218,7 @@
         <v>267</v>
       </c>
       <c r="W16" s="2">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="Y16" t="s">
         <v>261</v>
@@ -2321,16 +2318,16 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>3613</v>
+        <v>3616</v>
       </c>
       <c r="L18" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N18" t="s">
         <v>256</v>
@@ -2572,7 +2569,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2640,7 +2637,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2708,7 +2705,7 @@
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2776,7 +2773,7 @@
         <v>135</v>
       </c>
       <c r="L25" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M25" t="s">
         <v>263</v>
@@ -2844,7 +2841,7 @@
         <v>128</v>
       </c>
       <c r="L26" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M26" t="s">
         <v>263</v>
@@ -3201,13 +3198,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K32">
-        <v>8182</v>
+        <v>8776</v>
       </c>
       <c r="L32" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M32" t="s">
         <v>261</v>
@@ -3228,7 +3225,7 @@
         <v>267</v>
       </c>
       <c r="W32" s="2">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="Y32" t="s">
         <v>261</v>
@@ -3393,7 +3390,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3461,7 +3458,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3529,7 +3526,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3597,7 +3594,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3665,7 +3662,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3733,7 +3730,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3801,7 +3798,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3869,7 +3866,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3937,7 +3934,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -4058,13 +4055,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K45">
-        <v>3039</v>
+        <v>3100</v>
       </c>
       <c r="L45" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4085,7 +4082,7 @@
         <v>267</v>
       </c>
       <c r="W45" s="2">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4129,10 +4126,10 @@
         <v>20</v>
       </c>
       <c r="K46">
-        <v>3666</v>
+        <v>3803</v>
       </c>
       <c r="L46" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4153,7 +4150,7 @@
         <v>267</v>
       </c>
       <c r="W46" s="2">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4194,13 +4191,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K47">
-        <v>3612</v>
+        <v>3666</v>
       </c>
       <c r="L47" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4221,7 +4218,7 @@
         <v>267</v>
       </c>
       <c r="W47" s="2">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4268,7 +4265,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4336,7 +4333,7 @@
         <v>1485</v>
       </c>
       <c r="L49" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M49" t="s">
         <v>263</v>
@@ -4401,10 +4398,10 @@
         <v>2</v>
       </c>
       <c r="K50">
-        <v>1547</v>
+        <v>1557</v>
       </c>
       <c r="L50" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M50" t="s">
         <v>262</v>
@@ -4425,7 +4422,7 @@
         <v>267</v>
       </c>
       <c r="W50" s="2">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="Y50" t="s">
         <v>261</v>
@@ -4466,16 +4463,16 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51">
-        <v>1468</v>
+        <v>1476</v>
       </c>
       <c r="L51" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N51" t="s">
         <v>256</v>
@@ -4493,7 +4490,7 @@
         <v>267</v>
       </c>
       <c r="W51" s="2">
-        <v>46247</v>
+        <v>46265</v>
       </c>
       <c r="Y51" t="s">
         <v>261</v>
@@ -4540,7 +4537,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4602,13 +4599,13 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>1957</v>
+        <v>1964</v>
       </c>
       <c r="L53" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M53" t="s">
         <v>261</v>
@@ -4629,7 +4626,7 @@
         <v>267</v>
       </c>
       <c r="W53" s="2">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="Y53" t="s">
         <v>261</v>
@@ -4670,16 +4667,16 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="L54" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N54" t="s">
         <v>256</v>
@@ -4697,7 +4694,7 @@
         <v>267</v>
       </c>
       <c r="W54" s="2">
-        <v>46253</v>
+        <v>46267</v>
       </c>
       <c r="Y54" t="s">
         <v>261</v>
@@ -4738,13 +4735,13 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K55">
-        <v>1849</v>
+        <v>1912</v>
       </c>
       <c r="L55" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M55" t="s">
         <v>261</v>
@@ -4765,7 +4762,7 @@
         <v>267</v>
       </c>
       <c r="W55" s="2">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="Y55" t="s">
         <v>261</v>
@@ -4868,10 +4865,10 @@
         <v>2</v>
       </c>
       <c r="K57">
-        <v>3783</v>
+        <v>3790</v>
       </c>
       <c r="L57" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M57" t="s">
         <v>262</v>
@@ -4892,7 +4889,7 @@
         <v>267</v>
       </c>
       <c r="W57" s="2">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="Y57" t="s">
         <v>261</v>
@@ -5172,10 +5169,10 @@
         <v>1</v>
       </c>
       <c r="K62">
-        <v>1634</v>
+        <v>1641</v>
       </c>
       <c r="L62" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M62" t="s">
         <v>262</v>
@@ -5196,7 +5193,7 @@
         <v>267</v>
       </c>
       <c r="W62" s="2">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="Y62" t="s">
         <v>261</v>
@@ -5355,13 +5352,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K65">
-        <v>3548</v>
+        <v>3692</v>
       </c>
       <c r="L65" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5382,7 +5379,7 @@
         <v>267</v>
       </c>
       <c r="W65" s="2">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="Y65" t="s">
         <v>261</v>
@@ -5429,7 +5426,7 @@
         <v>3037</v>
       </c>
       <c r="L66" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5494,10 +5491,10 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>1659</v>
+        <v>1674</v>
       </c>
       <c r="L67" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M67" t="s">
         <v>263</v>
@@ -5518,7 +5515,7 @@
         <v>267</v>
       </c>
       <c r="W67" s="2">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="Y67" t="s">
         <v>261</v>
@@ -5559,13 +5556,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K68">
-        <v>3398</v>
+        <v>3510</v>
       </c>
       <c r="L68" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5586,7 +5583,7 @@
         <v>267</v>
       </c>
       <c r="W68" s="2">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="Y68" t="s">
         <v>261</v>
@@ -5633,7 +5630,7 @@
         <v>3058</v>
       </c>
       <c r="L69" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5695,13 +5692,13 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K70">
-        <v>2150</v>
+        <v>2218</v>
       </c>
       <c r="L70" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M70" t="s">
         <v>261</v>
@@ -5722,7 +5719,7 @@
         <v>267</v>
       </c>
       <c r="W70" s="2">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="Y70" t="s">
         <v>261</v>
@@ -5763,13 +5760,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K71">
-        <v>2173</v>
+        <v>2207</v>
       </c>
       <c r="L71" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5790,7 +5787,7 @@
         <v>267</v>
       </c>
       <c r="W71" s="2">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="Y71" t="s">
         <v>261</v>
@@ -5799,7 +5796,7 @@
         <v>270</v>
       </c>
       <c r="AA71" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -5893,10 +5890,10 @@
         <v>1</v>
       </c>
       <c r="K73">
-        <v>1299</v>
+        <v>1306</v>
       </c>
       <c r="L73" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M73" t="s">
         <v>262</v>
@@ -5964,7 +5961,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -6032,7 +6029,7 @@
         <v>1480</v>
       </c>
       <c r="L75" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6100,7 +6097,7 @@
         <v>1524</v>
       </c>
       <c r="L76" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M76" t="s">
         <v>263</v>
@@ -6168,7 +6165,7 @@
         <v>1537</v>
       </c>
       <c r="L77" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M77" t="s">
         <v>263</v>
@@ -6236,7 +6233,7 @@
         <v>1537</v>
       </c>
       <c r="L78" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M78" t="s">
         <v>263</v>
@@ -6304,7 +6301,7 @@
         <v>1550</v>
       </c>
       <c r="L79" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M79" t="s">
         <v>263</v>
@@ -6366,16 +6363,16 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K80">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="L80" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M80" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N80" t="s">
         <v>256</v>
@@ -6393,7 +6390,7 @@
         <v>267</v>
       </c>
       <c r="W80" s="2">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="Y80" t="s">
         <v>261</v>
@@ -6440,7 +6437,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6744,7 +6741,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6812,7 +6809,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6880,7 +6877,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6989,7 +6986,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46265.21172453704</v>
+        <v>46268.21164351852</v>
       </c>
       <c r="M90" t="s">
         <v>263</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -1547,7 +1547,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1990,7 +1990,7 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M13" t="s">
         <v>263</v>
@@ -2061,7 +2061,7 @@
         <v>3534</v>
       </c>
       <c r="L14" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M14" t="s">
         <v>263</v>
@@ -2126,10 +2126,10 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="L15" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M15" t="s">
         <v>262</v>
@@ -2194,10 +2194,10 @@
         <v>2</v>
       </c>
       <c r="K16">
-        <v>3507</v>
+        <v>3509</v>
       </c>
       <c r="L16" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2324,7 +2324,7 @@
         <v>3616</v>
       </c>
       <c r="L18" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M18" t="s">
         <v>263</v>
@@ -2569,7 +2569,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2637,7 +2637,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2705,7 +2705,7 @@
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2773,7 +2773,7 @@
         <v>135</v>
       </c>
       <c r="L25" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M25" t="s">
         <v>263</v>
@@ -2841,7 +2841,7 @@
         <v>128</v>
       </c>
       <c r="L26" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M26" t="s">
         <v>263</v>
@@ -3201,10 +3201,10 @@
         <v>102</v>
       </c>
       <c r="K32">
-        <v>8776</v>
+        <v>8878</v>
       </c>
       <c r="L32" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M32" t="s">
         <v>261</v>
@@ -3390,7 +3390,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3458,7 +3458,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3526,7 +3526,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3594,7 +3594,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3662,7 +3662,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3730,7 +3730,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3798,7 +3798,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3866,7 +3866,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3934,7 +3934,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -4058,10 +4058,10 @@
         <v>14</v>
       </c>
       <c r="K45">
-        <v>3100</v>
+        <v>3114</v>
       </c>
       <c r="L45" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4126,10 +4126,10 @@
         <v>20</v>
       </c>
       <c r="K46">
-        <v>3803</v>
+        <v>3823</v>
       </c>
       <c r="L46" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4194,10 +4194,10 @@
         <v>11</v>
       </c>
       <c r="K47">
-        <v>3666</v>
+        <v>3677</v>
       </c>
       <c r="L47" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4265,7 +4265,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4333,7 +4333,7 @@
         <v>1485</v>
       </c>
       <c r="L49" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M49" t="s">
         <v>263</v>
@@ -4398,10 +4398,10 @@
         <v>2</v>
       </c>
       <c r="K50">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="L50" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M50" t="s">
         <v>262</v>
@@ -4466,10 +4466,10 @@
         <v>2</v>
       </c>
       <c r="K51">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="L51" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M51" t="s">
         <v>262</v>
@@ -4537,7 +4537,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4602,10 +4602,10 @@
         <v>4</v>
       </c>
       <c r="K53">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="L53" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M53" t="s">
         <v>261</v>
@@ -4670,10 +4670,10 @@
         <v>2</v>
       </c>
       <c r="K54">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="L54" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M54" t="s">
         <v>262</v>
@@ -4738,10 +4738,10 @@
         <v>10</v>
       </c>
       <c r="K55">
-        <v>1912</v>
+        <v>1922</v>
       </c>
       <c r="L55" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M55" t="s">
         <v>261</v>
@@ -4865,10 +4865,10 @@
         <v>2</v>
       </c>
       <c r="K57">
-        <v>3790</v>
+        <v>3792</v>
       </c>
       <c r="L57" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M57" t="s">
         <v>262</v>
@@ -5169,10 +5169,10 @@
         <v>1</v>
       </c>
       <c r="K62">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="L62" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M62" t="s">
         <v>262</v>
@@ -5355,10 +5355,10 @@
         <v>30</v>
       </c>
       <c r="K65">
-        <v>3692</v>
+        <v>3722</v>
       </c>
       <c r="L65" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5426,7 +5426,7 @@
         <v>3037</v>
       </c>
       <c r="L66" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5494,7 +5494,7 @@
         <v>1674</v>
       </c>
       <c r="L67" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M67" t="s">
         <v>263</v>
@@ -5556,13 +5556,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K68">
-        <v>3510</v>
+        <v>3528</v>
       </c>
       <c r="L68" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5630,7 +5630,7 @@
         <v>3058</v>
       </c>
       <c r="L69" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5695,10 +5695,10 @@
         <v>9</v>
       </c>
       <c r="K70">
-        <v>2218</v>
+        <v>2227</v>
       </c>
       <c r="L70" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M70" t="s">
         <v>261</v>
@@ -5763,10 +5763,10 @@
         <v>8</v>
       </c>
       <c r="K71">
-        <v>2207</v>
+        <v>2215</v>
       </c>
       <c r="L71" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5890,10 +5890,10 @@
         <v>1</v>
       </c>
       <c r="K73">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="L73" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M73" t="s">
         <v>262</v>
@@ -5961,7 +5961,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -6029,7 +6029,7 @@
         <v>1480</v>
       </c>
       <c r="L75" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6097,7 +6097,7 @@
         <v>1524</v>
       </c>
       <c r="L76" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M76" t="s">
         <v>263</v>
@@ -6165,7 +6165,7 @@
         <v>1537</v>
       </c>
       <c r="L77" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M77" t="s">
         <v>263</v>
@@ -6233,7 +6233,7 @@
         <v>1537</v>
       </c>
       <c r="L78" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M78" t="s">
         <v>263</v>
@@ -6301,7 +6301,7 @@
         <v>1550</v>
       </c>
       <c r="L79" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M79" t="s">
         <v>263</v>
@@ -6366,10 +6366,10 @@
         <v>4</v>
       </c>
       <c r="K80">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="L80" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M80" t="s">
         <v>261</v>
@@ -6437,7 +6437,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6741,7 +6741,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6809,7 +6809,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6877,7 +6877,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6986,7 +6986,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46268.21164351852</v>
+        <v>46268.26371527778</v>
       </c>
       <c r="M90" t="s">
         <v>263</v>
